--- a/templates/Training-Template.xlsx
+++ b/templates/Training-Template.xlsx
@@ -7,7 +7,6 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily" sheetId="3" r:id="R39db2b52ea4f47f3"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoring" sheetId="4" r:id="R2292ea7965d44d65"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="5" r:id="Rd2921e9d0a2e433b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loads" sheetId="6" r:id="Rbc1a7e7a33164042"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -171,7 +170,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:styleSheet xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="21">
     <x:numFmt numFmtId="164" formatCode="General"/>
     <x:numFmt numFmtId="165" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
@@ -195,7 +194,7 @@
     <x:numFmt numFmtId="205" formatCode="0.0;-0.0;;@"/>
     <x:numFmt numFmtId="206" formatCode="0.0%;-0.0%;;@"/>
   </x:numFmts>
-  <x:fonts count="35">
+  <x:fonts count="71">
     <x:font>
       <x:sz val="10"/>
       <x:name val="Arial"/>
@@ -402,8 +401,220 @@
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF243247"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF243247"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF243247"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF243247"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF475569"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF355A4B"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF475569"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF64748B"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF334D45"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF334D45"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF475569"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF253442"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF263343"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF33465B"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF263343"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="68">
+  <x:fills count="138">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -740,8 +951,354 @@
         <x:fgColor rgb="FFF3F8F5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E3EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF33465E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EFF8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F2F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6ECF3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4D5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EDEE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F3F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEFF5F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEBE4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE4EAF0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F9FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE6ECEA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F3F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCEAE3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE4EAF0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3ED"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3ED"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F9F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F9FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3ED"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3ED"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F9F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE4EAF0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F9FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3ED"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F9F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F9FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE4EAF0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE3EAF0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F2EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F8F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF2F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7F3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF1F8F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7F3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE9E3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDEE7EE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5F1E9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE9E3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDEE7EE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE9E3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDEE7EE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5F1E9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE9E3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDEE7EE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5F1E9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2E9EF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF2F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F2EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F8F5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE4EAF0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F3F4"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="11">
+  <x:borders count="23">
     <x:border diagonalUp="0" diagonalDown="0">
       <x:left/>
       <x:right/>
@@ -845,6 +1402,186 @@
       </x:bottom>
       <x:diagonal/>
     </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFC5D1D5"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFC5D1D5"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFC5D1D5"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFC5D1D5"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:left>
+      <x:right style="medium">
+        <x:color rgb="FF94A3B8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E9ED"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="33">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -893,7 +1630,7 @@
     <x:xf numFmtId="173" fontId="4" fillId="0" borderId="0" applyFont="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="174" fontId="4" fillId="0" borderId="0" applyFont="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="490">
+  <x:cellXfs count="529">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <x:alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -1059,7 +1796,7 @@
       <x:protection locked="1" hidden="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1259,7 +1996,7 @@
       <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1276,7 +2013,7 @@
       <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1293,7 +2030,7 @@
       <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1304,7 +2041,7 @@
       <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1372,7 +2109,7 @@
       <x:alignment horizontal="general" vertical="center" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1389,7 +2126,7 @@
       <x:alignment horizontal="general" vertical="center" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1400,7 +2137,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1411,7 +2148,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1422,7 +2159,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1433,7 +2170,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1462,7 +2199,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1470,7 +2207,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1478,7 +2215,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1486,7 +2223,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1635,7 +2372,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1670,7 +2407,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1699,7 +2436,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1722,7 +2459,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1772,7 +2509,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1780,7 +2517,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1827,7 +2564,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1847,7 +2584,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -1990,7 +2727,7 @@
       <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2001,7 +2738,7 @@
       <x:alignment horizontal="general" vertical="center" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2021,7 +2758,7 @@
       <x:alignment horizontal="general" vertical="center" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2029,7 +2766,7 @@
       <x:alignment horizontal="general" vertical="center" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2043,7 +2780,7 @@
       <x:alignment horizontal="general" vertical="center" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2051,7 +2788,7 @@
       <x:alignment horizontal="general" vertical="center" wrapText="0"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2230,7 +2967,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2464,7 +3201,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2490,7 +3227,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2519,7 +3256,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2548,7 +3285,7 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+          <ns1:xfComplement i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
@@ -2574,6 +3311,134 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="16" fillId="65" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="16" fillId="65" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="16" fillId="67" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="31" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="70" fillId="136" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="53" fillId="137" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="53" fillId="137" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="70" fillId="136" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="53" fillId="137" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="0" applyProtection="0" applyFill="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="16" fillId="65" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <ns1:xfComplement i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="16" fillId="65" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="16" fillId="67" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <ns1:xfComplement i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="16" fillId="67" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="55" fillId="136" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="56" fillId="137" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="177" fontId="16" fillId="65" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="177" fontId="16" fillId="67" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2821,7 +3686,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TrainingScoring" displayName="TrainingScoring" ref="A4:S172" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TrainingScoring" displayName="TrainingScoring" ref="A2:S170" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="Date"/>
     <x:tableColumn id="2" name="Session"/>
@@ -2843,18 +3708,18 @@
     <x:tableColumn id="18" name="Scored metrics"/>
     <x:tableColumn id="19" name="Planned metrics"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ScoringAssumptions" displayName="ScoringAssumptions" ref="A176:C177" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ScoringAssumptions" displayName="ScoringAssumptions" ref="A174:C175" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="Setting"/>
     <x:tableColumn id="2" name="Value"/>
     <x:tableColumn id="3" name="Unit"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -2863,11 +3728,11 @@
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Group"/>
     <x:tableColumn id="2" name="Exercise"/>
-    <x:tableColumn id="3" name="Base intensity (0–10)"/>
-    <x:tableColumn id="4" name="Unit"/>
+    <x:tableColumn id="3" name="Unit"/>
+    <x:tableColumn id="4" name="Base intensity (0–10)"/>
     <x:tableColumn id="5" name="Growth per kg"/>
   </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <x:tableStyleInfo name="" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </x:table>
 </file>
 
@@ -3055,42 +3920,42 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" hidden="0" customHeight="1">
-      <x:c r="A1" s="181" t="s">
+      <x:c r="A1" t="s" s="493">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="181"/>
-      <x:c r="C1" s="181"/>
-      <x:c r="D1" s="181"/>
-      <x:c r="E1" s="181"/>
-      <x:c r="F1" s="181"/>
-      <x:c r="G1" s="181"/>
-      <x:c r="H1" s="175"/>
-      <x:c r="I1" s="175"/>
+      <x:c r="B1" s="493"/>
+      <x:c r="C1" s="493"/>
+      <x:c r="D1" s="493"/>
+      <x:c r="E1" s="493"/>
+      <x:c r="F1" s="493"/>
+      <x:c r="G1" s="493"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
     </x:row>
     <x:row r="2" ht="28" hidden="0" customHeight="1">
-      <x:c r="A2" s="183" t="s">
+      <x:c r="A2" t="s" s="494">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B2" s="183" t="s">
+      <x:c r="B2" t="s" s="494">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C2" s="183" t="s">
+      <x:c r="C2" t="s" s="494">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D2" s="183" t="s">
+      <x:c r="D2" t="s" s="494">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E2" s="183" t="s">
+      <x:c r="E2" t="s" s="494">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F2" s="183" t="str">
+      <x:c r="F2" t="str" s="494">
         <x:v>max_sets</x:v>
       </x:c>
-      <x:c r="G2" s="292" t="str">
+      <x:c r="G2" t="str" s="495">
         <x:v>max_reps</x:v>
       </x:c>
-      <x:c r="H2" s="175"/>
-      <x:c r="I2" s="175"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
     </x:row>
     <x:row r="3" ht="54" hidden="0" customHeight="1">
       <x:c r="A3" s="177" t="s">
@@ -3118,59 +3983,56 @@
       <x:c r="G3" s="295" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H3" s="179"/>
-      <x:c r="I3" s="179"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
     </x:row>
     <x:row r="4" ht="18" hidden="0" customHeight="1">
-      <x:c r="A4" s="174"/>
-      <x:c r="B4" s="174"/>
-      <x:c r="C4" s="174"/>
-      <x:c r="D4" s="174"/>
-      <x:c r="E4" s="174"/>
-      <x:c r="F4" s="174"/>
-      <x:c r="G4" s="174"/>
-      <x:c r="H4" s="175"/>
-      <x:c r="I4" s="175"/>
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
     </x:row>
     <x:row r="5" ht="26" hidden="0" customHeight="1">
-      <x:c r="A5" s="181" t="s">
+      <x:c r="A5" t="s" s="493">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B5" s="181"/>
-      <x:c r="C5" s="181"/>
-      <x:c r="D5" s="181"/>
-      <x:c r="E5" s="181"/>
-      <x:c r="F5" s="181"/>
-      <x:c r="G5" s="181"/>
-      <x:c r="H5" s="185"/>
-      <x:c r="I5" s="179"/>
+      <x:c r="B5" s="493"/>
+      <x:c r="C5" s="493"/>
+      <x:c r="D5" s="493"/>
+      <x:c r="E5" s="493"/>
+      <x:c r="F5" s="493"/>
+      <x:c r="G5" s="493"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
     </x:row>
     <x:row r="6" ht="28" hidden="0" customHeight="1">
-      <x:c r="A6" s="183" t="s">
+      <x:c r="A6" t="s" s="494">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B6" s="183" t="s">
+      <x:c r="B6" t="s" s="494">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C6" s="183" t="s">
+      <x:c r="C6" t="s" s="494">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D6" s="183" t="s">
+      <x:c r="D6" t="s" s="494">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E6" s="183" t="s">
+      <x:c r="E6" t="s" s="494">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="F6" s="183" t="s">
+      <x:c r="F6" t="s" s="494">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G6" s="183" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H6" s="183" t="s">
+      <x:c r="G6" t="s" s="494">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="I6" s="175"/>
+      <x:c r="I6"/>
     </x:row>
     <x:row r="7" ht="76" hidden="0" customHeight="1">
       <x:c r="A7" s="177"/>
@@ -3179,9 +4041,8 @@
       <x:c r="D7" s="278"/>
       <x:c r="E7" s="278"/>
       <x:c r="F7" s="278"/>
-      <x:c r="G7" s="278"/>
-      <x:c r="H7" s="282"/>
-      <x:c r="I7" s="179"/>
+      <x:c r="G7" s="282"/>
+      <x:c r="I7"/>
     </x:row>
     <x:row r="8" ht="76" hidden="0" customHeight="1">
       <x:c r="A8" s="174"/>
@@ -3190,9 +4051,8 @@
       <x:c r="D8" s="283"/>
       <x:c r="E8" s="283"/>
       <x:c r="F8" s="283"/>
-      <x:c r="G8" s="283"/>
-      <x:c r="H8" s="284"/>
-      <x:c r="I8" s="175"/>
+      <x:c r="G8" s="284"/>
+      <x:c r="I8"/>
     </x:row>
     <x:row r="9" ht="76" hidden="0" customHeight="1">
       <x:c r="A9" s="177"/>
@@ -3201,9 +4061,8 @@
       <x:c r="D9" s="278"/>
       <x:c r="E9" s="278"/>
       <x:c r="F9" s="278"/>
-      <x:c r="G9" s="278"/>
-      <x:c r="H9" s="282"/>
-      <x:c r="I9" s="179"/>
+      <x:c r="G9" s="282"/>
+      <x:c r="I9"/>
     </x:row>
     <x:row r="10" ht="76" hidden="0" customHeight="1">
       <x:c r="A10" s="174"/>
@@ -3212,9 +4071,8 @@
       <x:c r="D10" s="283"/>
       <x:c r="E10" s="283"/>
       <x:c r="F10" s="283"/>
-      <x:c r="G10" s="283"/>
-      <x:c r="H10" s="284"/>
-      <x:c r="I10" s="175"/>
+      <x:c r="G10" s="284"/>
+      <x:c r="I10"/>
     </x:row>
     <x:row r="11" ht="84" hidden="0" customHeight="1">
       <x:c r="A11" s="177"/>
@@ -3223,43 +4081,42 @@
       <x:c r="D11" s="278"/>
       <x:c r="E11" s="278"/>
       <x:c r="F11" s="278"/>
-      <x:c r="G11" s="278"/>
-      <x:c r="H11" s="282"/>
-      <x:c r="I11" s="179"/>
+      <x:c r="G11" s="282"/>
+      <x:c r="I11"/>
     </x:row>
     <x:row r="12" ht="26" hidden="0" customHeight="1">
-      <x:c r="A12" s="181" t="s">
+      <x:c r="A12" t="s" s="493">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B12" s="181"/>
-      <x:c r="C12" s="181"/>
-      <x:c r="D12" s="181"/>
-      <x:c r="E12" s="181"/>
-      <x:c r="F12" s="174"/>
-      <x:c r="G12" s="174"/>
-      <x:c r="H12" s="175"/>
-      <x:c r="I12" s="175"/>
+      <x:c r="B12" s="493"/>
+      <x:c r="C12" s="493"/>
+      <x:c r="D12" s="493"/>
+      <x:c r="E12" s="493"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
     </x:row>
     <x:row r="13" ht="28" hidden="0" customHeight="1">
-      <x:c r="A13" s="183" t="s">
+      <x:c r="A13" t="s" s="494">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B13" s="183" t="s">
+      <x:c r="B13" t="s" s="494">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C13" s="183" t="s">
+      <x:c r="C13" t="s" s="494">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D13" s="183" t="s">
+      <x:c r="D13" t="s" s="494">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E13" s="183" t="s">
+      <x:c r="E13" t="s" s="494">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F13" s="177"/>
-      <x:c r="G13" s="177"/>
-      <x:c r="H13" s="179"/>
-      <x:c r="I13" s="179"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
     </x:row>
     <x:row r="14" ht="110" hidden="0" customHeight="1">
       <x:c r="A14" s="174"/>
@@ -3267,10 +4124,10 @@
       <x:c r="C14" s="174"/>
       <x:c r="D14" s="385"/>
       <x:c r="E14" s="283"/>
-      <x:c r="F14" s="174"/>
-      <x:c r="G14" s="174"/>
-      <x:c r="H14" s="175"/>
-      <x:c r="I14" s="175"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
     </x:row>
     <x:row r="15" ht="110" hidden="0" customHeight="1">
       <x:c r="A15" s="177"/>
@@ -3278,10 +4135,10 @@
       <x:c r="C15" s="177"/>
       <x:c r="D15" s="278"/>
       <x:c r="E15" s="278"/>
-      <x:c r="F15" s="177"/>
-      <x:c r="G15" s="177"/>
-      <x:c r="H15" s="179"/>
-      <x:c r="I15" s="179"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
     </x:row>
     <x:row r="16" ht="110" hidden="0" customHeight="1">
       <x:c r="A16" s="174"/>
@@ -3289,10 +4146,10 @@
       <x:c r="C16" s="174"/>
       <x:c r="D16" s="283"/>
       <x:c r="E16" s="283"/>
-      <x:c r="F16" s="174"/>
-      <x:c r="G16" s="174"/>
-      <x:c r="H16" s="175"/>
-      <x:c r="I16" s="175"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16"/>
     </x:row>
     <x:row r="17" ht="110" hidden="0" customHeight="1">
       <x:c r="A17" s="177"/>
@@ -3300,61 +4157,61 @@
       <x:c r="C17" s="177"/>
       <x:c r="D17" s="278"/>
       <x:c r="E17" s="278"/>
-      <x:c r="F17" s="177"/>
-      <x:c r="G17" s="177"/>
-      <x:c r="H17" s="179"/>
-      <x:c r="I17" s="179"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+      <x:c r="I17"/>
     </x:row>
     <x:row r="18" ht="18" hidden="0" customHeight="1">
-      <x:c r="A18" s="175"/>
-      <x:c r="B18" s="175"/>
-      <x:c r="C18" s="175"/>
-      <x:c r="D18" s="175"/>
-      <x:c r="E18" s="175"/>
-      <x:c r="F18" s="175"/>
-      <x:c r="G18" s="175"/>
-      <x:c r="H18" s="175"/>
-      <x:c r="I18" s="175"/>
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+      <x:c r="I18"/>
     </x:row>
     <x:row r="19" ht="26" hidden="0" customHeight="1">
-      <x:c r="A19" s="181" t="s">
+      <x:c r="A19" t="s" s="493">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B19" s="181"/>
-      <x:c r="C19" s="181"/>
-      <x:c r="D19" s="181"/>
-      <x:c r="E19" s="181"/>
-      <x:c r="F19" s="181"/>
-      <x:c r="G19" s="181"/>
-      <x:c r="H19" s="185"/>
-      <x:c r="I19" s="185"/>
+      <x:c r="B19" s="493"/>
+      <x:c r="C19" s="493"/>
+      <x:c r="D19" s="493"/>
+      <x:c r="E19" s="493"/>
+      <x:c r="F19" s="493"/>
+      <x:c r="G19" s="493"/>
+      <x:c r="H19" s="496"/>
+      <x:c r="I19" s="496"/>
     </x:row>
     <x:row r="20" ht="28" hidden="0" customHeight="1">
-      <x:c r="A20" s="183" t="s">
+      <x:c r="A20" t="s" s="494">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B20" s="183" t="s">
+      <x:c r="B20" t="s" s="494">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C20" s="183" t="s">
+      <x:c r="C20" t="s" s="494">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D20" s="183" t="s">
+      <x:c r="D20" t="s" s="494">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E20" s="183" t="s">
+      <x:c r="E20" t="s" s="494">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F20" s="183" t="s">
+      <x:c r="F20" t="s" s="494">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="G20" s="183" t="s">
+      <x:c r="G20" t="s" s="494">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="H20" s="183" t="s">
+      <x:c r="H20" t="s" s="494">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="I20" s="183" t="s">
+      <x:c r="I20" t="s" s="494">
         <x:v>23</x:v>
       </x:c>
     </x:row>
@@ -3491,23 +4348,23 @@
       <x:c r="I32" s="283"/>
     </x:row>
     <x:row r="33" ht="18" hidden="0" customHeight="1">
-      <x:c r="A33" s="179"/>
-      <x:c r="B33" s="179"/>
-      <x:c r="C33" s="179"/>
-      <x:c r="D33" s="179"/>
-      <x:c r="E33" s="179"/>
-      <x:c r="F33" s="179"/>
-      <x:c r="G33" s="179"/>
-      <x:c r="H33" s="179"/>
-      <x:c r="I33" s="179"/>
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+      <x:c r="I33"/>
     </x:row>
     <x:row r="34" ht="26" hidden="0" customHeight="1">
-      <x:c r="A34" s="394" t="str">
+      <x:c r="A34" t="str" s="497">
         <x:v>Plan summary</x:v>
       </x:c>
-      <x:c r="B34" s="394"/>
-      <x:c r="C34" s="394"/>
-      <x:c r="D34" s="394"/>
+      <x:c r="B34" s="497"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
       <x:c r="E34"/>
       <x:c r="F34"/>
       <x:c r="G34"/>
@@ -3515,14 +4372,14 @@
       <x:c r="I34"/>
     </x:row>
     <x:row r="35" ht="26" hidden="0" customHeight="1">
-      <x:c r="A35" s="397" t="str">
+      <x:c r="A35" t="str" s="498">
         <x:v>Metric</x:v>
       </x:c>
-      <x:c r="B35" s="397" t="str">
+      <x:c r="B35" t="str" s="498">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="C35" s="391"/>
-      <x:c r="D35" s="391"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
       <x:c r="E35"/>
       <x:c r="F35"/>
       <x:c r="G35"/>
@@ -3534,8 +4391,8 @@
         <x:v>Planned sessions</x:v>
       </x:c>
       <x:c r="B36" s="391"/>
-      <x:c r="C36" s="391"/>
-      <x:c r="D36" s="391"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
       <x:c r="E36"/>
       <x:c r="F36"/>
       <x:c r="G36"/>
@@ -3547,8 +4404,8 @@
         <x:v>Completed sessions</x:v>
       </x:c>
       <x:c r="B37" s="391"/>
-      <x:c r="C37" s="391"/>
-      <x:c r="D37" s="391"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
       <x:c r="E37"/>
       <x:c r="F37"/>
       <x:c r="G37"/>
@@ -3560,8 +4417,8 @@
         <x:v>Recorded manual minutes</x:v>
       </x:c>
       <x:c r="B38" s="391"/>
-      <x:c r="C38" s="391"/>
-      <x:c r="D38" s="391"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
       <x:c r="E38"/>
       <x:c r="F38"/>
       <x:c r="G38"/>
@@ -3573,8 +4430,8 @@
         <x:v>Recorded performance (%)</x:v>
       </x:c>
       <x:c r="B39" s="391"/>
-      <x:c r="C39" s="391"/>
-      <x:c r="D39" s="391"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
       <x:c r="E39"/>
       <x:c r="F39"/>
       <x:c r="G39"/>
@@ -3582,10 +4439,10 @@
       <x:c r="I39"/>
     </x:row>
     <x:row r="40" ht="26" hidden="0" customHeight="1">
-      <x:c r="A40" s="391"/>
-      <x:c r="B40" s="391"/>
-      <x:c r="C40" s="391"/>
-      <x:c r="D40" s="391"/>
+      <x:c r="A40"/>
+      <x:c r="B40"/>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
       <x:c r="E40"/>
       <x:c r="F40"/>
       <x:c r="G40"/>
@@ -3593,10 +4450,10 @@
       <x:c r="I40"/>
     </x:row>
     <x:row r="41" ht="26" hidden="0" customHeight="1">
-      <x:c r="A41" s="391"/>
-      <x:c r="B41" s="391"/>
-      <x:c r="C41" s="391"/>
-      <x:c r="D41" s="391"/>
+      <x:c r="A41"/>
+      <x:c r="B41"/>
+      <x:c r="C41"/>
+      <x:c r="D41"/>
       <x:c r="E41"/>
       <x:c r="F41"/>
       <x:c r="G41"/>
@@ -3604,12 +4461,12 @@
       <x:c r="I41"/>
     </x:row>
     <x:row r="42" ht="26" hidden="0" customHeight="1">
-      <x:c r="A42" s="394" t="str">
+      <x:c r="A42" t="str" s="497">
         <x:v>Plan recap</x:v>
       </x:c>
-      <x:c r="B42" s="394"/>
-      <x:c r="C42" s="394"/>
-      <x:c r="D42" s="394"/>
+      <x:c r="B42" s="497"/>
+      <x:c r="C42" s="497"/>
+      <x:c r="D42" s="497"/>
       <x:c r="E42"/>
       <x:c r="F42"/>
       <x:c r="G42"/>
@@ -3617,14 +4474,14 @@
       <x:c r="I42"/>
     </x:row>
     <x:row r="43" ht="26" hidden="0" customHeight="1">
-      <x:c r="A43" s="397" t="str">
+      <x:c r="A43" t="str" s="498">
         <x:v>Prompt</x:v>
       </x:c>
-      <x:c r="B43" s="397" t="str">
+      <x:c r="B43" t="str" s="498">
         <x:v>Response</x:v>
       </x:c>
-      <x:c r="C43" s="397"/>
-      <x:c r="D43" s="397"/>
+      <x:c r="C43" s="498"/>
+      <x:c r="D43" s="498"/>
       <x:c r="E43"/>
       <x:c r="F43"/>
       <x:c r="G43"/>
@@ -4180,7 +5037,7 @@
     <x:row r="1048576" ht="12.800000190734863" hidden="0"/>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A34:D34"/>
+    <x:mergeCell ref="A34:B34"/>
     <x:mergeCell ref="A42:D42"/>
     <x:mergeCell ref="B44:D44"/>
     <x:mergeCell ref="B45:D45"/>
@@ -4217,36 +5074,36 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" hidden="0" customHeight="1">
-      <x:c r="A1" s="306" t="s">
+      <x:c r="A1" t="s" s="499">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B1" s="306"/>
-      <x:c r="C1" s="306"/>
-      <x:c r="D1" s="306"/>
-      <x:c r="E1" s="306"/>
-      <x:c r="F1" s="306"/>
-      <x:c r="G1" s="307"/>
+      <x:c r="B1" s="499"/>
+      <x:c r="C1" s="499"/>
+      <x:c r="D1" s="499"/>
+      <x:c r="E1" s="499"/>
+      <x:c r="F1" s="499"/>
+      <x:c r="G1" s="500"/>
     </x:row>
     <x:row r="2" ht="28" hidden="0" customHeight="1">
-      <x:c r="A2" s="183" t="s">
+      <x:c r="A2" t="s" s="494">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B2" s="183" t="s">
+      <x:c r="B2" t="s" s="494">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C2" s="183" t="s">
+      <x:c r="C2" t="s" s="494">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D2" s="183" t="s">
+      <x:c r="D2" t="s" s="494">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E2" s="183" t="s">
+      <x:c r="E2" t="s" s="494">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F2" s="183" t="s">
+      <x:c r="F2" t="s" s="494">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G2" s="183" t="s">
+      <x:c r="G2" t="s" s="494">
         <x:v>38</x:v>
       </x:c>
     </x:row>
@@ -4421,63 +5278,62 @@
     <x:col min="4" max="4" width="29" style="1" hidden="0" customWidth="1"/>
     <x:col min="5" max="7" width="17" style="1" hidden="0" customWidth="1"/>
     <x:col min="8" max="11" width="9" style="1" hidden="0" customWidth="1"/>
-    <x:col min="12" max="24" width="9" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="18" hidden="0" customWidth="1"/>
-    <x:col min="26" max="27" width="9" hidden="0" customWidth="1"/>
-    <x:col min="28" max="28" width="13" hidden="0" customWidth="1"/>
-    <x:col min="29" max="29" width="32" hidden="0" customWidth="1"/>
-    <x:col min="30" max="32" width="27" hidden="0" customWidth="1"/>
-    <x:col min="33" max="34" width="19" hidden="0" customWidth="1"/>
-    <x:col min="35" max="36" width="24" hidden="0" customWidth="1"/>
-    <x:col min="37" max="38" width="19" hidden="0" customWidth="1"/>
-    <x:col min="16383" max="16384" width="11.529999732971191" hidden="0" customWidth="1"/>
+    <x:col min="12" max="27" width="9" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="18" hidden="0" customWidth="1"/>
+    <x:col min="29" max="30" width="9" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="13" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="32" hidden="0" customWidth="1"/>
+    <x:col min="33" max="35" width="27" hidden="0" customWidth="1"/>
+    <x:col min="36" max="37" width="19" hidden="0" customWidth="1"/>
+    <x:col min="38" max="39" width="24" hidden="0" customWidth="1"/>
+    <x:col min="40" max="41" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" hidden="0" customHeight="1">
-      <x:c r="A1" s="449" t="str">
+      <x:c r="A1" t="str" s="501">
         <x:v>Session</x:v>
       </x:c>
-      <x:c r="B1" s="449"/>
-      <x:c r="C1" s="449"/>
-      <x:c r="D1" s="449"/>
-      <x:c r="E1" s="449"/>
-      <x:c r="F1" s="449"/>
-      <x:c r="G1" s="450"/>
-      <x:c r="H1" s="449" t="str">
+      <x:c r="B1" s="501"/>
+      <x:c r="C1" s="501"/>
+      <x:c r="D1" s="501"/>
+      <x:c r="E1" s="501"/>
+      <x:c r="F1" s="501"/>
+      <x:c r="G1" s="517"/>
+      <x:c r="H1" t="str" s="501">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="I1" s="449"/>
-      <x:c r="J1" s="449"/>
-      <x:c r="K1" s="449"/>
-      <x:c r="L1" s="449"/>
-      <x:c r="M1" s="449" t="str">
+      <x:c r="I1" s="501"/>
+      <x:c r="J1" s="501"/>
+      <x:c r="K1" s="501"/>
+      <x:c r="L1" s="501"/>
+      <x:c r="M1" s="518"/>
+      <x:c r="N1" t="str" s="501">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="N1" s="449"/>
-      <x:c r="O1" s="449"/>
-      <x:c r="P1" s="449"/>
-      <x:c r="Q1" s="449"/>
-      <x:c r="R1" s="449" t="str">
+      <x:c r="O1" s="501"/>
+      <x:c r="P1" s="501"/>
+      <x:c r="Q1" s="501"/>
+      <x:c r="R1" s="501"/>
+      <x:c r="S1" s="518"/>
+      <x:c r="T1" t="str" s="501">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="S1" s="449"/>
-      <x:c r="T1" s="449"/>
-      <x:c r="U1" s="449"/>
-      <x:c r="V1" s="449"/>
-      <x:c r="W1" s="449" t="str">
+      <x:c r="U1" s="501"/>
+      <x:c r="V1" s="501"/>
+      <x:c r="W1" s="501"/>
+      <x:c r="X1" s="501"/>
+      <x:c r="Y1" s="518"/>
+      <x:c r="Z1" t="str" s="525">
         <x:v>Cal-Intervals</x:v>
       </x:c>
-      <x:c r="X1" s="449" t="str">
+      <x:c r="AA1" t="str" s="501">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="Y1" s="449"/>
-      <x:c r="Z1" s="451" t="str">
+      <x:c r="AB1" s="501"/>
+      <x:c r="AC1" t="str" s="503">
         <x:v>Ratings</x:v>
       </x:c>
-      <x:c r="AA1" s="451"/>
-      <x:c r="AB1"/>
-      <x:c r="AC1"/>
-      <x:c r="AD1"/>
+      <x:c r="AD1" s="503"/>
       <x:c r="AE1"/>
       <x:c r="AF1"/>
       <x:c r="AG1"/>
@@ -4486,92 +5342,101 @@
       <x:c r="AJ1"/>
       <x:c r="AK1"/>
       <x:c r="AL1"/>
+      <x:c r="AM1"/>
+      <x:c r="AN1"/>
+      <x:c r="AO1"/>
     </x:row>
     <x:row r="2" ht="42" hidden="0" customHeight="1">
-      <x:c r="A2" s="452" t="s">
+      <x:c r="A2" t="s" s="504">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="B2" s="452" t="s">
+      <x:c r="B2" t="s" s="504">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="C2" s="452" t="s">
+      <x:c r="C2" t="s" s="504">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D2" s="452" t="s">
+      <x:c r="D2" t="s" s="504">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="E2" s="452" t="s">
+      <x:c r="E2" t="s" s="504">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F2" s="452" t="s">
+      <x:c r="F2" t="s" s="504">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G2" s="453" t="str">
+      <x:c r="G2" t="str" s="519">
         <x:v>Session done</x:v>
       </x:c>
-      <x:c r="H2" s="454" t="n">
+      <x:c r="H2" t="n" s="506">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I2" s="454" t="n">
+      <x:c r="I2" t="n" s="506">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J2" s="454" t="n">
+      <x:c r="J2" t="n" s="506">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K2" s="454" t="n">
+      <x:c r="K2" t="n" s="506">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L2" s="454" t="n">
+      <x:c r="L2" t="n" s="506">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="M2" s="454" t="n">
+      <x:c r="M2" t="str" s="520">
+        <x:v>Weight</x:v>
+      </x:c>
+      <x:c r="N2" t="n" s="506">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N2" s="454" t="n">
+      <x:c r="O2" t="n" s="506">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O2" s="454" t="n">
+      <x:c r="P2" t="n" s="506">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P2" s="454" t="n">
+      <x:c r="Q2" t="n" s="506">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="Q2" s="454" t="n">
+      <x:c r="R2" t="n" s="506">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="R2" s="454" t="n">
+      <x:c r="S2" t="str" s="520">
+        <x:v>Weight</x:v>
+      </x:c>
+      <x:c r="T2" t="n" s="506">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="S2" s="454" t="n">
+      <x:c r="U2" t="n" s="506">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="T2" s="454" t="n">
+      <x:c r="V2" t="n" s="506">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="U2" s="454" t="n">
+      <x:c r="W2" t="n" s="506">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="V2" s="454" t="n">
+      <x:c r="X2" t="n" s="506">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="W2" s="454" t="str">
+      <x:c r="Y2" t="str" s="520">
+        <x:v>Weight</x:v>
+      </x:c>
+      <x:c r="Z2" t="str" s="526">
         <x:v>Rounds</x:v>
       </x:c>
-      <x:c r="X2" s="453" t="str">
+      <x:c r="AA2" t="str" s="505">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="Y2" s="454" t="str">
+      <x:c r="AB2" t="str" s="506">
         <x:v>Notes topic</x:v>
       </x:c>
-      <x:c r="Z2" s="337" t="str">
+      <x:c r="AC2" t="str" s="507">
         <x:v>Planned intensity</x:v>
       </x:c>
-      <x:c r="AA2" s="337" t="str">
+      <x:c r="AD2" t="str" s="507">
         <x:v>Effort rating</x:v>
       </x:c>
-      <x:c r="AB2"/>
-      <x:c r="AC2"/>
-      <x:c r="AD2"/>
       <x:c r="AE2"/>
       <x:c r="AF2"/>
       <x:c r="AG2"/>
@@ -4580,6 +5445,9 @@
       <x:c r="AJ2"/>
       <x:c r="AK2"/>
       <x:c r="AL2"/>
+      <x:c r="AM2"/>
+      <x:c r="AN2"/>
+      <x:c r="AO2"/>
     </x:row>
     <x:row r="3" ht="88" hidden="0" customHeight="1">
       <x:c r="A3" s="456"/>
@@ -4588,30 +5456,30 @@
       <x:c r="D3" s="457"/>
       <x:c r="E3" s="457"/>
       <x:c r="F3" s="464"/>
-      <x:c r="G3" s="465"/>
+      <x:c r="G3" s="521"/>
       <x:c r="H3" s="466"/>
       <x:c r="I3" s="466"/>
       <x:c r="J3" s="466"/>
       <x:c r="K3" s="467"/>
       <x:c r="L3" s="467"/>
-      <x:c r="M3" s="466"/>
+      <x:c r="M3" s="522"/>
       <x:c r="N3" s="466"/>
       <x:c r="O3" s="466"/>
-      <x:c r="P3" s="467"/>
+      <x:c r="P3" s="466"/>
       <x:c r="Q3" s="467"/>
-      <x:c r="R3" s="466"/>
-      <x:c r="S3" s="466"/>
+      <x:c r="R3" s="467"/>
+      <x:c r="S3" s="522"/>
       <x:c r="T3" s="466"/>
-      <x:c r="U3" s="467"/>
-      <x:c r="V3" s="467"/>
-      <x:c r="W3" s="466"/>
-      <x:c r="X3" s="468"/>
-      <x:c r="Y3" s="469"/>
-      <x:c r="Z3" s="329"/>
-      <x:c r="AA3" s="328"/>
-      <x:c r="AB3"/>
-      <x:c r="AC3"/>
-      <x:c r="AD3"/>
+      <x:c r="U3" s="466"/>
+      <x:c r="V3" s="466"/>
+      <x:c r="W3" s="467"/>
+      <x:c r="X3" s="467"/>
+      <x:c r="Y3" s="522"/>
+      <x:c r="Z3" s="527"/>
+      <x:c r="AA3" s="468"/>
+      <x:c r="AB3" s="469"/>
+      <x:c r="AC3" s="329"/>
+      <x:c r="AD3" s="328"/>
       <x:c r="AE3"/>
       <x:c r="AF3"/>
       <x:c r="AG3"/>
@@ -4620,6 +5488,9 @@
       <x:c r="AJ3"/>
       <x:c r="AK3"/>
       <x:c r="AL3"/>
+      <x:c r="AM3"/>
+      <x:c r="AN3"/>
+      <x:c r="AO3"/>
     </x:row>
     <x:row r="4" ht="88" hidden="0" customHeight="1">
       <x:c r="A4" s="471"/>
@@ -4628,30 +5499,30 @@
       <x:c r="D4" s="472"/>
       <x:c r="E4" s="472"/>
       <x:c r="F4" s="480"/>
-      <x:c r="G4" s="481"/>
+      <x:c r="G4" s="523"/>
       <x:c r="H4" s="482"/>
       <x:c r="I4" s="483"/>
       <x:c r="J4" s="483"/>
       <x:c r="K4" s="483"/>
       <x:c r="L4" s="483"/>
-      <x:c r="M4" s="482"/>
+      <x:c r="M4" s="524"/>
       <x:c r="N4" s="482"/>
       <x:c r="O4" s="482"/>
-      <x:c r="P4" s="483"/>
+      <x:c r="P4" s="482"/>
       <x:c r="Q4" s="483"/>
-      <x:c r="R4" s="482"/>
-      <x:c r="S4" s="482"/>
-      <x:c r="T4" s="483"/>
-      <x:c r="U4" s="483"/>
+      <x:c r="R4" s="483"/>
+      <x:c r="S4" s="524"/>
+      <x:c r="T4" s="482"/>
+      <x:c r="U4" s="482"/>
       <x:c r="V4" s="483"/>
-      <x:c r="W4" s="484"/>
-      <x:c r="X4" s="485"/>
-      <x:c r="Y4" s="486"/>
-      <x:c r="Z4" s="409"/>
-      <x:c r="AA4" s="487"/>
-      <x:c r="AB4"/>
-      <x:c r="AC4"/>
-      <x:c r="AD4"/>
+      <x:c r="W4" s="483"/>
+      <x:c r="X4" s="483"/>
+      <x:c r="Y4" s="524"/>
+      <x:c r="Z4" s="528"/>
+      <x:c r="AA4" s="485"/>
+      <x:c r="AB4" s="486"/>
+      <x:c r="AC4" s="409"/>
+      <x:c r="AD4" s="487"/>
       <x:c r="AE4"/>
       <x:c r="AF4"/>
       <x:c r="AG4"/>
@@ -4660,6 +5531,9 @@
       <x:c r="AJ4"/>
       <x:c r="AK4"/>
       <x:c r="AL4"/>
+      <x:c r="AM4"/>
+      <x:c r="AN4"/>
+      <x:c r="AO4"/>
     </x:row>
     <x:row r="5" ht="88" hidden="0" customHeight="1">
       <x:c r="A5" s="456"/>
@@ -4668,30 +5542,30 @@
       <x:c r="D5" s="457"/>
       <x:c r="E5" s="457"/>
       <x:c r="F5" s="464"/>
-      <x:c r="G5" s="465"/>
+      <x:c r="G5" s="521"/>
       <x:c r="H5" s="489"/>
       <x:c r="I5" s="489"/>
       <x:c r="J5" s="489"/>
       <x:c r="K5" s="467"/>
       <x:c r="L5" s="467"/>
-      <x:c r="M5" s="466"/>
+      <x:c r="M5" s="522"/>
       <x:c r="N5" s="466"/>
       <x:c r="O5" s="466"/>
-      <x:c r="P5" s="467"/>
+      <x:c r="P5" s="466"/>
       <x:c r="Q5" s="467"/>
-      <x:c r="R5" s="466"/>
-      <x:c r="S5" s="466"/>
+      <x:c r="R5" s="467"/>
+      <x:c r="S5" s="522"/>
       <x:c r="T5" s="466"/>
-      <x:c r="U5" s="467"/>
-      <x:c r="V5" s="467"/>
-      <x:c r="W5" s="466"/>
-      <x:c r="X5" s="468"/>
-      <x:c r="Y5" s="469"/>
-      <x:c r="Z5" s="329"/>
-      <x:c r="AA5" s="328"/>
-      <x:c r="AB5"/>
-      <x:c r="AC5"/>
-      <x:c r="AD5"/>
+      <x:c r="U5" s="466"/>
+      <x:c r="V5" s="466"/>
+      <x:c r="W5" s="467"/>
+      <x:c r="X5" s="467"/>
+      <x:c r="Y5" s="522"/>
+      <x:c r="Z5" s="527"/>
+      <x:c r="AA5" s="468"/>
+      <x:c r="AB5" s="469"/>
+      <x:c r="AC5" s="329"/>
+      <x:c r="AD5" s="328"/>
       <x:c r="AE5"/>
       <x:c r="AF5"/>
       <x:c r="AG5"/>
@@ -4700,6 +5574,9 @@
       <x:c r="AJ5"/>
       <x:c r="AK5"/>
       <x:c r="AL5"/>
+      <x:c r="AM5"/>
+      <x:c r="AN5"/>
+      <x:c r="AO5"/>
     </x:row>
     <x:row r="6" ht="88" hidden="0" customHeight="1">
       <x:c r="A6" s="471"/>
@@ -4708,30 +5585,30 @@
       <x:c r="D6" s="472"/>
       <x:c r="E6" s="472"/>
       <x:c r="F6" s="480"/>
-      <x:c r="G6" s="481"/>
+      <x:c r="G6" s="523"/>
       <x:c r="H6" s="482"/>
       <x:c r="I6" s="483"/>
       <x:c r="J6" s="483"/>
       <x:c r="K6" s="483"/>
       <x:c r="L6" s="483"/>
-      <x:c r="M6" s="482"/>
+      <x:c r="M6" s="524"/>
       <x:c r="N6" s="482"/>
       <x:c r="O6" s="482"/>
-      <x:c r="P6" s="483"/>
+      <x:c r="P6" s="482"/>
       <x:c r="Q6" s="483"/>
-      <x:c r="R6" s="482"/>
-      <x:c r="S6" s="482"/>
+      <x:c r="R6" s="483"/>
+      <x:c r="S6" s="524"/>
       <x:c r="T6" s="482"/>
-      <x:c r="U6" s="483"/>
-      <x:c r="V6" s="483"/>
-      <x:c r="W6" s="484"/>
-      <x:c r="X6" s="485"/>
-      <x:c r="Y6" s="486"/>
-      <x:c r="Z6" s="409"/>
-      <x:c r="AA6" s="487"/>
-      <x:c r="AB6"/>
-      <x:c r="AC6"/>
-      <x:c r="AD6"/>
+      <x:c r="U6" s="482"/>
+      <x:c r="V6" s="482"/>
+      <x:c r="W6" s="483"/>
+      <x:c r="X6" s="483"/>
+      <x:c r="Y6" s="524"/>
+      <x:c r="Z6" s="528"/>
+      <x:c r="AA6" s="485"/>
+      <x:c r="AB6" s="486"/>
+      <x:c r="AC6" s="409"/>
+      <x:c r="AD6" s="487"/>
       <x:c r="AE6"/>
       <x:c r="AF6"/>
       <x:c r="AG6"/>
@@ -4740,6 +5617,9 @@
       <x:c r="AJ6"/>
       <x:c r="AK6"/>
       <x:c r="AL6"/>
+      <x:c r="AM6"/>
+      <x:c r="AN6"/>
+      <x:c r="AO6"/>
     </x:row>
     <x:row r="7" ht="88" hidden="0" customHeight="1">
       <x:c r="A7" s="456"/>
@@ -4748,30 +5628,30 @@
       <x:c r="D7" s="457"/>
       <x:c r="E7" s="457"/>
       <x:c r="F7" s="464"/>
-      <x:c r="G7" s="465"/>
+      <x:c r="G7" s="521"/>
       <x:c r="H7" s="466"/>
       <x:c r="I7" s="466"/>
       <x:c r="J7" s="466"/>
       <x:c r="K7" s="467"/>
       <x:c r="L7" s="467"/>
-      <x:c r="M7" s="466"/>
+      <x:c r="M7" s="522"/>
       <x:c r="N7" s="466"/>
       <x:c r="O7" s="466"/>
-      <x:c r="P7" s="467"/>
+      <x:c r="P7" s="466"/>
       <x:c r="Q7" s="467"/>
-      <x:c r="R7" s="466"/>
-      <x:c r="S7" s="466"/>
+      <x:c r="R7" s="467"/>
+      <x:c r="S7" s="522"/>
       <x:c r="T7" s="466"/>
-      <x:c r="U7" s="467"/>
-      <x:c r="V7" s="467"/>
-      <x:c r="W7" s="466"/>
-      <x:c r="X7" s="468"/>
-      <x:c r="Y7" s="469"/>
-      <x:c r="Z7" s="329"/>
-      <x:c r="AA7" s="328"/>
-      <x:c r="AB7"/>
-      <x:c r="AC7"/>
-      <x:c r="AD7"/>
+      <x:c r="U7" s="466"/>
+      <x:c r="V7" s="466"/>
+      <x:c r="W7" s="467"/>
+      <x:c r="X7" s="467"/>
+      <x:c r="Y7" s="522"/>
+      <x:c r="Z7" s="527"/>
+      <x:c r="AA7" s="468"/>
+      <x:c r="AB7" s="469"/>
+      <x:c r="AC7" s="329"/>
+      <x:c r="AD7" s="328"/>
       <x:c r="AE7"/>
       <x:c r="AF7"/>
       <x:c r="AG7"/>
@@ -4780,6 +5660,9 @@
       <x:c r="AJ7"/>
       <x:c r="AK7"/>
       <x:c r="AL7"/>
+      <x:c r="AM7"/>
+      <x:c r="AN7"/>
+      <x:c r="AO7"/>
     </x:row>
     <x:row r="8" ht="88" hidden="0" customHeight="1">
       <x:c r="A8" s="471"/>
@@ -4788,30 +5671,30 @@
       <x:c r="D8" s="472"/>
       <x:c r="E8" s="472"/>
       <x:c r="F8" s="480"/>
-      <x:c r="G8" s="481"/>
+      <x:c r="G8" s="523"/>
       <x:c r="H8" s="482"/>
       <x:c r="I8" s="483"/>
       <x:c r="J8" s="483"/>
       <x:c r="K8" s="483"/>
       <x:c r="L8" s="483"/>
-      <x:c r="M8" s="482"/>
+      <x:c r="M8" s="524"/>
       <x:c r="N8" s="482"/>
       <x:c r="O8" s="482"/>
-      <x:c r="P8" s="483"/>
+      <x:c r="P8" s="482"/>
       <x:c r="Q8" s="483"/>
-      <x:c r="R8" s="482"/>
-      <x:c r="S8" s="482"/>
-      <x:c r="T8" s="483"/>
-      <x:c r="U8" s="483"/>
+      <x:c r="R8" s="483"/>
+      <x:c r="S8" s="524"/>
+      <x:c r="T8" s="482"/>
+      <x:c r="U8" s="482"/>
       <x:c r="V8" s="483"/>
-      <x:c r="W8" s="484"/>
-      <x:c r="X8" s="485"/>
-      <x:c r="Y8" s="486"/>
-      <x:c r="Z8" s="409"/>
-      <x:c r="AA8" s="487"/>
-      <x:c r="AB8"/>
-      <x:c r="AC8"/>
-      <x:c r="AD8"/>
+      <x:c r="W8" s="483"/>
+      <x:c r="X8" s="483"/>
+      <x:c r="Y8" s="524"/>
+      <x:c r="Z8" s="528"/>
+      <x:c r="AA8" s="485"/>
+      <x:c r="AB8" s="486"/>
+      <x:c r="AC8" s="409"/>
+      <x:c r="AD8" s="487"/>
       <x:c r="AE8"/>
       <x:c r="AF8"/>
       <x:c r="AG8"/>
@@ -4820,6 +5703,9 @@
       <x:c r="AJ8"/>
       <x:c r="AK8"/>
       <x:c r="AL8"/>
+      <x:c r="AM8"/>
+      <x:c r="AN8"/>
+      <x:c r="AO8"/>
     </x:row>
     <x:row r="9" ht="88" hidden="0" customHeight="1">
       <x:c r="A9" s="456"/>
@@ -4828,30 +5714,30 @@
       <x:c r="D9" s="457"/>
       <x:c r="E9" s="457"/>
       <x:c r="F9" s="464"/>
-      <x:c r="G9" s="465"/>
+      <x:c r="G9" s="521"/>
       <x:c r="H9" s="489"/>
       <x:c r="I9" s="489"/>
       <x:c r="J9" s="489"/>
       <x:c r="K9" s="467"/>
       <x:c r="L9" s="467"/>
-      <x:c r="M9" s="466"/>
+      <x:c r="M9" s="522"/>
       <x:c r="N9" s="466"/>
       <x:c r="O9" s="466"/>
-      <x:c r="P9" s="467"/>
+      <x:c r="P9" s="466"/>
       <x:c r="Q9" s="467"/>
-      <x:c r="R9" s="466"/>
-      <x:c r="S9" s="466"/>
+      <x:c r="R9" s="467"/>
+      <x:c r="S9" s="522"/>
       <x:c r="T9" s="466"/>
-      <x:c r="U9" s="467"/>
-      <x:c r="V9" s="467"/>
-      <x:c r="W9" s="466"/>
-      <x:c r="X9" s="468"/>
-      <x:c r="Y9" s="469"/>
-      <x:c r="Z9" s="329"/>
-      <x:c r="AA9" s="328"/>
-      <x:c r="AB9"/>
-      <x:c r="AC9"/>
-      <x:c r="AD9"/>
+      <x:c r="U9" s="466"/>
+      <x:c r="V9" s="466"/>
+      <x:c r="W9" s="467"/>
+      <x:c r="X9" s="467"/>
+      <x:c r="Y9" s="522"/>
+      <x:c r="Z9" s="527"/>
+      <x:c r="AA9" s="468"/>
+      <x:c r="AB9" s="469"/>
+      <x:c r="AC9" s="329"/>
+      <x:c r="AD9" s="328"/>
       <x:c r="AE9"/>
       <x:c r="AF9"/>
       <x:c r="AG9"/>
@@ -4860,6 +5746,9 @@
       <x:c r="AJ9"/>
       <x:c r="AK9"/>
       <x:c r="AL9"/>
+      <x:c r="AM9"/>
+      <x:c r="AN9"/>
+      <x:c r="AO9"/>
     </x:row>
     <x:row r="10" ht="88" hidden="0" customHeight="1">
       <x:c r="A10" s="471"/>
@@ -4868,30 +5757,30 @@
       <x:c r="D10" s="472"/>
       <x:c r="E10" s="472"/>
       <x:c r="F10" s="480"/>
-      <x:c r="G10" s="481"/>
+      <x:c r="G10" s="523"/>
       <x:c r="H10" s="482"/>
       <x:c r="I10" s="483"/>
       <x:c r="J10" s="483"/>
       <x:c r="K10" s="483"/>
       <x:c r="L10" s="483"/>
-      <x:c r="M10" s="482"/>
+      <x:c r="M10" s="524"/>
       <x:c r="N10" s="482"/>
       <x:c r="O10" s="482"/>
-      <x:c r="P10" s="483"/>
+      <x:c r="P10" s="482"/>
       <x:c r="Q10" s="483"/>
-      <x:c r="R10" s="482"/>
-      <x:c r="S10" s="482"/>
+      <x:c r="R10" s="483"/>
+      <x:c r="S10" s="524"/>
       <x:c r="T10" s="482"/>
-      <x:c r="U10" s="483"/>
-      <x:c r="V10" s="483"/>
-      <x:c r="W10" s="484"/>
-      <x:c r="X10" s="485"/>
-      <x:c r="Y10" s="486"/>
-      <x:c r="Z10" s="409"/>
-      <x:c r="AA10" s="487"/>
-      <x:c r="AB10"/>
-      <x:c r="AC10"/>
-      <x:c r="AD10"/>
+      <x:c r="U10" s="482"/>
+      <x:c r="V10" s="482"/>
+      <x:c r="W10" s="483"/>
+      <x:c r="X10" s="483"/>
+      <x:c r="Y10" s="524"/>
+      <x:c r="Z10" s="528"/>
+      <x:c r="AA10" s="485"/>
+      <x:c r="AB10" s="486"/>
+      <x:c r="AC10" s="409"/>
+      <x:c r="AD10" s="487"/>
       <x:c r="AE10"/>
       <x:c r="AF10"/>
       <x:c r="AG10"/>
@@ -4900,6 +5789,9 @@
       <x:c r="AJ10"/>
       <x:c r="AK10"/>
       <x:c r="AL10"/>
+      <x:c r="AM10"/>
+      <x:c r="AN10"/>
+      <x:c r="AO10"/>
     </x:row>
     <x:row r="11" ht="88" hidden="0" customHeight="1">
       <x:c r="A11" s="456"/>
@@ -4908,30 +5800,30 @@
       <x:c r="D11" s="457"/>
       <x:c r="E11" s="457"/>
       <x:c r="F11" s="464"/>
-      <x:c r="G11" s="465"/>
+      <x:c r="G11" s="521"/>
       <x:c r="H11" s="466"/>
       <x:c r="I11" s="466"/>
       <x:c r="J11" s="466"/>
       <x:c r="K11" s="466"/>
       <x:c r="L11" s="467"/>
-      <x:c r="M11" s="466"/>
+      <x:c r="M11" s="522"/>
       <x:c r="N11" s="466"/>
       <x:c r="O11" s="466"/>
-      <x:c r="P11" s="467"/>
+      <x:c r="P11" s="466"/>
       <x:c r="Q11" s="467"/>
-      <x:c r="R11" s="466"/>
-      <x:c r="S11" s="466"/>
+      <x:c r="R11" s="467"/>
+      <x:c r="S11" s="522"/>
       <x:c r="T11" s="466"/>
-      <x:c r="U11" s="467"/>
-      <x:c r="V11" s="467"/>
-      <x:c r="W11" s="466"/>
-      <x:c r="X11" s="468"/>
-      <x:c r="Y11" s="469"/>
-      <x:c r="Z11" s="329"/>
-      <x:c r="AA11" s="328"/>
-      <x:c r="AB11"/>
-      <x:c r="AC11"/>
-      <x:c r="AD11"/>
+      <x:c r="U11" s="466"/>
+      <x:c r="V11" s="466"/>
+      <x:c r="W11" s="467"/>
+      <x:c r="X11" s="467"/>
+      <x:c r="Y11" s="522"/>
+      <x:c r="Z11" s="527"/>
+      <x:c r="AA11" s="468"/>
+      <x:c r="AB11" s="469"/>
+      <x:c r="AC11" s="329"/>
+      <x:c r="AD11" s="328"/>
       <x:c r="AE11"/>
       <x:c r="AF11"/>
       <x:c r="AG11"/>
@@ -4940,6 +5832,9 @@
       <x:c r="AJ11"/>
       <x:c r="AK11"/>
       <x:c r="AL11"/>
+      <x:c r="AM11"/>
+      <x:c r="AN11"/>
+      <x:c r="AO11"/>
     </x:row>
     <x:row r="12" ht="88" hidden="0" customHeight="1">
       <x:c r="A12" s="471"/>
@@ -4948,30 +5843,30 @@
       <x:c r="D12" s="472"/>
       <x:c r="E12" s="472"/>
       <x:c r="F12" s="480"/>
-      <x:c r="G12" s="481"/>
+      <x:c r="G12" s="523"/>
       <x:c r="H12" s="482"/>
       <x:c r="I12" s="483"/>
       <x:c r="J12" s="483"/>
       <x:c r="K12" s="483"/>
       <x:c r="L12" s="483"/>
-      <x:c r="M12" s="482"/>
+      <x:c r="M12" s="524"/>
       <x:c r="N12" s="482"/>
       <x:c r="O12" s="482"/>
-      <x:c r="P12" s="483"/>
+      <x:c r="P12" s="482"/>
       <x:c r="Q12" s="483"/>
-      <x:c r="R12" s="482"/>
-      <x:c r="S12" s="482"/>
-      <x:c r="T12" s="483"/>
-      <x:c r="U12" s="483"/>
+      <x:c r="R12" s="483"/>
+      <x:c r="S12" s="524"/>
+      <x:c r="T12" s="482"/>
+      <x:c r="U12" s="482"/>
       <x:c r="V12" s="483"/>
-      <x:c r="W12" s="484"/>
-      <x:c r="X12" s="485"/>
-      <x:c r="Y12" s="486"/>
-      <x:c r="Z12" s="409"/>
-      <x:c r="AA12" s="487"/>
-      <x:c r="AB12"/>
-      <x:c r="AC12"/>
-      <x:c r="AD12"/>
+      <x:c r="W12" s="483"/>
+      <x:c r="X12" s="483"/>
+      <x:c r="Y12" s="524"/>
+      <x:c r="Z12" s="528"/>
+      <x:c r="AA12" s="485"/>
+      <x:c r="AB12" s="486"/>
+      <x:c r="AC12" s="409"/>
+      <x:c r="AD12" s="487"/>
       <x:c r="AE12"/>
       <x:c r="AF12"/>
       <x:c r="AG12"/>
@@ -4980,6 +5875,9 @@
       <x:c r="AJ12"/>
       <x:c r="AK12"/>
       <x:c r="AL12"/>
+      <x:c r="AM12"/>
+      <x:c r="AN12"/>
+      <x:c r="AO12"/>
     </x:row>
     <x:row r="13" ht="88" hidden="0" customHeight="1">
       <x:c r="A13" s="456"/>
@@ -4988,30 +5886,30 @@
       <x:c r="D13" s="457"/>
       <x:c r="E13" s="457"/>
       <x:c r="F13" s="464"/>
-      <x:c r="G13" s="465"/>
+      <x:c r="G13" s="521"/>
       <x:c r="H13" s="466"/>
       <x:c r="I13" s="466"/>
       <x:c r="J13" s="466"/>
       <x:c r="K13" s="467"/>
       <x:c r="L13" s="467"/>
-      <x:c r="M13" s="466"/>
+      <x:c r="M13" s="522"/>
       <x:c r="N13" s="466"/>
       <x:c r="O13" s="466"/>
-      <x:c r="P13" s="467"/>
+      <x:c r="P13" s="466"/>
       <x:c r="Q13" s="467"/>
-      <x:c r="R13" s="466"/>
-      <x:c r="S13" s="466"/>
+      <x:c r="R13" s="467"/>
+      <x:c r="S13" s="522"/>
       <x:c r="T13" s="466"/>
-      <x:c r="U13" s="467"/>
-      <x:c r="V13" s="467"/>
-      <x:c r="W13" s="466"/>
-      <x:c r="X13" s="468"/>
-      <x:c r="Y13" s="469"/>
-      <x:c r="Z13" s="329"/>
-      <x:c r="AA13" s="328"/>
-      <x:c r="AB13"/>
-      <x:c r="AC13"/>
-      <x:c r="AD13"/>
+      <x:c r="U13" s="466"/>
+      <x:c r="V13" s="466"/>
+      <x:c r="W13" s="467"/>
+      <x:c r="X13" s="467"/>
+      <x:c r="Y13" s="522"/>
+      <x:c r="Z13" s="527"/>
+      <x:c r="AA13" s="468"/>
+      <x:c r="AB13" s="469"/>
+      <x:c r="AC13" s="329"/>
+      <x:c r="AD13" s="328"/>
       <x:c r="AE13"/>
       <x:c r="AF13"/>
       <x:c r="AG13"/>
@@ -5020,6 +5918,9 @@
       <x:c r="AJ13"/>
       <x:c r="AK13"/>
       <x:c r="AL13"/>
+      <x:c r="AM13"/>
+      <x:c r="AN13"/>
+      <x:c r="AO13"/>
     </x:row>
     <x:row r="14" ht="88" hidden="0" customHeight="1">
       <x:c r="A14" s="471"/>
@@ -5028,30 +5929,30 @@
       <x:c r="D14" s="472"/>
       <x:c r="E14" s="472"/>
       <x:c r="F14" s="480"/>
-      <x:c r="G14" s="481"/>
+      <x:c r="G14" s="523"/>
       <x:c r="H14" s="482"/>
       <x:c r="I14" s="483"/>
       <x:c r="J14" s="483"/>
       <x:c r="K14" s="483"/>
       <x:c r="L14" s="483"/>
-      <x:c r="M14" s="482"/>
+      <x:c r="M14" s="524"/>
       <x:c r="N14" s="482"/>
       <x:c r="O14" s="482"/>
-      <x:c r="P14" s="483"/>
+      <x:c r="P14" s="482"/>
       <x:c r="Q14" s="483"/>
-      <x:c r="R14" s="482"/>
-      <x:c r="S14" s="482"/>
+      <x:c r="R14" s="483"/>
+      <x:c r="S14" s="524"/>
       <x:c r="T14" s="482"/>
-      <x:c r="U14" s="483"/>
-      <x:c r="V14" s="483"/>
-      <x:c r="W14" s="484"/>
-      <x:c r="X14" s="485"/>
-      <x:c r="Y14" s="486"/>
-      <x:c r="Z14" s="409"/>
-      <x:c r="AA14" s="487"/>
-      <x:c r="AB14"/>
-      <x:c r="AC14"/>
-      <x:c r="AD14"/>
+      <x:c r="U14" s="482"/>
+      <x:c r="V14" s="482"/>
+      <x:c r="W14" s="483"/>
+      <x:c r="X14" s="483"/>
+      <x:c r="Y14" s="524"/>
+      <x:c r="Z14" s="528"/>
+      <x:c r="AA14" s="485"/>
+      <x:c r="AB14" s="486"/>
+      <x:c r="AC14" s="409"/>
+      <x:c r="AD14" s="487"/>
       <x:c r="AE14"/>
       <x:c r="AF14"/>
       <x:c r="AG14"/>
@@ -5060,6 +5961,9 @@
       <x:c r="AJ14"/>
       <x:c r="AK14"/>
       <x:c r="AL14"/>
+      <x:c r="AM14"/>
+      <x:c r="AN14"/>
+      <x:c r="AO14"/>
     </x:row>
     <x:row r="15" ht="88" hidden="0" customHeight="1">
       <x:c r="A15" s="456"/>
@@ -5068,30 +5972,30 @@
       <x:c r="D15" s="457"/>
       <x:c r="E15" s="457"/>
       <x:c r="F15" s="464"/>
-      <x:c r="G15" s="465"/>
+      <x:c r="G15" s="521"/>
       <x:c r="H15" s="466"/>
       <x:c r="I15" s="467"/>
       <x:c r="J15" s="467"/>
       <x:c r="K15" s="467"/>
       <x:c r="L15" s="467"/>
-      <x:c r="M15" s="466"/>
-      <x:c r="N15" s="467"/>
+      <x:c r="M15" s="522"/>
+      <x:c r="N15" s="466"/>
       <x:c r="O15" s="467"/>
       <x:c r="P15" s="467"/>
       <x:c r="Q15" s="467"/>
-      <x:c r="R15" s="466"/>
-      <x:c r="S15" s="467"/>
-      <x:c r="T15" s="467"/>
+      <x:c r="R15" s="467"/>
+      <x:c r="S15" s="522"/>
+      <x:c r="T15" s="466"/>
       <x:c r="U15" s="467"/>
       <x:c r="V15" s="467"/>
-      <x:c r="W15" s="466"/>
-      <x:c r="X15" s="468"/>
-      <x:c r="Y15" s="469"/>
-      <x:c r="Z15" s="329"/>
-      <x:c r="AA15" s="328"/>
-      <x:c r="AB15"/>
-      <x:c r="AC15"/>
-      <x:c r="AD15"/>
+      <x:c r="W15" s="467"/>
+      <x:c r="X15" s="467"/>
+      <x:c r="Y15" s="522"/>
+      <x:c r="Z15" s="527"/>
+      <x:c r="AA15" s="468"/>
+      <x:c r="AB15" s="469"/>
+      <x:c r="AC15" s="329"/>
+      <x:c r="AD15" s="328"/>
       <x:c r="AE15"/>
       <x:c r="AF15"/>
       <x:c r="AG15"/>
@@ -5100,6 +6004,9 @@
       <x:c r="AJ15"/>
       <x:c r="AK15"/>
       <x:c r="AL15"/>
+      <x:c r="AM15"/>
+      <x:c r="AN15"/>
+      <x:c r="AO15"/>
     </x:row>
     <x:row r="16" ht="88" hidden="0" customHeight="1">
       <x:c r="A16" s="471"/>
@@ -5108,30 +6015,30 @@
       <x:c r="D16" s="472"/>
       <x:c r="E16" s="472"/>
       <x:c r="F16" s="480"/>
-      <x:c r="G16" s="481"/>
+      <x:c r="G16" s="523"/>
       <x:c r="H16" s="482"/>
       <x:c r="I16" s="483"/>
       <x:c r="J16" s="483"/>
       <x:c r="K16" s="483"/>
       <x:c r="L16" s="483"/>
-      <x:c r="M16" s="482"/>
+      <x:c r="M16" s="524"/>
       <x:c r="N16" s="482"/>
-      <x:c r="O16" s="483"/>
+      <x:c r="O16" s="482"/>
       <x:c r="P16" s="483"/>
       <x:c r="Q16" s="483"/>
-      <x:c r="R16" s="482"/>
-      <x:c r="S16" s="483"/>
-      <x:c r="T16" s="483"/>
+      <x:c r="R16" s="483"/>
+      <x:c r="S16" s="524"/>
+      <x:c r="T16" s="482"/>
       <x:c r="U16" s="483"/>
       <x:c r="V16" s="483"/>
-      <x:c r="W16" s="484"/>
-      <x:c r="X16" s="485"/>
-      <x:c r="Y16" s="486"/>
-      <x:c r="Z16" s="409"/>
-      <x:c r="AA16" s="487"/>
-      <x:c r="AB16"/>
-      <x:c r="AC16"/>
-      <x:c r="AD16"/>
+      <x:c r="W16" s="483"/>
+      <x:c r="X16" s="483"/>
+      <x:c r="Y16" s="524"/>
+      <x:c r="Z16" s="528"/>
+      <x:c r="AA16" s="485"/>
+      <x:c r="AB16" s="486"/>
+      <x:c r="AC16" s="409"/>
+      <x:c r="AD16" s="487"/>
       <x:c r="AE16"/>
       <x:c r="AF16"/>
       <x:c r="AG16"/>
@@ -5140,6 +6047,9 @@
       <x:c r="AJ16"/>
       <x:c r="AK16"/>
       <x:c r="AL16"/>
+      <x:c r="AM16"/>
+      <x:c r="AN16"/>
+      <x:c r="AO16"/>
     </x:row>
     <x:row r="17" ht="88" hidden="0" customHeight="1">
       <x:c r="A17" s="456"/>
@@ -5148,30 +6058,30 @@
       <x:c r="D17" s="457"/>
       <x:c r="E17" s="457"/>
       <x:c r="F17" s="464"/>
-      <x:c r="G17" s="465"/>
+      <x:c r="G17" s="521"/>
       <x:c r="H17" s="489"/>
       <x:c r="I17" s="467"/>
       <x:c r="J17" s="467"/>
       <x:c r="K17" s="467"/>
       <x:c r="L17" s="467"/>
-      <x:c r="M17" s="489"/>
-      <x:c r="N17" s="467"/>
+      <x:c r="M17" s="522"/>
+      <x:c r="N17" s="489"/>
       <x:c r="O17" s="467"/>
       <x:c r="P17" s="467"/>
       <x:c r="Q17" s="467"/>
-      <x:c r="R17" s="466"/>
-      <x:c r="S17" s="467"/>
-      <x:c r="T17" s="467"/>
+      <x:c r="R17" s="467"/>
+      <x:c r="S17" s="522"/>
+      <x:c r="T17" s="466"/>
       <x:c r="U17" s="467"/>
       <x:c r="V17" s="467"/>
-      <x:c r="W17" s="466"/>
-      <x:c r="X17" s="468"/>
-      <x:c r="Y17" s="469"/>
-      <x:c r="Z17" s="329"/>
-      <x:c r="AA17" s="328"/>
-      <x:c r="AB17"/>
-      <x:c r="AC17"/>
-      <x:c r="AD17"/>
+      <x:c r="W17" s="467"/>
+      <x:c r="X17" s="467"/>
+      <x:c r="Y17" s="522"/>
+      <x:c r="Z17" s="527"/>
+      <x:c r="AA17" s="468"/>
+      <x:c r="AB17" s="469"/>
+      <x:c r="AC17" s="329"/>
+      <x:c r="AD17" s="328"/>
       <x:c r="AE17"/>
       <x:c r="AF17"/>
       <x:c r="AG17"/>
@@ -5180,6 +6090,9 @@
       <x:c r="AJ17"/>
       <x:c r="AK17"/>
       <x:c r="AL17"/>
+      <x:c r="AM17"/>
+      <x:c r="AN17"/>
+      <x:c r="AO17"/>
     </x:row>
     <x:row r="18" ht="88" hidden="0" customHeight="1">
       <x:c r="A18" s="471"/>
@@ -5188,30 +6101,30 @@
       <x:c r="D18" s="472"/>
       <x:c r="E18" s="472"/>
       <x:c r="F18" s="480"/>
-      <x:c r="G18" s="481"/>
+      <x:c r="G18" s="523"/>
       <x:c r="H18" s="482"/>
       <x:c r="I18" s="483"/>
       <x:c r="J18" s="483"/>
       <x:c r="K18" s="483"/>
       <x:c r="L18" s="483"/>
-      <x:c r="M18" s="482"/>
+      <x:c r="M18" s="524"/>
       <x:c r="N18" s="482"/>
-      <x:c r="O18" s="483"/>
+      <x:c r="O18" s="482"/>
       <x:c r="P18" s="483"/>
       <x:c r="Q18" s="483"/>
-      <x:c r="R18" s="482"/>
-      <x:c r="S18" s="483"/>
-      <x:c r="T18" s="483"/>
+      <x:c r="R18" s="483"/>
+      <x:c r="S18" s="524"/>
+      <x:c r="T18" s="482"/>
       <x:c r="U18" s="483"/>
       <x:c r="V18" s="483"/>
-      <x:c r="W18" s="484"/>
-      <x:c r="X18" s="485"/>
-      <x:c r="Y18" s="486"/>
-      <x:c r="Z18" s="409"/>
-      <x:c r="AA18" s="487"/>
-      <x:c r="AB18"/>
-      <x:c r="AC18"/>
-      <x:c r="AD18"/>
+      <x:c r="W18" s="483"/>
+      <x:c r="X18" s="483"/>
+      <x:c r="Y18" s="524"/>
+      <x:c r="Z18" s="528"/>
+      <x:c r="AA18" s="485"/>
+      <x:c r="AB18" s="486"/>
+      <x:c r="AC18" s="409"/>
+      <x:c r="AD18" s="487"/>
       <x:c r="AE18"/>
       <x:c r="AF18"/>
       <x:c r="AG18"/>
@@ -5220,6 +6133,9 @@
       <x:c r="AJ18"/>
       <x:c r="AK18"/>
       <x:c r="AL18"/>
+      <x:c r="AM18"/>
+      <x:c r="AN18"/>
+      <x:c r="AO18"/>
     </x:row>
     <x:row r="19" ht="88" hidden="0" customHeight="1">
       <x:c r="A19" s="456"/>
@@ -5228,30 +6144,30 @@
       <x:c r="D19" s="457"/>
       <x:c r="E19" s="457"/>
       <x:c r="F19" s="464"/>
-      <x:c r="G19" s="465"/>
+      <x:c r="G19" s="521"/>
       <x:c r="H19" s="466"/>
       <x:c r="I19" s="466"/>
       <x:c r="J19" s="466"/>
       <x:c r="K19" s="467"/>
       <x:c r="L19" s="467"/>
-      <x:c r="M19" s="466"/>
+      <x:c r="M19" s="522"/>
       <x:c r="N19" s="466"/>
       <x:c r="O19" s="466"/>
       <x:c r="P19" s="466"/>
-      <x:c r="Q19" s="467"/>
-      <x:c r="R19" s="466"/>
-      <x:c r="S19" s="466"/>
+      <x:c r="Q19" s="466"/>
+      <x:c r="R19" s="467"/>
+      <x:c r="S19" s="522"/>
       <x:c r="T19" s="466"/>
-      <x:c r="U19" s="467"/>
-      <x:c r="V19" s="467"/>
-      <x:c r="W19" s="466"/>
-      <x:c r="X19" s="468"/>
-      <x:c r="Y19" s="469"/>
-      <x:c r="Z19" s="329"/>
-      <x:c r="AA19" s="328"/>
-      <x:c r="AB19"/>
-      <x:c r="AC19"/>
-      <x:c r="AD19"/>
+      <x:c r="U19" s="466"/>
+      <x:c r="V19" s="466"/>
+      <x:c r="W19" s="467"/>
+      <x:c r="X19" s="467"/>
+      <x:c r="Y19" s="522"/>
+      <x:c r="Z19" s="527"/>
+      <x:c r="AA19" s="468"/>
+      <x:c r="AB19" s="469"/>
+      <x:c r="AC19" s="329"/>
+      <x:c r="AD19" s="328"/>
       <x:c r="AE19"/>
       <x:c r="AF19"/>
       <x:c r="AG19"/>
@@ -5260,6 +6176,9 @@
       <x:c r="AJ19"/>
       <x:c r="AK19"/>
       <x:c r="AL19"/>
+      <x:c r="AM19"/>
+      <x:c r="AN19"/>
+      <x:c r="AO19"/>
     </x:row>
     <x:row r="20" ht="88" hidden="0" customHeight="1">
       <x:c r="A20" s="471"/>
@@ -5268,30 +6187,30 @@
       <x:c r="D20" s="472"/>
       <x:c r="E20" s="472"/>
       <x:c r="F20" s="480"/>
-      <x:c r="G20" s="481"/>
+      <x:c r="G20" s="523"/>
       <x:c r="H20" s="482"/>
       <x:c r="I20" s="483"/>
       <x:c r="J20" s="483"/>
       <x:c r="K20" s="483"/>
       <x:c r="L20" s="483"/>
-      <x:c r="M20" s="482"/>
+      <x:c r="M20" s="524"/>
       <x:c r="N20" s="482"/>
       <x:c r="O20" s="482"/>
-      <x:c r="P20" s="483"/>
+      <x:c r="P20" s="482"/>
       <x:c r="Q20" s="483"/>
-      <x:c r="R20" s="482"/>
-      <x:c r="S20" s="482"/>
-      <x:c r="T20" s="483"/>
-      <x:c r="U20" s="483"/>
+      <x:c r="R20" s="483"/>
+      <x:c r="S20" s="524"/>
+      <x:c r="T20" s="482"/>
+      <x:c r="U20" s="482"/>
       <x:c r="V20" s="483"/>
-      <x:c r="W20" s="484"/>
-      <x:c r="X20" s="485"/>
-      <x:c r="Y20" s="486"/>
-      <x:c r="Z20" s="409"/>
-      <x:c r="AA20" s="487"/>
-      <x:c r="AB20"/>
-      <x:c r="AC20"/>
-      <x:c r="AD20"/>
+      <x:c r="W20" s="483"/>
+      <x:c r="X20" s="483"/>
+      <x:c r="Y20" s="524"/>
+      <x:c r="Z20" s="528"/>
+      <x:c r="AA20" s="485"/>
+      <x:c r="AB20" s="486"/>
+      <x:c r="AC20" s="409"/>
+      <x:c r="AD20" s="487"/>
       <x:c r="AE20"/>
       <x:c r="AF20"/>
       <x:c r="AG20"/>
@@ -5300,6 +6219,9 @@
       <x:c r="AJ20"/>
       <x:c r="AK20"/>
       <x:c r="AL20"/>
+      <x:c r="AM20"/>
+      <x:c r="AN20"/>
+      <x:c r="AO20"/>
     </x:row>
     <x:row r="21" ht="88" hidden="0" customHeight="1">
       <x:c r="A21" s="456"/>
@@ -5308,30 +6230,30 @@
       <x:c r="D21" s="457"/>
       <x:c r="E21" s="457"/>
       <x:c r="F21" s="464"/>
-      <x:c r="G21" s="465"/>
+      <x:c r="G21" s="521"/>
       <x:c r="H21" s="466"/>
       <x:c r="I21" s="466"/>
       <x:c r="J21" s="466"/>
       <x:c r="K21" s="467"/>
       <x:c r="L21" s="467"/>
-      <x:c r="M21" s="466"/>
+      <x:c r="M21" s="522"/>
       <x:c r="N21" s="466"/>
       <x:c r="O21" s="466"/>
-      <x:c r="P21" s="467"/>
+      <x:c r="P21" s="466"/>
       <x:c r="Q21" s="467"/>
-      <x:c r="R21" s="466"/>
-      <x:c r="S21" s="466"/>
+      <x:c r="R21" s="467"/>
+      <x:c r="S21" s="522"/>
       <x:c r="T21" s="466"/>
-      <x:c r="U21" s="467"/>
-      <x:c r="V21" s="467"/>
-      <x:c r="W21" s="466"/>
-      <x:c r="X21" s="468"/>
-      <x:c r="Y21" s="469"/>
-      <x:c r="Z21" s="329"/>
-      <x:c r="AA21" s="328"/>
-      <x:c r="AB21"/>
-      <x:c r="AC21"/>
-      <x:c r="AD21"/>
+      <x:c r="U21" s="466"/>
+      <x:c r="V21" s="466"/>
+      <x:c r="W21" s="467"/>
+      <x:c r="X21" s="467"/>
+      <x:c r="Y21" s="522"/>
+      <x:c r="Z21" s="527"/>
+      <x:c r="AA21" s="468"/>
+      <x:c r="AB21" s="469"/>
+      <x:c r="AC21" s="329"/>
+      <x:c r="AD21" s="328"/>
       <x:c r="AE21"/>
       <x:c r="AF21"/>
       <x:c r="AG21"/>
@@ -5340,6 +6262,9 @@
       <x:c r="AJ21"/>
       <x:c r="AK21"/>
       <x:c r="AL21"/>
+      <x:c r="AM21"/>
+      <x:c r="AN21"/>
+      <x:c r="AO21"/>
     </x:row>
     <x:row r="22" ht="88" hidden="0" customHeight="1">
       <x:c r="A22" s="471"/>
@@ -5348,30 +6273,30 @@
       <x:c r="D22" s="472"/>
       <x:c r="E22" s="472"/>
       <x:c r="F22" s="480"/>
-      <x:c r="G22" s="481"/>
+      <x:c r="G22" s="523"/>
       <x:c r="H22" s="482"/>
       <x:c r="I22" s="483"/>
       <x:c r="J22" s="483"/>
       <x:c r="K22" s="483"/>
       <x:c r="L22" s="483"/>
-      <x:c r="M22" s="482"/>
+      <x:c r="M22" s="524"/>
       <x:c r="N22" s="482"/>
       <x:c r="O22" s="482"/>
-      <x:c r="P22" s="483"/>
+      <x:c r="P22" s="482"/>
       <x:c r="Q22" s="483"/>
-      <x:c r="R22" s="482"/>
-      <x:c r="S22" s="482"/>
+      <x:c r="R22" s="483"/>
+      <x:c r="S22" s="524"/>
       <x:c r="T22" s="482"/>
-      <x:c r="U22" s="483"/>
-      <x:c r="V22" s="483"/>
-      <x:c r="W22" s="484"/>
-      <x:c r="X22" s="485"/>
-      <x:c r="Y22" s="486"/>
-      <x:c r="Z22" s="409"/>
-      <x:c r="AA22" s="487"/>
-      <x:c r="AB22"/>
-      <x:c r="AC22"/>
-      <x:c r="AD22"/>
+      <x:c r="U22" s="482"/>
+      <x:c r="V22" s="482"/>
+      <x:c r="W22" s="483"/>
+      <x:c r="X22" s="483"/>
+      <x:c r="Y22" s="524"/>
+      <x:c r="Z22" s="528"/>
+      <x:c r="AA22" s="485"/>
+      <x:c r="AB22" s="486"/>
+      <x:c r="AC22" s="409"/>
+      <x:c r="AD22" s="487"/>
       <x:c r="AE22"/>
       <x:c r="AF22"/>
       <x:c r="AG22"/>
@@ -5380,6 +6305,9 @@
       <x:c r="AJ22"/>
       <x:c r="AK22"/>
       <x:c r="AL22"/>
+      <x:c r="AM22"/>
+      <x:c r="AN22"/>
+      <x:c r="AO22"/>
     </x:row>
     <x:row r="23" ht="88" hidden="0" customHeight="1">
       <x:c r="A23" s="456"/>
@@ -5388,30 +6316,30 @@
       <x:c r="D23" s="457"/>
       <x:c r="E23" s="457"/>
       <x:c r="F23" s="464"/>
-      <x:c r="G23" s="465"/>
+      <x:c r="G23" s="521"/>
       <x:c r="H23" s="466"/>
       <x:c r="I23" s="466"/>
       <x:c r="J23" s="466"/>
       <x:c r="K23" s="467"/>
       <x:c r="L23" s="467"/>
-      <x:c r="M23" s="466"/>
+      <x:c r="M23" s="522"/>
       <x:c r="N23" s="466"/>
       <x:c r="O23" s="466"/>
-      <x:c r="P23" s="467"/>
+      <x:c r="P23" s="466"/>
       <x:c r="Q23" s="467"/>
-      <x:c r="R23" s="466"/>
-      <x:c r="S23" s="466"/>
+      <x:c r="R23" s="467"/>
+      <x:c r="S23" s="522"/>
       <x:c r="T23" s="466"/>
-      <x:c r="U23" s="467"/>
-      <x:c r="V23" s="467"/>
-      <x:c r="W23" s="466"/>
-      <x:c r="X23" s="468"/>
-      <x:c r="Y23" s="469"/>
-      <x:c r="Z23" s="329"/>
-      <x:c r="AA23" s="328"/>
-      <x:c r="AB23"/>
-      <x:c r="AC23"/>
-      <x:c r="AD23"/>
+      <x:c r="U23" s="466"/>
+      <x:c r="V23" s="466"/>
+      <x:c r="W23" s="467"/>
+      <x:c r="X23" s="467"/>
+      <x:c r="Y23" s="522"/>
+      <x:c r="Z23" s="527"/>
+      <x:c r="AA23" s="468"/>
+      <x:c r="AB23" s="469"/>
+      <x:c r="AC23" s="329"/>
+      <x:c r="AD23" s="328"/>
       <x:c r="AE23"/>
       <x:c r="AF23"/>
       <x:c r="AG23"/>
@@ -5420,6 +6348,9 @@
       <x:c r="AJ23"/>
       <x:c r="AK23"/>
       <x:c r="AL23"/>
+      <x:c r="AM23"/>
+      <x:c r="AN23"/>
+      <x:c r="AO23"/>
     </x:row>
     <x:row r="24" ht="88" hidden="0" customHeight="1">
       <x:c r="A24" s="471"/>
@@ -5428,30 +6359,30 @@
       <x:c r="D24" s="472"/>
       <x:c r="E24" s="472"/>
       <x:c r="F24" s="480"/>
-      <x:c r="G24" s="481"/>
+      <x:c r="G24" s="523"/>
       <x:c r="H24" s="482"/>
       <x:c r="I24" s="483"/>
       <x:c r="J24" s="483"/>
       <x:c r="K24" s="483"/>
       <x:c r="L24" s="483"/>
-      <x:c r="M24" s="482"/>
+      <x:c r="M24" s="524"/>
       <x:c r="N24" s="482"/>
       <x:c r="O24" s="482"/>
-      <x:c r="P24" s="483"/>
+      <x:c r="P24" s="482"/>
       <x:c r="Q24" s="483"/>
-      <x:c r="R24" s="482"/>
-      <x:c r="S24" s="482"/>
-      <x:c r="T24" s="483"/>
-      <x:c r="U24" s="483"/>
+      <x:c r="R24" s="483"/>
+      <x:c r="S24" s="524"/>
+      <x:c r="T24" s="482"/>
+      <x:c r="U24" s="482"/>
       <x:c r="V24" s="483"/>
-      <x:c r="W24" s="484"/>
-      <x:c r="X24" s="485"/>
-      <x:c r="Y24" s="486"/>
-      <x:c r="Z24" s="409"/>
-      <x:c r="AA24" s="487"/>
-      <x:c r="AB24"/>
-      <x:c r="AC24"/>
-      <x:c r="AD24"/>
+      <x:c r="W24" s="483"/>
+      <x:c r="X24" s="483"/>
+      <x:c r="Y24" s="524"/>
+      <x:c r="Z24" s="528"/>
+      <x:c r="AA24" s="485"/>
+      <x:c r="AB24" s="486"/>
+      <x:c r="AC24" s="409"/>
+      <x:c r="AD24" s="487"/>
       <x:c r="AE24"/>
       <x:c r="AF24"/>
       <x:c r="AG24"/>
@@ -5460,6 +6391,9 @@
       <x:c r="AJ24"/>
       <x:c r="AK24"/>
       <x:c r="AL24"/>
+      <x:c r="AM24"/>
+      <x:c r="AN24"/>
+      <x:c r="AO24"/>
     </x:row>
     <x:row r="25" ht="88" hidden="0" customHeight="1">
       <x:c r="A25" s="456"/>
@@ -5468,30 +6402,30 @@
       <x:c r="D25" s="457"/>
       <x:c r="E25" s="457"/>
       <x:c r="F25" s="464"/>
-      <x:c r="G25" s="465"/>
+      <x:c r="G25" s="521"/>
       <x:c r="H25" s="466"/>
       <x:c r="I25" s="466"/>
       <x:c r="J25" s="466"/>
       <x:c r="K25" s="467"/>
       <x:c r="L25" s="467"/>
-      <x:c r="M25" s="466"/>
+      <x:c r="M25" s="522"/>
       <x:c r="N25" s="466"/>
       <x:c r="O25" s="466"/>
-      <x:c r="P25" s="467"/>
+      <x:c r="P25" s="466"/>
       <x:c r="Q25" s="467"/>
-      <x:c r="R25" s="466"/>
-      <x:c r="S25" s="466"/>
+      <x:c r="R25" s="467"/>
+      <x:c r="S25" s="522"/>
       <x:c r="T25" s="466"/>
-      <x:c r="U25" s="467"/>
-      <x:c r="V25" s="467"/>
-      <x:c r="W25" s="466"/>
-      <x:c r="X25" s="468"/>
-      <x:c r="Y25" s="469"/>
-      <x:c r="Z25" s="329"/>
-      <x:c r="AA25" s="328"/>
-      <x:c r="AB25"/>
-      <x:c r="AC25"/>
-      <x:c r="AD25"/>
+      <x:c r="U25" s="466"/>
+      <x:c r="V25" s="466"/>
+      <x:c r="W25" s="467"/>
+      <x:c r="X25" s="467"/>
+      <x:c r="Y25" s="522"/>
+      <x:c r="Z25" s="527"/>
+      <x:c r="AA25" s="468"/>
+      <x:c r="AB25" s="469"/>
+      <x:c r="AC25" s="329"/>
+      <x:c r="AD25" s="328"/>
       <x:c r="AE25"/>
       <x:c r="AF25"/>
       <x:c r="AG25"/>
@@ -5500,6 +6434,9 @@
       <x:c r="AJ25"/>
       <x:c r="AK25"/>
       <x:c r="AL25"/>
+      <x:c r="AM25"/>
+      <x:c r="AN25"/>
+      <x:c r="AO25"/>
     </x:row>
     <x:row r="26" ht="88" hidden="0" customHeight="1">
       <x:c r="A26" s="471"/>
@@ -5508,30 +6445,30 @@
       <x:c r="D26" s="472"/>
       <x:c r="E26" s="472"/>
       <x:c r="F26" s="480"/>
-      <x:c r="G26" s="481"/>
+      <x:c r="G26" s="523"/>
       <x:c r="H26" s="482"/>
       <x:c r="I26" s="483"/>
       <x:c r="J26" s="483"/>
       <x:c r="K26" s="483"/>
       <x:c r="L26" s="483"/>
-      <x:c r="M26" s="482"/>
+      <x:c r="M26" s="524"/>
       <x:c r="N26" s="482"/>
       <x:c r="O26" s="482"/>
-      <x:c r="P26" s="483"/>
+      <x:c r="P26" s="482"/>
       <x:c r="Q26" s="483"/>
-      <x:c r="R26" s="482"/>
-      <x:c r="S26" s="482"/>
+      <x:c r="R26" s="483"/>
+      <x:c r="S26" s="524"/>
       <x:c r="T26" s="482"/>
-      <x:c r="U26" s="483"/>
-      <x:c r="V26" s="483"/>
-      <x:c r="W26" s="484"/>
-      <x:c r="X26" s="485"/>
-      <x:c r="Y26" s="486"/>
-      <x:c r="Z26" s="409"/>
-      <x:c r="AA26" s="487"/>
-      <x:c r="AB26"/>
-      <x:c r="AC26"/>
-      <x:c r="AD26"/>
+      <x:c r="U26" s="482"/>
+      <x:c r="V26" s="482"/>
+      <x:c r="W26" s="483"/>
+      <x:c r="X26" s="483"/>
+      <x:c r="Y26" s="524"/>
+      <x:c r="Z26" s="528"/>
+      <x:c r="AA26" s="485"/>
+      <x:c r="AB26" s="486"/>
+      <x:c r="AC26" s="409"/>
+      <x:c r="AD26" s="487"/>
       <x:c r="AE26"/>
       <x:c r="AF26"/>
       <x:c r="AG26"/>
@@ -5540,6 +6477,9 @@
       <x:c r="AJ26"/>
       <x:c r="AK26"/>
       <x:c r="AL26"/>
+      <x:c r="AM26"/>
+      <x:c r="AN26"/>
+      <x:c r="AO26"/>
     </x:row>
     <x:row r="27" ht="88" hidden="0" customHeight="1">
       <x:c r="A27" s="456"/>
@@ -5548,30 +6488,30 @@
       <x:c r="D27" s="457"/>
       <x:c r="E27" s="457"/>
       <x:c r="F27" s="464"/>
-      <x:c r="G27" s="465"/>
+      <x:c r="G27" s="521"/>
       <x:c r="H27" s="466"/>
       <x:c r="I27" s="466"/>
       <x:c r="J27" s="466"/>
       <x:c r="K27" s="466"/>
       <x:c r="L27" s="467"/>
-      <x:c r="M27" s="466"/>
+      <x:c r="M27" s="522"/>
       <x:c r="N27" s="466"/>
       <x:c r="O27" s="466"/>
-      <x:c r="P27" s="467"/>
+      <x:c r="P27" s="466"/>
       <x:c r="Q27" s="467"/>
-      <x:c r="R27" s="466"/>
-      <x:c r="S27" s="466"/>
+      <x:c r="R27" s="467"/>
+      <x:c r="S27" s="522"/>
       <x:c r="T27" s="466"/>
-      <x:c r="U27" s="467"/>
-      <x:c r="V27" s="467"/>
-      <x:c r="W27" s="466"/>
-      <x:c r="X27" s="468"/>
-      <x:c r="Y27" s="469"/>
-      <x:c r="Z27" s="329"/>
-      <x:c r="AA27" s="328"/>
-      <x:c r="AB27"/>
-      <x:c r="AC27"/>
-      <x:c r="AD27"/>
+      <x:c r="U27" s="466"/>
+      <x:c r="V27" s="466"/>
+      <x:c r="W27" s="467"/>
+      <x:c r="X27" s="467"/>
+      <x:c r="Y27" s="522"/>
+      <x:c r="Z27" s="527"/>
+      <x:c r="AA27" s="468"/>
+      <x:c r="AB27" s="469"/>
+      <x:c r="AC27" s="329"/>
+      <x:c r="AD27" s="328"/>
       <x:c r="AE27"/>
       <x:c r="AF27"/>
       <x:c r="AG27"/>
@@ -5580,6 +6520,9 @@
       <x:c r="AJ27"/>
       <x:c r="AK27"/>
       <x:c r="AL27"/>
+      <x:c r="AM27"/>
+      <x:c r="AN27"/>
+      <x:c r="AO27"/>
     </x:row>
     <x:row r="28" ht="88" hidden="0" customHeight="1">
       <x:c r="A28" s="471"/>
@@ -5588,30 +6531,30 @@
       <x:c r="D28" s="472"/>
       <x:c r="E28" s="472"/>
       <x:c r="F28" s="480"/>
-      <x:c r="G28" s="481"/>
+      <x:c r="G28" s="523"/>
       <x:c r="H28" s="482"/>
       <x:c r="I28" s="483"/>
       <x:c r="J28" s="483"/>
       <x:c r="K28" s="483"/>
       <x:c r="L28" s="483"/>
-      <x:c r="M28" s="482"/>
+      <x:c r="M28" s="524"/>
       <x:c r="N28" s="482"/>
       <x:c r="O28" s="482"/>
-      <x:c r="P28" s="483"/>
+      <x:c r="P28" s="482"/>
       <x:c r="Q28" s="483"/>
-      <x:c r="R28" s="482"/>
-      <x:c r="S28" s="482"/>
-      <x:c r="T28" s="483"/>
-      <x:c r="U28" s="483"/>
+      <x:c r="R28" s="483"/>
+      <x:c r="S28" s="524"/>
+      <x:c r="T28" s="482"/>
+      <x:c r="U28" s="482"/>
       <x:c r="V28" s="483"/>
-      <x:c r="W28" s="484"/>
-      <x:c r="X28" s="485"/>
-      <x:c r="Y28" s="486"/>
-      <x:c r="Z28" s="409"/>
-      <x:c r="AA28" s="487"/>
-      <x:c r="AB28"/>
-      <x:c r="AC28"/>
-      <x:c r="AD28"/>
+      <x:c r="W28" s="483"/>
+      <x:c r="X28" s="483"/>
+      <x:c r="Y28" s="524"/>
+      <x:c r="Z28" s="528"/>
+      <x:c r="AA28" s="485"/>
+      <x:c r="AB28" s="486"/>
+      <x:c r="AC28" s="409"/>
+      <x:c r="AD28" s="487"/>
       <x:c r="AE28"/>
       <x:c r="AF28"/>
       <x:c r="AG28"/>
@@ -5620,6 +6563,9 @@
       <x:c r="AJ28"/>
       <x:c r="AK28"/>
       <x:c r="AL28"/>
+      <x:c r="AM28"/>
+      <x:c r="AN28"/>
+      <x:c r="AO28"/>
     </x:row>
     <x:row r="29" ht="88" hidden="0" customHeight="1">
       <x:c r="A29" s="456"/>
@@ -5628,30 +6574,30 @@
       <x:c r="D29" s="457"/>
       <x:c r="E29" s="457"/>
       <x:c r="F29" s="464"/>
-      <x:c r="G29" s="465"/>
+      <x:c r="G29" s="521"/>
       <x:c r="H29" s="466"/>
       <x:c r="I29" s="466"/>
       <x:c r="J29" s="466"/>
       <x:c r="K29" s="467"/>
       <x:c r="L29" s="467"/>
-      <x:c r="M29" s="489"/>
+      <x:c r="M29" s="522"/>
       <x:c r="N29" s="489"/>
-      <x:c r="O29" s="467"/>
+      <x:c r="O29" s="489"/>
       <x:c r="P29" s="467"/>
       <x:c r="Q29" s="467"/>
-      <x:c r="R29" s="466"/>
-      <x:c r="S29" s="466"/>
+      <x:c r="R29" s="467"/>
+      <x:c r="S29" s="522"/>
       <x:c r="T29" s="466"/>
-      <x:c r="U29" s="467"/>
-      <x:c r="V29" s="467"/>
-      <x:c r="W29" s="466"/>
-      <x:c r="X29" s="468"/>
-      <x:c r="Y29" s="469"/>
-      <x:c r="Z29" s="329"/>
-      <x:c r="AA29" s="328"/>
-      <x:c r="AB29"/>
-      <x:c r="AC29"/>
-      <x:c r="AD29"/>
+      <x:c r="U29" s="466"/>
+      <x:c r="V29" s="466"/>
+      <x:c r="W29" s="467"/>
+      <x:c r="X29" s="467"/>
+      <x:c r="Y29" s="522"/>
+      <x:c r="Z29" s="527"/>
+      <x:c r="AA29" s="468"/>
+      <x:c r="AB29" s="469"/>
+      <x:c r="AC29" s="329"/>
+      <x:c r="AD29" s="328"/>
       <x:c r="AE29"/>
       <x:c r="AF29"/>
       <x:c r="AG29"/>
@@ -5660,6 +6606,9 @@
       <x:c r="AJ29"/>
       <x:c r="AK29"/>
       <x:c r="AL29"/>
+      <x:c r="AM29"/>
+      <x:c r="AN29"/>
+      <x:c r="AO29"/>
     </x:row>
     <x:row r="30" ht="88" hidden="0" customHeight="1">
       <x:c r="A30" s="471"/>
@@ -5668,30 +6617,30 @@
       <x:c r="D30" s="472"/>
       <x:c r="E30" s="472"/>
       <x:c r="F30" s="480"/>
-      <x:c r="G30" s="481"/>
+      <x:c r="G30" s="523"/>
       <x:c r="H30" s="482"/>
       <x:c r="I30" s="483"/>
       <x:c r="J30" s="483"/>
       <x:c r="K30" s="483"/>
       <x:c r="L30" s="483"/>
-      <x:c r="M30" s="482"/>
+      <x:c r="M30" s="524"/>
       <x:c r="N30" s="482"/>
       <x:c r="O30" s="482"/>
-      <x:c r="P30" s="483"/>
+      <x:c r="P30" s="482"/>
       <x:c r="Q30" s="483"/>
-      <x:c r="R30" s="482"/>
-      <x:c r="S30" s="482"/>
+      <x:c r="R30" s="483"/>
+      <x:c r="S30" s="524"/>
       <x:c r="T30" s="482"/>
-      <x:c r="U30" s="483"/>
-      <x:c r="V30" s="483"/>
-      <x:c r="W30" s="484"/>
-      <x:c r="X30" s="485"/>
-      <x:c r="Y30" s="486"/>
-      <x:c r="Z30" s="409"/>
-      <x:c r="AA30" s="487"/>
-      <x:c r="AB30"/>
-      <x:c r="AC30"/>
-      <x:c r="AD30"/>
+      <x:c r="U30" s="482"/>
+      <x:c r="V30" s="482"/>
+      <x:c r="W30" s="483"/>
+      <x:c r="X30" s="483"/>
+      <x:c r="Y30" s="524"/>
+      <x:c r="Z30" s="528"/>
+      <x:c r="AA30" s="485"/>
+      <x:c r="AB30" s="486"/>
+      <x:c r="AC30" s="409"/>
+      <x:c r="AD30" s="487"/>
       <x:c r="AE30"/>
       <x:c r="AF30"/>
       <x:c r="AG30"/>
@@ -5700,6 +6649,9 @@
       <x:c r="AJ30"/>
       <x:c r="AK30"/>
       <x:c r="AL30"/>
+      <x:c r="AM30"/>
+      <x:c r="AN30"/>
+      <x:c r="AO30"/>
     </x:row>
     <x:row r="31" ht="88" hidden="0" customHeight="1">
       <x:c r="A31" s="456"/>
@@ -5708,30 +6660,30 @@
       <x:c r="D31" s="457"/>
       <x:c r="E31" s="457"/>
       <x:c r="F31" s="464"/>
-      <x:c r="G31" s="465"/>
+      <x:c r="G31" s="521"/>
       <x:c r="H31" s="466"/>
       <x:c r="I31" s="467"/>
       <x:c r="J31" s="467"/>
       <x:c r="K31" s="467"/>
       <x:c r="L31" s="467"/>
-      <x:c r="M31" s="466"/>
-      <x:c r="N31" s="467"/>
+      <x:c r="M31" s="522"/>
+      <x:c r="N31" s="466"/>
       <x:c r="O31" s="467"/>
       <x:c r="P31" s="467"/>
       <x:c r="Q31" s="467"/>
-      <x:c r="R31" s="466"/>
-      <x:c r="S31" s="467"/>
-      <x:c r="T31" s="467"/>
+      <x:c r="R31" s="467"/>
+      <x:c r="S31" s="522"/>
+      <x:c r="T31" s="466"/>
       <x:c r="U31" s="467"/>
       <x:c r="V31" s="467"/>
-      <x:c r="W31" s="466"/>
-      <x:c r="X31" s="468"/>
-      <x:c r="Y31" s="469"/>
-      <x:c r="Z31" s="329"/>
-      <x:c r="AA31" s="328"/>
-      <x:c r="AB31"/>
-      <x:c r="AC31"/>
-      <x:c r="AD31"/>
+      <x:c r="W31" s="467"/>
+      <x:c r="X31" s="467"/>
+      <x:c r="Y31" s="522"/>
+      <x:c r="Z31" s="527"/>
+      <x:c r="AA31" s="468"/>
+      <x:c r="AB31" s="469"/>
+      <x:c r="AC31" s="329"/>
+      <x:c r="AD31" s="328"/>
       <x:c r="AE31"/>
       <x:c r="AF31"/>
       <x:c r="AG31"/>
@@ -5740,6 +6692,9 @@
       <x:c r="AJ31"/>
       <x:c r="AK31"/>
       <x:c r="AL31"/>
+      <x:c r="AM31"/>
+      <x:c r="AN31"/>
+      <x:c r="AO31"/>
     </x:row>
     <x:row r="32" ht="88" hidden="0" customHeight="1">
       <x:c r="A32" s="471"/>
@@ -5748,30 +6703,30 @@
       <x:c r="D32" s="472"/>
       <x:c r="E32" s="472"/>
       <x:c r="F32" s="480"/>
-      <x:c r="G32" s="481"/>
+      <x:c r="G32" s="523"/>
       <x:c r="H32" s="482"/>
       <x:c r="I32" s="483"/>
       <x:c r="J32" s="483"/>
       <x:c r="K32" s="483"/>
       <x:c r="L32" s="483"/>
-      <x:c r="M32" s="482"/>
+      <x:c r="M32" s="524"/>
       <x:c r="N32" s="482"/>
-      <x:c r="O32" s="483"/>
+      <x:c r="O32" s="482"/>
       <x:c r="P32" s="483"/>
       <x:c r="Q32" s="483"/>
-      <x:c r="R32" s="482"/>
-      <x:c r="S32" s="483"/>
-      <x:c r="T32" s="483"/>
+      <x:c r="R32" s="483"/>
+      <x:c r="S32" s="524"/>
+      <x:c r="T32" s="482"/>
       <x:c r="U32" s="483"/>
       <x:c r="V32" s="483"/>
-      <x:c r="W32" s="484"/>
-      <x:c r="X32" s="485"/>
-      <x:c r="Y32" s="486"/>
-      <x:c r="Z32" s="409"/>
-      <x:c r="AA32" s="487"/>
-      <x:c r="AB32"/>
-      <x:c r="AC32"/>
-      <x:c r="AD32"/>
+      <x:c r="W32" s="483"/>
+      <x:c r="X32" s="483"/>
+      <x:c r="Y32" s="524"/>
+      <x:c r="Z32" s="528"/>
+      <x:c r="AA32" s="485"/>
+      <x:c r="AB32" s="486"/>
+      <x:c r="AC32" s="409"/>
+      <x:c r="AD32" s="487"/>
       <x:c r="AE32"/>
       <x:c r="AF32"/>
       <x:c r="AG32"/>
@@ -5780,6 +6735,9 @@
       <x:c r="AJ32"/>
       <x:c r="AK32"/>
       <x:c r="AL32"/>
+      <x:c r="AM32"/>
+      <x:c r="AN32"/>
+      <x:c r="AO32"/>
     </x:row>
     <x:row r="33" ht="88" hidden="0" customHeight="1">
       <x:c r="A33" s="456"/>
@@ -5788,30 +6746,30 @@
       <x:c r="D33" s="457"/>
       <x:c r="E33" s="457"/>
       <x:c r="F33" s="464"/>
-      <x:c r="G33" s="465"/>
+      <x:c r="G33" s="521"/>
       <x:c r="H33" s="489"/>
       <x:c r="I33" s="467"/>
       <x:c r="J33" s="467"/>
       <x:c r="K33" s="467"/>
       <x:c r="L33" s="467"/>
-      <x:c r="M33" s="466"/>
-      <x:c r="N33" s="467"/>
+      <x:c r="M33" s="522"/>
+      <x:c r="N33" s="466"/>
       <x:c r="O33" s="467"/>
       <x:c r="P33" s="467"/>
       <x:c r="Q33" s="467"/>
-      <x:c r="R33" s="466"/>
-      <x:c r="S33" s="467"/>
-      <x:c r="T33" s="467"/>
+      <x:c r="R33" s="467"/>
+      <x:c r="S33" s="522"/>
+      <x:c r="T33" s="466"/>
       <x:c r="U33" s="467"/>
       <x:c r="V33" s="467"/>
-      <x:c r="W33" s="466"/>
-      <x:c r="X33" s="468"/>
-      <x:c r="Y33" s="469"/>
-      <x:c r="Z33" s="329"/>
-      <x:c r="AA33" s="328"/>
-      <x:c r="AB33"/>
-      <x:c r="AC33"/>
-      <x:c r="AD33"/>
+      <x:c r="W33" s="467"/>
+      <x:c r="X33" s="467"/>
+      <x:c r="Y33" s="522"/>
+      <x:c r="Z33" s="527"/>
+      <x:c r="AA33" s="468"/>
+      <x:c r="AB33" s="469"/>
+      <x:c r="AC33" s="329"/>
+      <x:c r="AD33" s="328"/>
       <x:c r="AE33"/>
       <x:c r="AF33"/>
       <x:c r="AG33"/>
@@ -5820,6 +6778,9 @@
       <x:c r="AJ33"/>
       <x:c r="AK33"/>
       <x:c r="AL33"/>
+      <x:c r="AM33"/>
+      <x:c r="AN33"/>
+      <x:c r="AO33"/>
     </x:row>
     <x:row r="34" ht="88" hidden="0" customHeight="1">
       <x:c r="A34" s="471"/>
@@ -5828,30 +6789,30 @@
       <x:c r="D34" s="472"/>
       <x:c r="E34" s="472"/>
       <x:c r="F34" s="480"/>
-      <x:c r="G34" s="481"/>
+      <x:c r="G34" s="523"/>
       <x:c r="H34" s="482"/>
       <x:c r="I34" s="483"/>
       <x:c r="J34" s="483"/>
       <x:c r="K34" s="483"/>
       <x:c r="L34" s="483"/>
-      <x:c r="M34" s="482"/>
+      <x:c r="M34" s="524"/>
       <x:c r="N34" s="482"/>
-      <x:c r="O34" s="483"/>
+      <x:c r="O34" s="482"/>
       <x:c r="P34" s="483"/>
       <x:c r="Q34" s="483"/>
-      <x:c r="R34" s="482"/>
-      <x:c r="S34" s="483"/>
-      <x:c r="T34" s="483"/>
+      <x:c r="R34" s="483"/>
+      <x:c r="S34" s="524"/>
+      <x:c r="T34" s="482"/>
       <x:c r="U34" s="483"/>
       <x:c r="V34" s="483"/>
-      <x:c r="W34" s="484"/>
-      <x:c r="X34" s="485"/>
-      <x:c r="Y34" s="486"/>
-      <x:c r="Z34" s="409"/>
-      <x:c r="AA34" s="487"/>
-      <x:c r="AB34"/>
-      <x:c r="AC34"/>
-      <x:c r="AD34"/>
+      <x:c r="W34" s="483"/>
+      <x:c r="X34" s="483"/>
+      <x:c r="Y34" s="524"/>
+      <x:c r="Z34" s="528"/>
+      <x:c r="AA34" s="485"/>
+      <x:c r="AB34" s="486"/>
+      <x:c r="AC34" s="409"/>
+      <x:c r="AD34" s="487"/>
       <x:c r="AE34"/>
       <x:c r="AF34"/>
       <x:c r="AG34"/>
@@ -5860,6 +6821,9 @@
       <x:c r="AJ34"/>
       <x:c r="AK34"/>
       <x:c r="AL34"/>
+      <x:c r="AM34"/>
+      <x:c r="AN34"/>
+      <x:c r="AO34"/>
     </x:row>
     <x:row r="35" ht="88" hidden="0" customHeight="1">
       <x:c r="A35" s="456"/>
@@ -5868,30 +6832,30 @@
       <x:c r="D35" s="457"/>
       <x:c r="E35" s="457"/>
       <x:c r="F35" s="464"/>
-      <x:c r="G35" s="465"/>
+      <x:c r="G35" s="521"/>
       <x:c r="H35" s="466"/>
       <x:c r="I35" s="466"/>
       <x:c r="J35" s="466"/>
       <x:c r="K35" s="467"/>
       <x:c r="L35" s="467"/>
-      <x:c r="M35" s="466"/>
+      <x:c r="M35" s="522"/>
       <x:c r="N35" s="466"/>
-      <x:c r="O35" s="467"/>
+      <x:c r="O35" s="466"/>
       <x:c r="P35" s="467"/>
       <x:c r="Q35" s="467"/>
-      <x:c r="R35" s="466"/>
-      <x:c r="S35" s="466"/>
+      <x:c r="R35" s="467"/>
+      <x:c r="S35" s="522"/>
       <x:c r="T35" s="466"/>
-      <x:c r="U35" s="467"/>
-      <x:c r="V35" s="467"/>
-      <x:c r="W35" s="466"/>
-      <x:c r="X35" s="468"/>
-      <x:c r="Y35" s="469"/>
-      <x:c r="Z35" s="329"/>
-      <x:c r="AA35" s="328"/>
-      <x:c r="AB35"/>
-      <x:c r="AC35"/>
-      <x:c r="AD35"/>
+      <x:c r="U35" s="466"/>
+      <x:c r="V35" s="466"/>
+      <x:c r="W35" s="467"/>
+      <x:c r="X35" s="467"/>
+      <x:c r="Y35" s="522"/>
+      <x:c r="Z35" s="527"/>
+      <x:c r="AA35" s="468"/>
+      <x:c r="AB35" s="469"/>
+      <x:c r="AC35" s="329"/>
+      <x:c r="AD35" s="328"/>
       <x:c r="AE35"/>
       <x:c r="AF35"/>
       <x:c r="AG35"/>
@@ -5900,6 +6864,9 @@
       <x:c r="AJ35"/>
       <x:c r="AK35"/>
       <x:c r="AL35"/>
+      <x:c r="AM35"/>
+      <x:c r="AN35"/>
+      <x:c r="AO35"/>
     </x:row>
     <x:row r="36" ht="88" hidden="0" customHeight="1">
       <x:c r="A36" s="471"/>
@@ -5908,30 +6875,30 @@
       <x:c r="D36" s="472"/>
       <x:c r="E36" s="472"/>
       <x:c r="F36" s="480"/>
-      <x:c r="G36" s="481"/>
+      <x:c r="G36" s="523"/>
       <x:c r="H36" s="482"/>
       <x:c r="I36" s="483"/>
       <x:c r="J36" s="483"/>
       <x:c r="K36" s="483"/>
       <x:c r="L36" s="483"/>
-      <x:c r="M36" s="482"/>
+      <x:c r="M36" s="524"/>
       <x:c r="N36" s="482"/>
       <x:c r="O36" s="482"/>
-      <x:c r="P36" s="483"/>
+      <x:c r="P36" s="482"/>
       <x:c r="Q36" s="483"/>
-      <x:c r="R36" s="482"/>
-      <x:c r="S36" s="482"/>
-      <x:c r="T36" s="483"/>
-      <x:c r="U36" s="483"/>
+      <x:c r="R36" s="483"/>
+      <x:c r="S36" s="524"/>
+      <x:c r="T36" s="482"/>
+      <x:c r="U36" s="482"/>
       <x:c r="V36" s="483"/>
-      <x:c r="W36" s="484"/>
-      <x:c r="X36" s="485"/>
-      <x:c r="Y36" s="486"/>
-      <x:c r="Z36" s="409"/>
-      <x:c r="AA36" s="487"/>
-      <x:c r="AB36"/>
-      <x:c r="AC36"/>
-      <x:c r="AD36"/>
+      <x:c r="W36" s="483"/>
+      <x:c r="X36" s="483"/>
+      <x:c r="Y36" s="524"/>
+      <x:c r="Z36" s="528"/>
+      <x:c r="AA36" s="485"/>
+      <x:c r="AB36" s="486"/>
+      <x:c r="AC36" s="409"/>
+      <x:c r="AD36" s="487"/>
       <x:c r="AE36"/>
       <x:c r="AF36"/>
       <x:c r="AG36"/>
@@ -5940,6 +6907,9 @@
       <x:c r="AJ36"/>
       <x:c r="AK36"/>
       <x:c r="AL36"/>
+      <x:c r="AM36"/>
+      <x:c r="AN36"/>
+      <x:c r="AO36"/>
     </x:row>
     <x:row r="37" ht="88" hidden="0" customHeight="1">
       <x:c r="A37" s="456"/>
@@ -5948,30 +6918,30 @@
       <x:c r="D37" s="457"/>
       <x:c r="E37" s="457"/>
       <x:c r="F37" s="464"/>
-      <x:c r="G37" s="465"/>
+      <x:c r="G37" s="521"/>
       <x:c r="H37" s="466"/>
       <x:c r="I37" s="466"/>
       <x:c r="J37" s="466"/>
       <x:c r="K37" s="467"/>
       <x:c r="L37" s="467"/>
-      <x:c r="M37" s="466"/>
+      <x:c r="M37" s="522"/>
       <x:c r="N37" s="466"/>
       <x:c r="O37" s="466"/>
-      <x:c r="P37" s="467"/>
+      <x:c r="P37" s="466"/>
       <x:c r="Q37" s="467"/>
-      <x:c r="R37" s="466"/>
-      <x:c r="S37" s="466"/>
+      <x:c r="R37" s="467"/>
+      <x:c r="S37" s="522"/>
       <x:c r="T37" s="466"/>
-      <x:c r="U37" s="467"/>
-      <x:c r="V37" s="467"/>
-      <x:c r="W37" s="466"/>
-      <x:c r="X37" s="468"/>
-      <x:c r="Y37" s="469"/>
-      <x:c r="Z37" s="329"/>
-      <x:c r="AA37" s="328"/>
-      <x:c r="AB37"/>
-      <x:c r="AC37"/>
-      <x:c r="AD37"/>
+      <x:c r="U37" s="466"/>
+      <x:c r="V37" s="466"/>
+      <x:c r="W37" s="467"/>
+      <x:c r="X37" s="467"/>
+      <x:c r="Y37" s="522"/>
+      <x:c r="Z37" s="527"/>
+      <x:c r="AA37" s="468"/>
+      <x:c r="AB37" s="469"/>
+      <x:c r="AC37" s="329"/>
+      <x:c r="AD37" s="328"/>
       <x:c r="AE37"/>
       <x:c r="AF37"/>
       <x:c r="AG37"/>
@@ -5980,6 +6950,9 @@
       <x:c r="AJ37"/>
       <x:c r="AK37"/>
       <x:c r="AL37"/>
+      <x:c r="AM37"/>
+      <x:c r="AN37"/>
+      <x:c r="AO37"/>
     </x:row>
     <x:row r="38" ht="88" hidden="0" customHeight="1">
       <x:c r="A38" s="471"/>
@@ -5988,30 +6961,30 @@
       <x:c r="D38" s="472"/>
       <x:c r="E38" s="472"/>
       <x:c r="F38" s="480"/>
-      <x:c r="G38" s="481"/>
+      <x:c r="G38" s="523"/>
       <x:c r="H38" s="482"/>
       <x:c r="I38" s="483"/>
       <x:c r="J38" s="483"/>
       <x:c r="K38" s="483"/>
       <x:c r="L38" s="483"/>
-      <x:c r="M38" s="482"/>
+      <x:c r="M38" s="524"/>
       <x:c r="N38" s="482"/>
       <x:c r="O38" s="482"/>
-      <x:c r="P38" s="483"/>
+      <x:c r="P38" s="482"/>
       <x:c r="Q38" s="483"/>
-      <x:c r="R38" s="482"/>
-      <x:c r="S38" s="482"/>
+      <x:c r="R38" s="483"/>
+      <x:c r="S38" s="524"/>
       <x:c r="T38" s="482"/>
-      <x:c r="U38" s="483"/>
-      <x:c r="V38" s="483"/>
-      <x:c r="W38" s="484"/>
-      <x:c r="X38" s="485"/>
-      <x:c r="Y38" s="486"/>
-      <x:c r="Z38" s="409"/>
-      <x:c r="AA38" s="487"/>
-      <x:c r="AB38"/>
-      <x:c r="AC38"/>
-      <x:c r="AD38"/>
+      <x:c r="U38" s="482"/>
+      <x:c r="V38" s="482"/>
+      <x:c r="W38" s="483"/>
+      <x:c r="X38" s="483"/>
+      <x:c r="Y38" s="524"/>
+      <x:c r="Z38" s="528"/>
+      <x:c r="AA38" s="485"/>
+      <x:c r="AB38" s="486"/>
+      <x:c r="AC38" s="409"/>
+      <x:c r="AD38" s="487"/>
       <x:c r="AE38"/>
       <x:c r="AF38"/>
       <x:c r="AG38"/>
@@ -6020,6 +6993,9 @@
       <x:c r="AJ38"/>
       <x:c r="AK38"/>
       <x:c r="AL38"/>
+      <x:c r="AM38"/>
+      <x:c r="AN38"/>
+      <x:c r="AO38"/>
     </x:row>
     <x:row r="39" ht="88" hidden="0" customHeight="1">
       <x:c r="A39" s="456"/>
@@ -6028,30 +7004,30 @@
       <x:c r="D39" s="457"/>
       <x:c r="E39" s="457"/>
       <x:c r="F39" s="464"/>
-      <x:c r="G39" s="465"/>
+      <x:c r="G39" s="521"/>
       <x:c r="H39" s="466"/>
       <x:c r="I39" s="466"/>
       <x:c r="J39" s="466"/>
       <x:c r="K39" s="467"/>
       <x:c r="L39" s="467"/>
-      <x:c r="M39" s="466"/>
+      <x:c r="M39" s="522"/>
       <x:c r="N39" s="466"/>
-      <x:c r="O39" s="467"/>
+      <x:c r="O39" s="466"/>
       <x:c r="P39" s="467"/>
       <x:c r="Q39" s="467"/>
-      <x:c r="R39" s="466"/>
-      <x:c r="S39" s="466"/>
+      <x:c r="R39" s="467"/>
+      <x:c r="S39" s="522"/>
       <x:c r="T39" s="466"/>
-      <x:c r="U39" s="467"/>
-      <x:c r="V39" s="467"/>
-      <x:c r="W39" s="466"/>
-      <x:c r="X39" s="468"/>
-      <x:c r="Y39" s="469"/>
-      <x:c r="Z39" s="329"/>
-      <x:c r="AA39" s="328"/>
-      <x:c r="AB39"/>
-      <x:c r="AC39"/>
-      <x:c r="AD39"/>
+      <x:c r="U39" s="466"/>
+      <x:c r="V39" s="466"/>
+      <x:c r="W39" s="467"/>
+      <x:c r="X39" s="467"/>
+      <x:c r="Y39" s="522"/>
+      <x:c r="Z39" s="527"/>
+      <x:c r="AA39" s="468"/>
+      <x:c r="AB39" s="469"/>
+      <x:c r="AC39" s="329"/>
+      <x:c r="AD39" s="328"/>
       <x:c r="AE39"/>
       <x:c r="AF39"/>
       <x:c r="AG39"/>
@@ -6060,6 +7036,9 @@
       <x:c r="AJ39"/>
       <x:c r="AK39"/>
       <x:c r="AL39"/>
+      <x:c r="AM39"/>
+      <x:c r="AN39"/>
+      <x:c r="AO39"/>
     </x:row>
     <x:row r="40" ht="88" hidden="0" customHeight="1">
       <x:c r="A40" s="471"/>
@@ -6068,30 +7047,30 @@
       <x:c r="D40" s="472"/>
       <x:c r="E40" s="472"/>
       <x:c r="F40" s="480"/>
-      <x:c r="G40" s="481"/>
+      <x:c r="G40" s="523"/>
       <x:c r="H40" s="482"/>
       <x:c r="I40" s="483"/>
       <x:c r="J40" s="483"/>
       <x:c r="K40" s="483"/>
       <x:c r="L40" s="483"/>
-      <x:c r="M40" s="482"/>
+      <x:c r="M40" s="524"/>
       <x:c r="N40" s="482"/>
       <x:c r="O40" s="482"/>
-      <x:c r="P40" s="483"/>
+      <x:c r="P40" s="482"/>
       <x:c r="Q40" s="483"/>
-      <x:c r="R40" s="482"/>
-      <x:c r="S40" s="482"/>
-      <x:c r="T40" s="483"/>
-      <x:c r="U40" s="483"/>
+      <x:c r="R40" s="483"/>
+      <x:c r="S40" s="524"/>
+      <x:c r="T40" s="482"/>
+      <x:c r="U40" s="482"/>
       <x:c r="V40" s="483"/>
-      <x:c r="W40" s="484"/>
-      <x:c r="X40" s="485"/>
-      <x:c r="Y40" s="486"/>
-      <x:c r="Z40" s="409"/>
-      <x:c r="AA40" s="487"/>
-      <x:c r="AB40"/>
-      <x:c r="AC40"/>
-      <x:c r="AD40"/>
+      <x:c r="W40" s="483"/>
+      <x:c r="X40" s="483"/>
+      <x:c r="Y40" s="524"/>
+      <x:c r="Z40" s="528"/>
+      <x:c r="AA40" s="485"/>
+      <x:c r="AB40" s="486"/>
+      <x:c r="AC40" s="409"/>
+      <x:c r="AD40" s="487"/>
       <x:c r="AE40"/>
       <x:c r="AF40"/>
       <x:c r="AG40"/>
@@ -6100,6 +7079,9 @@
       <x:c r="AJ40"/>
       <x:c r="AK40"/>
       <x:c r="AL40"/>
+      <x:c r="AM40"/>
+      <x:c r="AN40"/>
+      <x:c r="AO40"/>
     </x:row>
     <x:row r="41" ht="88" hidden="0" customHeight="1">
       <x:c r="A41" s="456"/>
@@ -6108,30 +7090,30 @@
       <x:c r="D41" s="457"/>
       <x:c r="E41" s="457"/>
       <x:c r="F41" s="464"/>
-      <x:c r="G41" s="465"/>
+      <x:c r="G41" s="521"/>
       <x:c r="H41" s="466"/>
       <x:c r="I41" s="466"/>
       <x:c r="J41" s="466"/>
       <x:c r="K41" s="467"/>
       <x:c r="L41" s="467"/>
-      <x:c r="M41" s="489"/>
+      <x:c r="M41" s="522"/>
       <x:c r="N41" s="489"/>
-      <x:c r="O41" s="467"/>
+      <x:c r="O41" s="489"/>
       <x:c r="P41" s="467"/>
       <x:c r="Q41" s="467"/>
-      <x:c r="R41" s="466"/>
-      <x:c r="S41" s="466"/>
+      <x:c r="R41" s="467"/>
+      <x:c r="S41" s="522"/>
       <x:c r="T41" s="466"/>
-      <x:c r="U41" s="467"/>
-      <x:c r="V41" s="467"/>
-      <x:c r="W41" s="466"/>
-      <x:c r="X41" s="468"/>
-      <x:c r="Y41" s="469"/>
-      <x:c r="Z41" s="329"/>
-      <x:c r="AA41" s="328"/>
-      <x:c r="AB41"/>
-      <x:c r="AC41"/>
-      <x:c r="AD41"/>
+      <x:c r="U41" s="466"/>
+      <x:c r="V41" s="466"/>
+      <x:c r="W41" s="467"/>
+      <x:c r="X41" s="467"/>
+      <x:c r="Y41" s="522"/>
+      <x:c r="Z41" s="527"/>
+      <x:c r="AA41" s="468"/>
+      <x:c r="AB41" s="469"/>
+      <x:c r="AC41" s="329"/>
+      <x:c r="AD41" s="328"/>
       <x:c r="AE41"/>
       <x:c r="AF41"/>
       <x:c r="AG41"/>
@@ -6140,6 +7122,9 @@
       <x:c r="AJ41"/>
       <x:c r="AK41"/>
       <x:c r="AL41"/>
+      <x:c r="AM41"/>
+      <x:c r="AN41"/>
+      <x:c r="AO41"/>
     </x:row>
     <x:row r="42" ht="88" hidden="0" customHeight="1">
       <x:c r="A42" s="471"/>
@@ -6148,30 +7133,30 @@
       <x:c r="D42" s="472"/>
       <x:c r="E42" s="472"/>
       <x:c r="F42" s="480"/>
-      <x:c r="G42" s="481"/>
+      <x:c r="G42" s="523"/>
       <x:c r="H42" s="482"/>
       <x:c r="I42" s="483"/>
       <x:c r="J42" s="483"/>
       <x:c r="K42" s="483"/>
       <x:c r="L42" s="483"/>
-      <x:c r="M42" s="482"/>
+      <x:c r="M42" s="524"/>
       <x:c r="N42" s="482"/>
       <x:c r="O42" s="482"/>
-      <x:c r="P42" s="483"/>
+      <x:c r="P42" s="482"/>
       <x:c r="Q42" s="483"/>
-      <x:c r="R42" s="482"/>
-      <x:c r="S42" s="482"/>
+      <x:c r="R42" s="483"/>
+      <x:c r="S42" s="524"/>
       <x:c r="T42" s="482"/>
-      <x:c r="U42" s="483"/>
-      <x:c r="V42" s="483"/>
-      <x:c r="W42" s="484"/>
-      <x:c r="X42" s="485"/>
-      <x:c r="Y42" s="486"/>
-      <x:c r="Z42" s="409"/>
-      <x:c r="AA42" s="487"/>
-      <x:c r="AB42"/>
-      <x:c r="AC42"/>
-      <x:c r="AD42"/>
+      <x:c r="U42" s="482"/>
+      <x:c r="V42" s="482"/>
+      <x:c r="W42" s="483"/>
+      <x:c r="X42" s="483"/>
+      <x:c r="Y42" s="524"/>
+      <x:c r="Z42" s="528"/>
+      <x:c r="AA42" s="485"/>
+      <x:c r="AB42" s="486"/>
+      <x:c r="AC42" s="409"/>
+      <x:c r="AD42" s="487"/>
       <x:c r="AE42"/>
       <x:c r="AF42"/>
       <x:c r="AG42"/>
@@ -6180,6 +7165,9 @@
       <x:c r="AJ42"/>
       <x:c r="AK42"/>
       <x:c r="AL42"/>
+      <x:c r="AM42"/>
+      <x:c r="AN42"/>
+      <x:c r="AO42"/>
     </x:row>
     <x:row r="43" ht="88" hidden="0" customHeight="1">
       <x:c r="A43" s="456"/>
@@ -6188,30 +7176,30 @@
       <x:c r="D43" s="457"/>
       <x:c r="E43" s="457"/>
       <x:c r="F43" s="464"/>
-      <x:c r="G43" s="465"/>
+      <x:c r="G43" s="521"/>
       <x:c r="H43" s="466"/>
       <x:c r="I43" s="466"/>
       <x:c r="J43" s="466"/>
       <x:c r="K43" s="467"/>
       <x:c r="L43" s="467"/>
-      <x:c r="M43" s="466"/>
+      <x:c r="M43" s="522"/>
       <x:c r="N43" s="466"/>
       <x:c r="O43" s="466"/>
-      <x:c r="P43" s="467"/>
+      <x:c r="P43" s="466"/>
       <x:c r="Q43" s="467"/>
-      <x:c r="R43" s="466"/>
-      <x:c r="S43" s="466"/>
+      <x:c r="R43" s="467"/>
+      <x:c r="S43" s="522"/>
       <x:c r="T43" s="466"/>
-      <x:c r="U43" s="467"/>
-      <x:c r="V43" s="467"/>
-      <x:c r="W43" s="466"/>
-      <x:c r="X43" s="468"/>
-      <x:c r="Y43" s="469"/>
-      <x:c r="Z43" s="329"/>
-      <x:c r="AA43" s="328"/>
-      <x:c r="AB43"/>
-      <x:c r="AC43"/>
-      <x:c r="AD43"/>
+      <x:c r="U43" s="466"/>
+      <x:c r="V43" s="466"/>
+      <x:c r="W43" s="467"/>
+      <x:c r="X43" s="467"/>
+      <x:c r="Y43" s="522"/>
+      <x:c r="Z43" s="527"/>
+      <x:c r="AA43" s="468"/>
+      <x:c r="AB43" s="469"/>
+      <x:c r="AC43" s="329"/>
+      <x:c r="AD43" s="328"/>
       <x:c r="AE43"/>
       <x:c r="AF43"/>
       <x:c r="AG43"/>
@@ -6220,6 +7208,9 @@
       <x:c r="AJ43"/>
       <x:c r="AK43"/>
       <x:c r="AL43"/>
+      <x:c r="AM43"/>
+      <x:c r="AN43"/>
+      <x:c r="AO43"/>
     </x:row>
     <x:row r="44" ht="88" hidden="0" customHeight="1">
       <x:c r="A44" s="471"/>
@@ -6228,30 +7219,30 @@
       <x:c r="D44" s="472"/>
       <x:c r="E44" s="472"/>
       <x:c r="F44" s="480"/>
-      <x:c r="G44" s="481"/>
+      <x:c r="G44" s="523"/>
       <x:c r="H44" s="482"/>
       <x:c r="I44" s="483"/>
       <x:c r="J44" s="483"/>
       <x:c r="K44" s="483"/>
       <x:c r="L44" s="483"/>
-      <x:c r="M44" s="482"/>
+      <x:c r="M44" s="524"/>
       <x:c r="N44" s="482"/>
       <x:c r="O44" s="482"/>
-      <x:c r="P44" s="483"/>
+      <x:c r="P44" s="482"/>
       <x:c r="Q44" s="483"/>
-      <x:c r="R44" s="482"/>
-      <x:c r="S44" s="482"/>
-      <x:c r="T44" s="483"/>
-      <x:c r="U44" s="483"/>
+      <x:c r="R44" s="483"/>
+      <x:c r="S44" s="524"/>
+      <x:c r="T44" s="482"/>
+      <x:c r="U44" s="482"/>
       <x:c r="V44" s="483"/>
-      <x:c r="W44" s="484"/>
-      <x:c r="X44" s="485"/>
-      <x:c r="Y44" s="486"/>
-      <x:c r="Z44" s="409"/>
-      <x:c r="AA44" s="487"/>
-      <x:c r="AB44"/>
-      <x:c r="AC44"/>
-      <x:c r="AD44"/>
+      <x:c r="W44" s="483"/>
+      <x:c r="X44" s="483"/>
+      <x:c r="Y44" s="524"/>
+      <x:c r="Z44" s="528"/>
+      <x:c r="AA44" s="485"/>
+      <x:c r="AB44" s="486"/>
+      <x:c r="AC44" s="409"/>
+      <x:c r="AD44" s="487"/>
       <x:c r="AE44"/>
       <x:c r="AF44"/>
       <x:c r="AG44"/>
@@ -6260,6 +7251,9 @@
       <x:c r="AJ44"/>
       <x:c r="AK44"/>
       <x:c r="AL44"/>
+      <x:c r="AM44"/>
+      <x:c r="AN44"/>
+      <x:c r="AO44"/>
     </x:row>
     <x:row r="45" ht="88" hidden="0" customHeight="1">
       <x:c r="A45" s="456"/>
@@ -6268,30 +7262,30 @@
       <x:c r="D45" s="457"/>
       <x:c r="E45" s="457"/>
       <x:c r="F45" s="464"/>
-      <x:c r="G45" s="465"/>
+      <x:c r="G45" s="521"/>
       <x:c r="H45" s="466"/>
       <x:c r="I45" s="466"/>
       <x:c r="J45" s="466"/>
       <x:c r="K45" s="467"/>
       <x:c r="L45" s="467"/>
-      <x:c r="M45" s="466"/>
+      <x:c r="M45" s="522"/>
       <x:c r="N45" s="466"/>
-      <x:c r="O45" s="467"/>
+      <x:c r="O45" s="466"/>
       <x:c r="P45" s="467"/>
       <x:c r="Q45" s="467"/>
-      <x:c r="R45" s="466"/>
-      <x:c r="S45" s="466"/>
+      <x:c r="R45" s="467"/>
+      <x:c r="S45" s="522"/>
       <x:c r="T45" s="466"/>
-      <x:c r="U45" s="467"/>
-      <x:c r="V45" s="467"/>
-      <x:c r="W45" s="466"/>
-      <x:c r="X45" s="468"/>
-      <x:c r="Y45" s="469"/>
-      <x:c r="Z45" s="329"/>
-      <x:c r="AA45" s="328"/>
-      <x:c r="AB45"/>
-      <x:c r="AC45"/>
-      <x:c r="AD45"/>
+      <x:c r="U45" s="466"/>
+      <x:c r="V45" s="466"/>
+      <x:c r="W45" s="467"/>
+      <x:c r="X45" s="467"/>
+      <x:c r="Y45" s="522"/>
+      <x:c r="Z45" s="527"/>
+      <x:c r="AA45" s="468"/>
+      <x:c r="AB45" s="469"/>
+      <x:c r="AC45" s="329"/>
+      <x:c r="AD45" s="328"/>
       <x:c r="AE45"/>
       <x:c r="AF45"/>
       <x:c r="AG45"/>
@@ -6300,6 +7294,9 @@
       <x:c r="AJ45"/>
       <x:c r="AK45"/>
       <x:c r="AL45"/>
+      <x:c r="AM45"/>
+      <x:c r="AN45"/>
+      <x:c r="AO45"/>
     </x:row>
     <x:row r="46" ht="88" hidden="0" customHeight="1">
       <x:c r="A46" s="471"/>
@@ -6308,30 +7305,30 @@
       <x:c r="D46" s="472"/>
       <x:c r="E46" s="472"/>
       <x:c r="F46" s="480"/>
-      <x:c r="G46" s="481"/>
+      <x:c r="G46" s="523"/>
       <x:c r="H46" s="482"/>
       <x:c r="I46" s="483"/>
       <x:c r="J46" s="483"/>
       <x:c r="K46" s="483"/>
       <x:c r="L46" s="483"/>
-      <x:c r="M46" s="482"/>
+      <x:c r="M46" s="524"/>
       <x:c r="N46" s="482"/>
       <x:c r="O46" s="482"/>
-      <x:c r="P46" s="483"/>
+      <x:c r="P46" s="482"/>
       <x:c r="Q46" s="483"/>
-      <x:c r="R46" s="482"/>
-      <x:c r="S46" s="482"/>
+      <x:c r="R46" s="483"/>
+      <x:c r="S46" s="524"/>
       <x:c r="T46" s="482"/>
-      <x:c r="U46" s="483"/>
-      <x:c r="V46" s="483"/>
-      <x:c r="W46" s="484"/>
-      <x:c r="X46" s="485"/>
-      <x:c r="Y46" s="486"/>
-      <x:c r="Z46" s="409"/>
-      <x:c r="AA46" s="487"/>
-      <x:c r="AB46"/>
-      <x:c r="AC46"/>
-      <x:c r="AD46"/>
+      <x:c r="U46" s="482"/>
+      <x:c r="V46" s="482"/>
+      <x:c r="W46" s="483"/>
+      <x:c r="X46" s="483"/>
+      <x:c r="Y46" s="524"/>
+      <x:c r="Z46" s="528"/>
+      <x:c r="AA46" s="485"/>
+      <x:c r="AB46" s="486"/>
+      <x:c r="AC46" s="409"/>
+      <x:c r="AD46" s="487"/>
       <x:c r="AE46"/>
       <x:c r="AF46"/>
       <x:c r="AG46"/>
@@ -6340,6 +7337,9 @@
       <x:c r="AJ46"/>
       <x:c r="AK46"/>
       <x:c r="AL46"/>
+      <x:c r="AM46"/>
+      <x:c r="AN46"/>
+      <x:c r="AO46"/>
     </x:row>
     <x:row r="47" ht="88" hidden="0" customHeight="1">
       <x:c r="A47" s="456"/>
@@ -6348,30 +7348,30 @@
       <x:c r="D47" s="457"/>
       <x:c r="E47" s="457"/>
       <x:c r="F47" s="464"/>
-      <x:c r="G47" s="465"/>
+      <x:c r="G47" s="521"/>
       <x:c r="H47" s="466"/>
       <x:c r="I47" s="466"/>
       <x:c r="J47" s="466"/>
       <x:c r="K47" s="467"/>
       <x:c r="L47" s="467"/>
-      <x:c r="M47" s="466"/>
-      <x:c r="N47" s="467"/>
+      <x:c r="M47" s="522"/>
+      <x:c r="N47" s="466"/>
       <x:c r="O47" s="467"/>
       <x:c r="P47" s="467"/>
       <x:c r="Q47" s="467"/>
-      <x:c r="R47" s="466"/>
-      <x:c r="S47" s="467"/>
-      <x:c r="T47" s="467"/>
+      <x:c r="R47" s="467"/>
+      <x:c r="S47" s="522"/>
+      <x:c r="T47" s="466"/>
       <x:c r="U47" s="467"/>
       <x:c r="V47" s="467"/>
-      <x:c r="W47" s="466"/>
-      <x:c r="X47" s="468"/>
-      <x:c r="Y47" s="469"/>
-      <x:c r="Z47" s="329"/>
-      <x:c r="AA47" s="328"/>
-      <x:c r="AB47"/>
-      <x:c r="AC47"/>
-      <x:c r="AD47"/>
+      <x:c r="W47" s="467"/>
+      <x:c r="X47" s="467"/>
+      <x:c r="Y47" s="522"/>
+      <x:c r="Z47" s="527"/>
+      <x:c r="AA47" s="468"/>
+      <x:c r="AB47" s="469"/>
+      <x:c r="AC47" s="329"/>
+      <x:c r="AD47" s="328"/>
       <x:c r="AE47"/>
       <x:c r="AF47"/>
       <x:c r="AG47"/>
@@ -6380,6 +7380,9 @@
       <x:c r="AJ47"/>
       <x:c r="AK47"/>
       <x:c r="AL47"/>
+      <x:c r="AM47"/>
+      <x:c r="AN47"/>
+      <x:c r="AO47"/>
     </x:row>
     <x:row r="48" ht="88" hidden="0" customHeight="1">
       <x:c r="A48" s="471"/>
@@ -6388,30 +7391,30 @@
       <x:c r="D48" s="472"/>
       <x:c r="E48" s="472"/>
       <x:c r="F48" s="480"/>
-      <x:c r="G48" s="481"/>
+      <x:c r="G48" s="523"/>
       <x:c r="H48" s="482"/>
       <x:c r="I48" s="483"/>
       <x:c r="J48" s="483"/>
       <x:c r="K48" s="483"/>
       <x:c r="L48" s="483"/>
-      <x:c r="M48" s="482"/>
+      <x:c r="M48" s="524"/>
       <x:c r="N48" s="482"/>
-      <x:c r="O48" s="483"/>
+      <x:c r="O48" s="482"/>
       <x:c r="P48" s="483"/>
       <x:c r="Q48" s="483"/>
-      <x:c r="R48" s="482"/>
-      <x:c r="S48" s="483"/>
-      <x:c r="T48" s="483"/>
+      <x:c r="R48" s="483"/>
+      <x:c r="S48" s="524"/>
+      <x:c r="T48" s="482"/>
       <x:c r="U48" s="483"/>
       <x:c r="V48" s="483"/>
-      <x:c r="W48" s="484"/>
-      <x:c r="X48" s="485"/>
-      <x:c r="Y48" s="486"/>
-      <x:c r="Z48" s="409"/>
-      <x:c r="AA48" s="487"/>
-      <x:c r="AB48"/>
-      <x:c r="AC48"/>
-      <x:c r="AD48"/>
+      <x:c r="W48" s="483"/>
+      <x:c r="X48" s="483"/>
+      <x:c r="Y48" s="524"/>
+      <x:c r="Z48" s="528"/>
+      <x:c r="AA48" s="485"/>
+      <x:c r="AB48" s="486"/>
+      <x:c r="AC48" s="409"/>
+      <x:c r="AD48" s="487"/>
       <x:c r="AE48"/>
       <x:c r="AF48"/>
       <x:c r="AG48"/>
@@ -6420,6 +7423,9 @@
       <x:c r="AJ48"/>
       <x:c r="AK48"/>
       <x:c r="AL48"/>
+      <x:c r="AM48"/>
+      <x:c r="AN48"/>
+      <x:c r="AO48"/>
     </x:row>
     <x:row r="49" ht="88" hidden="0" customHeight="1">
       <x:c r="A49" s="456"/>
@@ -6428,30 +7434,30 @@
       <x:c r="D49" s="457"/>
       <x:c r="E49" s="457"/>
       <x:c r="F49" s="464"/>
-      <x:c r="G49" s="465"/>
+      <x:c r="G49" s="521"/>
       <x:c r="H49" s="466"/>
       <x:c r="I49" s="467"/>
       <x:c r="J49" s="467"/>
       <x:c r="K49" s="467"/>
       <x:c r="L49" s="467"/>
-      <x:c r="M49" s="489"/>
-      <x:c r="N49" s="467"/>
+      <x:c r="M49" s="522"/>
+      <x:c r="N49" s="489"/>
       <x:c r="O49" s="467"/>
       <x:c r="P49" s="467"/>
       <x:c r="Q49" s="467"/>
-      <x:c r="R49" s="489"/>
-      <x:c r="S49" s="467"/>
-      <x:c r="T49" s="467"/>
+      <x:c r="R49" s="467"/>
+      <x:c r="S49" s="522"/>
+      <x:c r="T49" s="489"/>
       <x:c r="U49" s="467"/>
       <x:c r="V49" s="467"/>
-      <x:c r="W49" s="466"/>
-      <x:c r="X49" s="468"/>
-      <x:c r="Y49" s="469"/>
-      <x:c r="Z49" s="329"/>
-      <x:c r="AA49" s="328"/>
-      <x:c r="AB49"/>
-      <x:c r="AC49"/>
-      <x:c r="AD49"/>
+      <x:c r="W49" s="467"/>
+      <x:c r="X49" s="467"/>
+      <x:c r="Y49" s="522"/>
+      <x:c r="Z49" s="527"/>
+      <x:c r="AA49" s="468"/>
+      <x:c r="AB49" s="469"/>
+      <x:c r="AC49" s="329"/>
+      <x:c r="AD49" s="328"/>
       <x:c r="AE49"/>
       <x:c r="AF49"/>
       <x:c r="AG49"/>
@@ -6460,6 +7466,9 @@
       <x:c r="AJ49"/>
       <x:c r="AK49"/>
       <x:c r="AL49"/>
+      <x:c r="AM49"/>
+      <x:c r="AN49"/>
+      <x:c r="AO49"/>
     </x:row>
     <x:row r="50" ht="88" hidden="0" customHeight="1">
       <x:c r="A50" s="471"/>
@@ -6468,30 +7477,30 @@
       <x:c r="D50" s="472"/>
       <x:c r="E50" s="472"/>
       <x:c r="F50" s="480"/>
-      <x:c r="G50" s="481"/>
+      <x:c r="G50" s="523"/>
       <x:c r="H50" s="482"/>
       <x:c r="I50" s="483"/>
       <x:c r="J50" s="483"/>
       <x:c r="K50" s="483"/>
       <x:c r="L50" s="483"/>
-      <x:c r="M50" s="482"/>
+      <x:c r="M50" s="524"/>
       <x:c r="N50" s="482"/>
-      <x:c r="O50" s="483"/>
+      <x:c r="O50" s="482"/>
       <x:c r="P50" s="483"/>
       <x:c r="Q50" s="483"/>
-      <x:c r="R50" s="482"/>
-      <x:c r="S50" s="483"/>
-      <x:c r="T50" s="483"/>
+      <x:c r="R50" s="483"/>
+      <x:c r="S50" s="524"/>
+      <x:c r="T50" s="482"/>
       <x:c r="U50" s="483"/>
       <x:c r="V50" s="483"/>
-      <x:c r="W50" s="484"/>
-      <x:c r="X50" s="485"/>
-      <x:c r="Y50" s="486"/>
-      <x:c r="Z50" s="409"/>
-      <x:c r="AA50" s="487"/>
-      <x:c r="AB50"/>
-      <x:c r="AC50"/>
-      <x:c r="AD50"/>
+      <x:c r="W50" s="483"/>
+      <x:c r="X50" s="483"/>
+      <x:c r="Y50" s="524"/>
+      <x:c r="Z50" s="528"/>
+      <x:c r="AA50" s="485"/>
+      <x:c r="AB50" s="486"/>
+      <x:c r="AC50" s="409"/>
+      <x:c r="AD50" s="487"/>
       <x:c r="AE50"/>
       <x:c r="AF50"/>
       <x:c r="AG50"/>
@@ -6500,12 +7509,15 @@
       <x:c r="AJ50"/>
       <x:c r="AK50"/>
       <x:c r="AL50"/>
+      <x:c r="AM50"/>
+      <x:c r="AN50"/>
+      <x:c r="AO50"/>
     </x:row>
     <x:row r="51">
-      <x:c r="G51" s="448"/>
-      <x:c r="H51" s="448"/>
-      <x:c r="I51" s="448"/>
-      <x:c r="J51" s="448"/>
+      <x:c r="G51"/>
+      <x:c r="H51"/>
+      <x:c r="I51"/>
+      <x:c r="J51"/>
       <x:c r="K51"/>
       <x:c r="L51"/>
       <x:c r="M51"/>
@@ -6526,12 +7538,15 @@
       <x:c r="AB51"/>
       <x:c r="AC51"/>
       <x:c r="AD51"/>
+      <x:c r="AE51"/>
+      <x:c r="AF51"/>
+      <x:c r="AG51"/>
     </x:row>
     <x:row r="52">
-      <x:c r="G52" s="448"/>
-      <x:c r="H52" s="448"/>
-      <x:c r="I52" s="448"/>
-      <x:c r="J52" s="448"/>
+      <x:c r="G52"/>
+      <x:c r="H52"/>
+      <x:c r="I52"/>
+      <x:c r="J52"/>
       <x:c r="K52"/>
       <x:c r="L52"/>
       <x:c r="M52"/>
@@ -6552,12 +7567,15 @@
       <x:c r="AB52"/>
       <x:c r="AC52"/>
       <x:c r="AD52"/>
+      <x:c r="AE52"/>
+      <x:c r="AF52"/>
+      <x:c r="AG52"/>
     </x:row>
     <x:row r="53">
-      <x:c r="G53" s="448"/>
-      <x:c r="H53" s="448"/>
-      <x:c r="I53" s="448"/>
-      <x:c r="J53" s="448"/>
+      <x:c r="G53"/>
+      <x:c r="H53"/>
+      <x:c r="I53"/>
+      <x:c r="J53"/>
       <x:c r="K53"/>
       <x:c r="L53"/>
       <x:c r="M53"/>
@@ -6578,12 +7596,15 @@
       <x:c r="AB53"/>
       <x:c r="AC53"/>
       <x:c r="AD53"/>
+      <x:c r="AE53"/>
+      <x:c r="AF53"/>
+      <x:c r="AG53"/>
     </x:row>
     <x:row r="54">
-      <x:c r="G54" s="448"/>
-      <x:c r="H54" s="448"/>
-      <x:c r="I54" s="448"/>
-      <x:c r="J54" s="448"/>
+      <x:c r="G54"/>
+      <x:c r="H54"/>
+      <x:c r="I54"/>
+      <x:c r="J54"/>
       <x:c r="K54"/>
       <x:c r="L54"/>
       <x:c r="M54"/>
@@ -6604,12 +7625,15 @@
       <x:c r="AB54"/>
       <x:c r="AC54"/>
       <x:c r="AD54"/>
+      <x:c r="AE54"/>
+      <x:c r="AF54"/>
+      <x:c r="AG54"/>
     </x:row>
     <x:row r="55">
-      <x:c r="G55" s="448"/>
-      <x:c r="H55" s="448"/>
-      <x:c r="I55" s="448"/>
-      <x:c r="J55" s="448"/>
+      <x:c r="G55"/>
+      <x:c r="H55"/>
+      <x:c r="I55"/>
+      <x:c r="J55"/>
       <x:c r="K55"/>
       <x:c r="L55"/>
       <x:c r="M55"/>
@@ -6630,12 +7654,15 @@
       <x:c r="AB55"/>
       <x:c r="AC55"/>
       <x:c r="AD55"/>
+      <x:c r="AE55"/>
+      <x:c r="AF55"/>
+      <x:c r="AG55"/>
     </x:row>
     <x:row r="56">
-      <x:c r="G56" s="448"/>
-      <x:c r="H56" s="448"/>
-      <x:c r="I56" s="448"/>
-      <x:c r="J56" s="448"/>
+      <x:c r="G56"/>
+      <x:c r="H56"/>
+      <x:c r="I56"/>
+      <x:c r="J56"/>
       <x:c r="K56"/>
       <x:c r="L56"/>
       <x:c r="M56"/>
@@ -6656,12 +7683,15 @@
       <x:c r="AB56"/>
       <x:c r="AC56"/>
       <x:c r="AD56"/>
+      <x:c r="AE56"/>
+      <x:c r="AF56"/>
+      <x:c r="AG56"/>
     </x:row>
     <x:row r="57">
-      <x:c r="G57" s="448"/>
-      <x:c r="H57" s="448"/>
-      <x:c r="I57" s="448"/>
-      <x:c r="J57" s="448"/>
+      <x:c r="G57"/>
+      <x:c r="H57"/>
+      <x:c r="I57"/>
+      <x:c r="J57"/>
       <x:c r="K57"/>
       <x:c r="L57"/>
       <x:c r="M57"/>
@@ -6682,12 +7712,15 @@
       <x:c r="AB57"/>
       <x:c r="AC57"/>
       <x:c r="AD57"/>
+      <x:c r="AE57"/>
+      <x:c r="AF57"/>
+      <x:c r="AG57"/>
     </x:row>
     <x:row r="58">
-      <x:c r="G58" s="448"/>
-      <x:c r="H58" s="448"/>
-      <x:c r="I58" s="448"/>
-      <x:c r="J58" s="448"/>
+      <x:c r="G58"/>
+      <x:c r="H58"/>
+      <x:c r="I58"/>
+      <x:c r="J58"/>
       <x:c r="K58"/>
       <x:c r="L58"/>
       <x:c r="M58"/>
@@ -6708,12 +7741,15 @@
       <x:c r="AB58"/>
       <x:c r="AC58"/>
       <x:c r="AD58"/>
+      <x:c r="AE58"/>
+      <x:c r="AF58"/>
+      <x:c r="AG58"/>
     </x:row>
     <x:row r="59">
-      <x:c r="G59" s="448"/>
-      <x:c r="H59" s="448"/>
-      <x:c r="I59" s="448"/>
-      <x:c r="J59" s="448"/>
+      <x:c r="G59"/>
+      <x:c r="H59"/>
+      <x:c r="I59"/>
+      <x:c r="J59"/>
       <x:c r="K59"/>
       <x:c r="L59"/>
       <x:c r="M59"/>
@@ -6734,12 +7770,15 @@
       <x:c r="AB59"/>
       <x:c r="AC59"/>
       <x:c r="AD59"/>
+      <x:c r="AE59"/>
+      <x:c r="AF59"/>
+      <x:c r="AG59"/>
     </x:row>
     <x:row r="60">
-      <x:c r="G60" s="448"/>
-      <x:c r="H60" s="448"/>
-      <x:c r="I60" s="448"/>
-      <x:c r="J60" s="448"/>
+      <x:c r="G60"/>
+      <x:c r="H60"/>
+      <x:c r="I60"/>
+      <x:c r="J60"/>
       <x:c r="K60"/>
       <x:c r="L60"/>
       <x:c r="M60"/>
@@ -6760,12 +7799,15 @@
       <x:c r="AB60"/>
       <x:c r="AC60"/>
       <x:c r="AD60"/>
+      <x:c r="AE60"/>
+      <x:c r="AF60"/>
+      <x:c r="AG60"/>
     </x:row>
     <x:row r="61">
-      <x:c r="G61" s="448"/>
-      <x:c r="H61" s="448"/>
-      <x:c r="I61" s="448"/>
-      <x:c r="J61" s="448"/>
+      <x:c r="G61"/>
+      <x:c r="H61"/>
+      <x:c r="I61"/>
+      <x:c r="J61"/>
       <x:c r="K61"/>
       <x:c r="L61"/>
       <x:c r="M61"/>
@@ -6786,12 +7828,15 @@
       <x:c r="AB61"/>
       <x:c r="AC61"/>
       <x:c r="AD61"/>
+      <x:c r="AE61"/>
+      <x:c r="AF61"/>
+      <x:c r="AG61"/>
     </x:row>
     <x:row r="62">
-      <x:c r="G62" s="448"/>
-      <x:c r="H62" s="448"/>
-      <x:c r="I62" s="448"/>
-      <x:c r="J62" s="448"/>
+      <x:c r="G62"/>
+      <x:c r="H62"/>
+      <x:c r="I62"/>
+      <x:c r="J62"/>
       <x:c r="K62"/>
       <x:c r="L62"/>
       <x:c r="M62"/>
@@ -6812,12 +7857,15 @@
       <x:c r="AB62"/>
       <x:c r="AC62"/>
       <x:c r="AD62"/>
+      <x:c r="AE62"/>
+      <x:c r="AF62"/>
+      <x:c r="AG62"/>
     </x:row>
     <x:row r="63">
-      <x:c r="G63" s="448"/>
-      <x:c r="H63" s="448"/>
-      <x:c r="I63" s="448"/>
-      <x:c r="J63" s="448"/>
+      <x:c r="G63"/>
+      <x:c r="H63"/>
+      <x:c r="I63"/>
+      <x:c r="J63"/>
       <x:c r="K63"/>
       <x:c r="L63"/>
       <x:c r="M63"/>
@@ -6838,12 +7886,15 @@
       <x:c r="AB63"/>
       <x:c r="AC63"/>
       <x:c r="AD63"/>
+      <x:c r="AE63"/>
+      <x:c r="AF63"/>
+      <x:c r="AG63"/>
     </x:row>
     <x:row r="64">
-      <x:c r="G64" s="448"/>
-      <x:c r="H64" s="448"/>
-      <x:c r="I64" s="448"/>
-      <x:c r="J64" s="448"/>
+      <x:c r="G64"/>
+      <x:c r="H64"/>
+      <x:c r="I64"/>
+      <x:c r="J64"/>
       <x:c r="K64"/>
       <x:c r="L64"/>
       <x:c r="M64"/>
@@ -6864,12 +7915,15 @@
       <x:c r="AB64"/>
       <x:c r="AC64"/>
       <x:c r="AD64"/>
+      <x:c r="AE64"/>
+      <x:c r="AF64"/>
+      <x:c r="AG64"/>
     </x:row>
     <x:row r="65">
-      <x:c r="G65" s="448"/>
-      <x:c r="H65" s="448"/>
-      <x:c r="I65" s="448"/>
-      <x:c r="J65" s="448"/>
+      <x:c r="G65"/>
+      <x:c r="H65"/>
+      <x:c r="I65"/>
+      <x:c r="J65"/>
       <x:c r="K65"/>
       <x:c r="L65"/>
       <x:c r="M65"/>
@@ -6890,12 +7944,15 @@
       <x:c r="AB65"/>
       <x:c r="AC65"/>
       <x:c r="AD65"/>
+      <x:c r="AE65"/>
+      <x:c r="AF65"/>
+      <x:c r="AG65"/>
     </x:row>
     <x:row r="66">
-      <x:c r="G66" s="448"/>
-      <x:c r="H66" s="448"/>
-      <x:c r="I66" s="448"/>
-      <x:c r="J66" s="448"/>
+      <x:c r="G66"/>
+      <x:c r="H66"/>
+      <x:c r="I66"/>
+      <x:c r="J66"/>
       <x:c r="K66"/>
       <x:c r="L66"/>
       <x:c r="M66"/>
@@ -6916,12 +7973,15 @@
       <x:c r="AB66"/>
       <x:c r="AC66"/>
       <x:c r="AD66"/>
+      <x:c r="AE66"/>
+      <x:c r="AF66"/>
+      <x:c r="AG66"/>
     </x:row>
     <x:row r="67">
-      <x:c r="G67" s="448"/>
-      <x:c r="H67" s="448"/>
-      <x:c r="I67" s="448"/>
-      <x:c r="J67" s="448"/>
+      <x:c r="G67"/>
+      <x:c r="H67"/>
+      <x:c r="I67"/>
+      <x:c r="J67"/>
       <x:c r="K67"/>
       <x:c r="L67"/>
       <x:c r="M67"/>
@@ -6942,12 +8002,15 @@
       <x:c r="AB67"/>
       <x:c r="AC67"/>
       <x:c r="AD67"/>
+      <x:c r="AE67"/>
+      <x:c r="AF67"/>
+      <x:c r="AG67"/>
     </x:row>
     <x:row r="68">
-      <x:c r="G68" s="448"/>
-      <x:c r="H68" s="448"/>
-      <x:c r="I68" s="448"/>
-      <x:c r="J68" s="448"/>
+      <x:c r="G68"/>
+      <x:c r="H68"/>
+      <x:c r="I68"/>
+      <x:c r="J68"/>
       <x:c r="K68"/>
       <x:c r="L68"/>
       <x:c r="M68"/>
@@ -6968,12 +8031,15 @@
       <x:c r="AB68"/>
       <x:c r="AC68"/>
       <x:c r="AD68"/>
+      <x:c r="AE68"/>
+      <x:c r="AF68"/>
+      <x:c r="AG68"/>
     </x:row>
     <x:row r="69">
-      <x:c r="G69" s="448"/>
-      <x:c r="H69" s="448"/>
-      <x:c r="I69" s="448"/>
-      <x:c r="J69" s="448"/>
+      <x:c r="G69"/>
+      <x:c r="H69"/>
+      <x:c r="I69"/>
+      <x:c r="J69"/>
       <x:c r="K69"/>
       <x:c r="L69"/>
       <x:c r="M69"/>
@@ -6994,12 +8060,15 @@
       <x:c r="AB69"/>
       <x:c r="AC69"/>
       <x:c r="AD69"/>
+      <x:c r="AE69"/>
+      <x:c r="AF69"/>
+      <x:c r="AG69"/>
     </x:row>
     <x:row r="70">
-      <x:c r="G70" s="448"/>
-      <x:c r="H70" s="448"/>
-      <x:c r="I70" s="448"/>
-      <x:c r="J70" s="448"/>
+      <x:c r="G70"/>
+      <x:c r="H70"/>
+      <x:c r="I70"/>
+      <x:c r="J70"/>
       <x:c r="K70"/>
       <x:c r="L70"/>
       <x:c r="M70"/>
@@ -7020,12 +8089,15 @@
       <x:c r="AB70"/>
       <x:c r="AC70"/>
       <x:c r="AD70"/>
+      <x:c r="AE70"/>
+      <x:c r="AF70"/>
+      <x:c r="AG70"/>
     </x:row>
     <x:row r="71">
-      <x:c r="G71" s="448"/>
-      <x:c r="H71" s="448"/>
-      <x:c r="I71" s="448"/>
-      <x:c r="J71" s="448"/>
+      <x:c r="G71"/>
+      <x:c r="H71"/>
+      <x:c r="I71"/>
+      <x:c r="J71"/>
       <x:c r="K71"/>
       <x:c r="L71"/>
       <x:c r="M71"/>
@@ -7046,12 +8118,15 @@
       <x:c r="AB71"/>
       <x:c r="AC71"/>
       <x:c r="AD71"/>
+      <x:c r="AE71"/>
+      <x:c r="AF71"/>
+      <x:c r="AG71"/>
     </x:row>
     <x:row r="72">
-      <x:c r="G72" s="448"/>
-      <x:c r="H72" s="448"/>
-      <x:c r="I72" s="448"/>
-      <x:c r="J72" s="448"/>
+      <x:c r="G72"/>
+      <x:c r="H72"/>
+      <x:c r="I72"/>
+      <x:c r="J72"/>
       <x:c r="K72"/>
       <x:c r="L72"/>
       <x:c r="M72"/>
@@ -7072,12 +8147,15 @@
       <x:c r="AB72"/>
       <x:c r="AC72"/>
       <x:c r="AD72"/>
+      <x:c r="AE72"/>
+      <x:c r="AF72"/>
+      <x:c r="AG72"/>
     </x:row>
     <x:row r="73">
-      <x:c r="G73" s="448"/>
-      <x:c r="H73" s="448"/>
-      <x:c r="I73" s="448"/>
-      <x:c r="J73" s="448"/>
+      <x:c r="G73"/>
+      <x:c r="H73"/>
+      <x:c r="I73"/>
+      <x:c r="J73"/>
       <x:c r="K73"/>
       <x:c r="L73"/>
       <x:c r="M73"/>
@@ -7098,12 +8176,15 @@
       <x:c r="AB73"/>
       <x:c r="AC73"/>
       <x:c r="AD73"/>
+      <x:c r="AE73"/>
+      <x:c r="AF73"/>
+      <x:c r="AG73"/>
     </x:row>
     <x:row r="74">
-      <x:c r="G74" s="448"/>
-      <x:c r="H74" s="448"/>
-      <x:c r="I74" s="448"/>
-      <x:c r="J74" s="448"/>
+      <x:c r="G74"/>
+      <x:c r="H74"/>
+      <x:c r="I74"/>
+      <x:c r="J74"/>
       <x:c r="K74"/>
       <x:c r="L74"/>
       <x:c r="M74"/>
@@ -7124,12 +8205,15 @@
       <x:c r="AB74"/>
       <x:c r="AC74"/>
       <x:c r="AD74"/>
+      <x:c r="AE74"/>
+      <x:c r="AF74"/>
+      <x:c r="AG74"/>
     </x:row>
     <x:row r="75">
-      <x:c r="G75" s="448"/>
-      <x:c r="H75" s="448"/>
-      <x:c r="I75" s="448"/>
-      <x:c r="J75" s="448"/>
+      <x:c r="G75"/>
+      <x:c r="H75"/>
+      <x:c r="I75"/>
+      <x:c r="J75"/>
       <x:c r="K75"/>
       <x:c r="L75"/>
       <x:c r="M75"/>
@@ -7150,12 +8234,15 @@
       <x:c r="AB75"/>
       <x:c r="AC75"/>
       <x:c r="AD75"/>
+      <x:c r="AE75"/>
+      <x:c r="AF75"/>
+      <x:c r="AG75"/>
     </x:row>
     <x:row r="76">
-      <x:c r="G76" s="448"/>
-      <x:c r="H76" s="448"/>
-      <x:c r="I76" s="448"/>
-      <x:c r="J76" s="448"/>
+      <x:c r="G76"/>
+      <x:c r="H76"/>
+      <x:c r="I76"/>
+      <x:c r="J76"/>
       <x:c r="K76"/>
       <x:c r="L76"/>
       <x:c r="M76"/>
@@ -7176,12 +8263,15 @@
       <x:c r="AB76"/>
       <x:c r="AC76"/>
       <x:c r="AD76"/>
+      <x:c r="AE76"/>
+      <x:c r="AF76"/>
+      <x:c r="AG76"/>
     </x:row>
     <x:row r="77">
-      <x:c r="G77" s="448"/>
-      <x:c r="H77" s="448"/>
-      <x:c r="I77" s="448"/>
-      <x:c r="J77" s="448"/>
+      <x:c r="G77"/>
+      <x:c r="H77"/>
+      <x:c r="I77"/>
+      <x:c r="J77"/>
       <x:c r="K77"/>
       <x:c r="L77"/>
       <x:c r="M77"/>
@@ -7202,12 +8292,15 @@
       <x:c r="AB77"/>
       <x:c r="AC77"/>
       <x:c r="AD77"/>
+      <x:c r="AE77"/>
+      <x:c r="AF77"/>
+      <x:c r="AG77"/>
     </x:row>
     <x:row r="78">
-      <x:c r="G78" s="448"/>
-      <x:c r="H78" s="448"/>
-      <x:c r="I78" s="448"/>
-      <x:c r="J78" s="448"/>
+      <x:c r="G78"/>
+      <x:c r="H78"/>
+      <x:c r="I78"/>
+      <x:c r="J78"/>
       <x:c r="K78"/>
       <x:c r="L78"/>
       <x:c r="M78"/>
@@ -7228,12 +8321,15 @@
       <x:c r="AB78"/>
       <x:c r="AC78"/>
       <x:c r="AD78"/>
+      <x:c r="AE78"/>
+      <x:c r="AF78"/>
+      <x:c r="AG78"/>
     </x:row>
     <x:row r="79">
-      <x:c r="G79" s="448"/>
-      <x:c r="H79" s="448"/>
-      <x:c r="I79" s="448"/>
-      <x:c r="J79" s="448"/>
+      <x:c r="G79"/>
+      <x:c r="H79"/>
+      <x:c r="I79"/>
+      <x:c r="J79"/>
       <x:c r="K79"/>
       <x:c r="L79"/>
       <x:c r="M79"/>
@@ -7254,12 +8350,15 @@
       <x:c r="AB79"/>
       <x:c r="AC79"/>
       <x:c r="AD79"/>
+      <x:c r="AE79"/>
+      <x:c r="AF79"/>
+      <x:c r="AG79"/>
     </x:row>
     <x:row r="80">
-      <x:c r="G80" s="448"/>
-      <x:c r="H80" s="448"/>
-      <x:c r="I80" s="448"/>
-      <x:c r="J80" s="448"/>
+      <x:c r="G80"/>
+      <x:c r="H80"/>
+      <x:c r="I80"/>
+      <x:c r="J80"/>
       <x:c r="K80"/>
       <x:c r="L80"/>
       <x:c r="M80"/>
@@ -7280,12 +8379,15 @@
       <x:c r="AB80"/>
       <x:c r="AC80"/>
       <x:c r="AD80"/>
+      <x:c r="AE80"/>
+      <x:c r="AF80"/>
+      <x:c r="AG80"/>
     </x:row>
     <x:row r="81">
-      <x:c r="G81" s="448"/>
-      <x:c r="H81" s="448"/>
-      <x:c r="I81" s="448"/>
-      <x:c r="J81" s="448"/>
+      <x:c r="G81"/>
+      <x:c r="H81"/>
+      <x:c r="I81"/>
+      <x:c r="J81"/>
       <x:c r="K81"/>
       <x:c r="L81"/>
       <x:c r="M81"/>
@@ -7306,12 +8408,15 @@
       <x:c r="AB81"/>
       <x:c r="AC81"/>
       <x:c r="AD81"/>
+      <x:c r="AE81"/>
+      <x:c r="AF81"/>
+      <x:c r="AG81"/>
     </x:row>
     <x:row r="82">
-      <x:c r="G82" s="448"/>
-      <x:c r="H82" s="448"/>
-      <x:c r="I82" s="448"/>
-      <x:c r="J82" s="448"/>
+      <x:c r="G82"/>
+      <x:c r="H82"/>
+      <x:c r="I82"/>
+      <x:c r="J82"/>
       <x:c r="K82"/>
       <x:c r="L82"/>
       <x:c r="M82"/>
@@ -7332,12 +8437,15 @@
       <x:c r="AB82"/>
       <x:c r="AC82"/>
       <x:c r="AD82"/>
+      <x:c r="AE82"/>
+      <x:c r="AF82"/>
+      <x:c r="AG82"/>
     </x:row>
     <x:row r="83">
-      <x:c r="G83" s="448"/>
-      <x:c r="H83" s="448"/>
-      <x:c r="I83" s="448"/>
-      <x:c r="J83" s="448"/>
+      <x:c r="G83"/>
+      <x:c r="H83"/>
+      <x:c r="I83"/>
+      <x:c r="J83"/>
       <x:c r="K83"/>
       <x:c r="L83"/>
       <x:c r="M83"/>
@@ -7358,12 +8466,15 @@
       <x:c r="AB83"/>
       <x:c r="AC83"/>
       <x:c r="AD83"/>
+      <x:c r="AE83"/>
+      <x:c r="AF83"/>
+      <x:c r="AG83"/>
     </x:row>
     <x:row r="84">
-      <x:c r="G84" s="448"/>
-      <x:c r="H84" s="448"/>
-      <x:c r="I84" s="448"/>
-      <x:c r="J84" s="448"/>
+      <x:c r="G84"/>
+      <x:c r="H84"/>
+      <x:c r="I84"/>
+      <x:c r="J84"/>
       <x:c r="K84"/>
       <x:c r="L84"/>
       <x:c r="M84"/>
@@ -7384,12 +8495,15 @@
       <x:c r="AB84"/>
       <x:c r="AC84"/>
       <x:c r="AD84"/>
+      <x:c r="AE84"/>
+      <x:c r="AF84"/>
+      <x:c r="AG84"/>
     </x:row>
     <x:row r="85">
-      <x:c r="G85" s="448"/>
-      <x:c r="H85" s="448"/>
-      <x:c r="I85" s="448"/>
-      <x:c r="J85" s="448"/>
+      <x:c r="G85"/>
+      <x:c r="H85"/>
+      <x:c r="I85"/>
+      <x:c r="J85"/>
       <x:c r="K85"/>
       <x:c r="L85"/>
       <x:c r="M85"/>
@@ -7410,12 +8524,15 @@
       <x:c r="AB85"/>
       <x:c r="AC85"/>
       <x:c r="AD85"/>
+      <x:c r="AE85"/>
+      <x:c r="AF85"/>
+      <x:c r="AG85"/>
     </x:row>
     <x:row r="86">
-      <x:c r="G86" s="448"/>
-      <x:c r="H86" s="448"/>
-      <x:c r="I86" s="448"/>
-      <x:c r="J86" s="448"/>
+      <x:c r="G86"/>
+      <x:c r="H86"/>
+      <x:c r="I86"/>
+      <x:c r="J86"/>
       <x:c r="K86"/>
       <x:c r="L86"/>
       <x:c r="M86"/>
@@ -7436,12 +8553,15 @@
       <x:c r="AB86"/>
       <x:c r="AC86"/>
       <x:c r="AD86"/>
+      <x:c r="AE86"/>
+      <x:c r="AF86"/>
+      <x:c r="AG86"/>
     </x:row>
     <x:row r="87">
-      <x:c r="G87" s="448"/>
-      <x:c r="H87" s="448"/>
-      <x:c r="I87" s="448"/>
-      <x:c r="J87" s="448"/>
+      <x:c r="G87"/>
+      <x:c r="H87"/>
+      <x:c r="I87"/>
+      <x:c r="J87"/>
       <x:c r="K87"/>
       <x:c r="L87"/>
       <x:c r="M87"/>
@@ -7462,12 +8582,15 @@
       <x:c r="AB87"/>
       <x:c r="AC87"/>
       <x:c r="AD87"/>
+      <x:c r="AE87"/>
+      <x:c r="AF87"/>
+      <x:c r="AG87"/>
     </x:row>
     <x:row r="88">
-      <x:c r="G88" s="448"/>
-      <x:c r="H88" s="448"/>
-      <x:c r="I88" s="448"/>
-      <x:c r="J88" s="448"/>
+      <x:c r="G88"/>
+      <x:c r="H88"/>
+      <x:c r="I88"/>
+      <x:c r="J88"/>
       <x:c r="K88"/>
       <x:c r="L88"/>
       <x:c r="M88"/>
@@ -7488,12 +8611,15 @@
       <x:c r="AB88"/>
       <x:c r="AC88"/>
       <x:c r="AD88"/>
+      <x:c r="AE88"/>
+      <x:c r="AF88"/>
+      <x:c r="AG88"/>
     </x:row>
     <x:row r="89">
-      <x:c r="G89" s="448"/>
-      <x:c r="H89" s="448"/>
-      <x:c r="I89" s="448"/>
-      <x:c r="J89" s="448"/>
+      <x:c r="G89"/>
+      <x:c r="H89"/>
+      <x:c r="I89"/>
+      <x:c r="J89"/>
       <x:c r="K89"/>
       <x:c r="L89"/>
       <x:c r="M89"/>
@@ -7514,12 +8640,15 @@
       <x:c r="AB89"/>
       <x:c r="AC89"/>
       <x:c r="AD89"/>
+      <x:c r="AE89"/>
+      <x:c r="AF89"/>
+      <x:c r="AG89"/>
     </x:row>
     <x:row r="90">
-      <x:c r="G90" s="448"/>
-      <x:c r="H90" s="448"/>
-      <x:c r="I90" s="448"/>
-      <x:c r="J90" s="448"/>
+      <x:c r="G90"/>
+      <x:c r="H90"/>
+      <x:c r="I90"/>
+      <x:c r="J90"/>
       <x:c r="K90"/>
       <x:c r="L90"/>
       <x:c r="M90"/>
@@ -7540,12 +8669,15 @@
       <x:c r="AB90"/>
       <x:c r="AC90"/>
       <x:c r="AD90"/>
+      <x:c r="AE90"/>
+      <x:c r="AF90"/>
+      <x:c r="AG90"/>
     </x:row>
     <x:row r="91">
-      <x:c r="G91" s="448"/>
-      <x:c r="H91" s="448"/>
-      <x:c r="I91" s="448"/>
-      <x:c r="J91" s="448"/>
+      <x:c r="G91"/>
+      <x:c r="H91"/>
+      <x:c r="I91"/>
+      <x:c r="J91"/>
       <x:c r="K91"/>
       <x:c r="L91"/>
       <x:c r="M91"/>
@@ -7566,12 +8698,15 @@
       <x:c r="AB91"/>
       <x:c r="AC91"/>
       <x:c r="AD91"/>
+      <x:c r="AE91"/>
+      <x:c r="AF91"/>
+      <x:c r="AG91"/>
     </x:row>
     <x:row r="92">
-      <x:c r="G92" s="448"/>
-      <x:c r="H92" s="448"/>
-      <x:c r="I92" s="448"/>
-      <x:c r="J92" s="448"/>
+      <x:c r="G92"/>
+      <x:c r="H92"/>
+      <x:c r="I92"/>
+      <x:c r="J92"/>
       <x:c r="K92"/>
       <x:c r="L92"/>
       <x:c r="M92"/>
@@ -7592,12 +8727,15 @@
       <x:c r="AB92"/>
       <x:c r="AC92"/>
       <x:c r="AD92"/>
+      <x:c r="AE92"/>
+      <x:c r="AF92"/>
+      <x:c r="AG92"/>
     </x:row>
     <x:row r="93">
-      <x:c r="G93" s="448"/>
-      <x:c r="H93" s="448"/>
-      <x:c r="I93" s="448"/>
-      <x:c r="J93" s="448"/>
+      <x:c r="G93"/>
+      <x:c r="H93"/>
+      <x:c r="I93"/>
+      <x:c r="J93"/>
       <x:c r="K93"/>
       <x:c r="L93"/>
       <x:c r="M93"/>
@@ -7618,12 +8756,15 @@
       <x:c r="AB93"/>
       <x:c r="AC93"/>
       <x:c r="AD93"/>
+      <x:c r="AE93"/>
+      <x:c r="AF93"/>
+      <x:c r="AG93"/>
     </x:row>
     <x:row r="94">
-      <x:c r="G94" s="448"/>
-      <x:c r="H94" s="448"/>
-      <x:c r="I94" s="448"/>
-      <x:c r="J94" s="448"/>
+      <x:c r="G94"/>
+      <x:c r="H94"/>
+      <x:c r="I94"/>
+      <x:c r="J94"/>
       <x:c r="K94"/>
       <x:c r="L94"/>
       <x:c r="M94"/>
@@ -7644,12 +8785,15 @@
       <x:c r="AB94"/>
       <x:c r="AC94"/>
       <x:c r="AD94"/>
+      <x:c r="AE94"/>
+      <x:c r="AF94"/>
+      <x:c r="AG94"/>
     </x:row>
     <x:row r="95">
-      <x:c r="G95" s="448"/>
-      <x:c r="H95" s="448"/>
-      <x:c r="I95" s="448"/>
-      <x:c r="J95" s="448"/>
+      <x:c r="G95"/>
+      <x:c r="H95"/>
+      <x:c r="I95"/>
+      <x:c r="J95"/>
       <x:c r="K95"/>
       <x:c r="L95"/>
       <x:c r="M95"/>
@@ -7670,12 +8814,15 @@
       <x:c r="AB95"/>
       <x:c r="AC95"/>
       <x:c r="AD95"/>
+      <x:c r="AE95"/>
+      <x:c r="AF95"/>
+      <x:c r="AG95"/>
     </x:row>
     <x:row r="96">
-      <x:c r="G96" s="448"/>
-      <x:c r="H96" s="448"/>
-      <x:c r="I96" s="448"/>
-      <x:c r="J96" s="448"/>
+      <x:c r="G96"/>
+      <x:c r="H96"/>
+      <x:c r="I96"/>
+      <x:c r="J96"/>
       <x:c r="K96"/>
       <x:c r="L96"/>
       <x:c r="M96"/>
@@ -7696,12 +8843,15 @@
       <x:c r="AB96"/>
       <x:c r="AC96"/>
       <x:c r="AD96"/>
+      <x:c r="AE96"/>
+      <x:c r="AF96"/>
+      <x:c r="AG96"/>
     </x:row>
     <x:row r="97">
-      <x:c r="G97" s="448"/>
-      <x:c r="H97" s="448"/>
-      <x:c r="I97" s="448"/>
-      <x:c r="J97" s="448"/>
+      <x:c r="G97"/>
+      <x:c r="H97"/>
+      <x:c r="I97"/>
+      <x:c r="J97"/>
       <x:c r="K97"/>
       <x:c r="L97"/>
       <x:c r="M97"/>
@@ -7722,12 +8872,15 @@
       <x:c r="AB97"/>
       <x:c r="AC97"/>
       <x:c r="AD97"/>
+      <x:c r="AE97"/>
+      <x:c r="AF97"/>
+      <x:c r="AG97"/>
     </x:row>
     <x:row r="98">
-      <x:c r="G98" s="448"/>
-      <x:c r="H98" s="448"/>
-      <x:c r="I98" s="448"/>
-      <x:c r="J98" s="448"/>
+      <x:c r="G98"/>
+      <x:c r="H98"/>
+      <x:c r="I98"/>
+      <x:c r="J98"/>
       <x:c r="K98"/>
       <x:c r="L98"/>
       <x:c r="M98"/>
@@ -7748,12 +8901,15 @@
       <x:c r="AB98"/>
       <x:c r="AC98"/>
       <x:c r="AD98"/>
+      <x:c r="AE98"/>
+      <x:c r="AF98"/>
+      <x:c r="AG98"/>
     </x:row>
     <x:row r="99">
-      <x:c r="G99" s="448"/>
-      <x:c r="H99" s="448"/>
-      <x:c r="I99" s="448"/>
-      <x:c r="J99" s="448"/>
+      <x:c r="G99"/>
+      <x:c r="H99"/>
+      <x:c r="I99"/>
+      <x:c r="J99"/>
       <x:c r="K99"/>
       <x:c r="L99"/>
       <x:c r="M99"/>
@@ -7774,12 +8930,15 @@
       <x:c r="AB99"/>
       <x:c r="AC99"/>
       <x:c r="AD99"/>
+      <x:c r="AE99"/>
+      <x:c r="AF99"/>
+      <x:c r="AG99"/>
     </x:row>
     <x:row r="100">
-      <x:c r="G100" s="448"/>
-      <x:c r="H100" s="448"/>
-      <x:c r="I100" s="448"/>
-      <x:c r="J100" s="448"/>
+      <x:c r="G100"/>
+      <x:c r="H100"/>
+      <x:c r="I100"/>
+      <x:c r="J100"/>
       <x:c r="K100"/>
       <x:c r="L100"/>
       <x:c r="M100"/>
@@ -7800,12 +8959,15 @@
       <x:c r="AB100"/>
       <x:c r="AC100"/>
       <x:c r="AD100"/>
+      <x:c r="AE100"/>
+      <x:c r="AF100"/>
+      <x:c r="AG100"/>
     </x:row>
     <x:row r="101">
-      <x:c r="G101" s="448"/>
-      <x:c r="H101" s="448"/>
-      <x:c r="I101" s="448"/>
-      <x:c r="J101" s="448"/>
+      <x:c r="G101"/>
+      <x:c r="H101"/>
+      <x:c r="I101"/>
+      <x:c r="J101"/>
       <x:c r="K101"/>
       <x:c r="L101"/>
       <x:c r="M101"/>
@@ -7826,12 +8988,15 @@
       <x:c r="AB101"/>
       <x:c r="AC101"/>
       <x:c r="AD101"/>
+      <x:c r="AE101"/>
+      <x:c r="AF101"/>
+      <x:c r="AG101"/>
     </x:row>
     <x:row r="102">
-      <x:c r="G102" s="448"/>
-      <x:c r="H102" s="448"/>
-      <x:c r="I102" s="448"/>
-      <x:c r="J102" s="448"/>
+      <x:c r="G102"/>
+      <x:c r="H102"/>
+      <x:c r="I102"/>
+      <x:c r="J102"/>
       <x:c r="K102"/>
       <x:c r="L102"/>
       <x:c r="M102"/>
@@ -7852,12 +9017,15 @@
       <x:c r="AB102"/>
       <x:c r="AC102"/>
       <x:c r="AD102"/>
+      <x:c r="AE102"/>
+      <x:c r="AF102"/>
+      <x:c r="AG102"/>
     </x:row>
     <x:row r="103">
-      <x:c r="G103" s="448"/>
-      <x:c r="H103" s="448"/>
-      <x:c r="I103" s="448"/>
-      <x:c r="J103" s="448"/>
+      <x:c r="G103"/>
+      <x:c r="H103"/>
+      <x:c r="I103"/>
+      <x:c r="J103"/>
       <x:c r="K103"/>
       <x:c r="L103"/>
       <x:c r="M103"/>
@@ -7878,12 +9046,15 @@
       <x:c r="AB103"/>
       <x:c r="AC103"/>
       <x:c r="AD103"/>
+      <x:c r="AE103"/>
+      <x:c r="AF103"/>
+      <x:c r="AG103"/>
     </x:row>
     <x:row r="104">
-      <x:c r="G104" s="448"/>
-      <x:c r="H104" s="448"/>
-      <x:c r="I104" s="448"/>
-      <x:c r="J104" s="448"/>
+      <x:c r="G104"/>
+      <x:c r="H104"/>
+      <x:c r="I104"/>
+      <x:c r="J104"/>
       <x:c r="K104"/>
       <x:c r="L104"/>
       <x:c r="M104"/>
@@ -7904,12 +9075,15 @@
       <x:c r="AB104"/>
       <x:c r="AC104"/>
       <x:c r="AD104"/>
+      <x:c r="AE104"/>
+      <x:c r="AF104"/>
+      <x:c r="AG104"/>
     </x:row>
     <x:row r="105">
-      <x:c r="G105" s="448"/>
-      <x:c r="H105" s="448"/>
-      <x:c r="I105" s="448"/>
-      <x:c r="J105" s="448"/>
+      <x:c r="G105"/>
+      <x:c r="H105"/>
+      <x:c r="I105"/>
+      <x:c r="J105"/>
       <x:c r="K105"/>
       <x:c r="L105"/>
       <x:c r="M105"/>
@@ -7930,12 +9104,15 @@
       <x:c r="AB105"/>
       <x:c r="AC105"/>
       <x:c r="AD105"/>
+      <x:c r="AE105"/>
+      <x:c r="AF105"/>
+      <x:c r="AG105"/>
     </x:row>
     <x:row r="106">
-      <x:c r="G106" s="448"/>
-      <x:c r="H106" s="448"/>
-      <x:c r="I106" s="448"/>
-      <x:c r="J106" s="448"/>
+      <x:c r="G106"/>
+      <x:c r="H106"/>
+      <x:c r="I106"/>
+      <x:c r="J106"/>
       <x:c r="K106"/>
       <x:c r="L106"/>
       <x:c r="M106"/>
@@ -7956,12 +9133,15 @@
       <x:c r="AB106"/>
       <x:c r="AC106"/>
       <x:c r="AD106"/>
+      <x:c r="AE106"/>
+      <x:c r="AF106"/>
+      <x:c r="AG106"/>
     </x:row>
     <x:row r="107">
-      <x:c r="G107" s="448"/>
-      <x:c r="H107" s="448"/>
-      <x:c r="I107" s="448"/>
-      <x:c r="J107" s="448"/>
+      <x:c r="G107"/>
+      <x:c r="H107"/>
+      <x:c r="I107"/>
+      <x:c r="J107"/>
       <x:c r="K107"/>
       <x:c r="L107"/>
       <x:c r="M107"/>
@@ -7982,12 +9162,15 @@
       <x:c r="AB107"/>
       <x:c r="AC107"/>
       <x:c r="AD107"/>
+      <x:c r="AE107"/>
+      <x:c r="AF107"/>
+      <x:c r="AG107"/>
     </x:row>
     <x:row r="108">
-      <x:c r="G108" s="448"/>
-      <x:c r="H108" s="448"/>
-      <x:c r="I108" s="448"/>
-      <x:c r="J108" s="448"/>
+      <x:c r="G108"/>
+      <x:c r="H108"/>
+      <x:c r="I108"/>
+      <x:c r="J108"/>
       <x:c r="K108"/>
       <x:c r="L108"/>
       <x:c r="M108"/>
@@ -8008,12 +9191,15 @@
       <x:c r="AB108"/>
       <x:c r="AC108"/>
       <x:c r="AD108"/>
+      <x:c r="AE108"/>
+      <x:c r="AF108"/>
+      <x:c r="AG108"/>
     </x:row>
     <x:row r="109">
-      <x:c r="G109" s="448"/>
-      <x:c r="H109" s="448"/>
-      <x:c r="I109" s="448"/>
-      <x:c r="J109" s="448"/>
+      <x:c r="G109"/>
+      <x:c r="H109"/>
+      <x:c r="I109"/>
+      <x:c r="J109"/>
       <x:c r="K109"/>
       <x:c r="L109"/>
       <x:c r="M109"/>
@@ -8034,12 +9220,15 @@
       <x:c r="AB109"/>
       <x:c r="AC109"/>
       <x:c r="AD109"/>
+      <x:c r="AE109"/>
+      <x:c r="AF109"/>
+      <x:c r="AG109"/>
     </x:row>
     <x:row r="110">
-      <x:c r="G110" s="448"/>
-      <x:c r="H110" s="448"/>
-      <x:c r="I110" s="448"/>
-      <x:c r="J110" s="448"/>
+      <x:c r="G110"/>
+      <x:c r="H110"/>
+      <x:c r="I110"/>
+      <x:c r="J110"/>
       <x:c r="K110"/>
       <x:c r="L110"/>
       <x:c r="M110"/>
@@ -8060,12 +9249,15 @@
       <x:c r="AB110"/>
       <x:c r="AC110"/>
       <x:c r="AD110"/>
+      <x:c r="AE110"/>
+      <x:c r="AF110"/>
+      <x:c r="AG110"/>
     </x:row>
     <x:row r="111">
-      <x:c r="G111" s="448"/>
-      <x:c r="H111" s="448"/>
-      <x:c r="I111" s="448"/>
-      <x:c r="J111" s="448"/>
+      <x:c r="G111"/>
+      <x:c r="H111"/>
+      <x:c r="I111"/>
+      <x:c r="J111"/>
       <x:c r="K111"/>
       <x:c r="L111"/>
       <x:c r="M111"/>
@@ -8086,12 +9278,15 @@
       <x:c r="AB111"/>
       <x:c r="AC111"/>
       <x:c r="AD111"/>
+      <x:c r="AE111"/>
+      <x:c r="AF111"/>
+      <x:c r="AG111"/>
     </x:row>
     <x:row r="112">
-      <x:c r="G112" s="448"/>
-      <x:c r="H112" s="448"/>
-      <x:c r="I112" s="448"/>
-      <x:c r="J112" s="448"/>
+      <x:c r="G112"/>
+      <x:c r="H112"/>
+      <x:c r="I112"/>
+      <x:c r="J112"/>
       <x:c r="K112"/>
       <x:c r="L112"/>
       <x:c r="M112"/>
@@ -8112,12 +9307,15 @@
       <x:c r="AB112"/>
       <x:c r="AC112"/>
       <x:c r="AD112"/>
+      <x:c r="AE112"/>
+      <x:c r="AF112"/>
+      <x:c r="AG112"/>
     </x:row>
     <x:row r="113">
-      <x:c r="G113" s="448"/>
-      <x:c r="H113" s="448"/>
-      <x:c r="I113" s="448"/>
-      <x:c r="J113" s="448"/>
+      <x:c r="G113"/>
+      <x:c r="H113"/>
+      <x:c r="I113"/>
+      <x:c r="J113"/>
       <x:c r="K113"/>
       <x:c r="L113"/>
       <x:c r="M113"/>
@@ -8138,12 +9336,15 @@
       <x:c r="AB113"/>
       <x:c r="AC113"/>
       <x:c r="AD113"/>
+      <x:c r="AE113"/>
+      <x:c r="AF113"/>
+      <x:c r="AG113"/>
     </x:row>
     <x:row r="114">
-      <x:c r="G114" s="448"/>
-      <x:c r="H114" s="448"/>
-      <x:c r="I114" s="448"/>
-      <x:c r="J114" s="448"/>
+      <x:c r="G114"/>
+      <x:c r="H114"/>
+      <x:c r="I114"/>
+      <x:c r="J114"/>
       <x:c r="K114"/>
       <x:c r="L114"/>
       <x:c r="M114"/>
@@ -8164,12 +9365,15 @@
       <x:c r="AB114"/>
       <x:c r="AC114"/>
       <x:c r="AD114"/>
+      <x:c r="AE114"/>
+      <x:c r="AF114"/>
+      <x:c r="AG114"/>
     </x:row>
     <x:row r="115">
-      <x:c r="G115" s="448"/>
-      <x:c r="H115" s="448"/>
-      <x:c r="I115" s="448"/>
-      <x:c r="J115" s="448"/>
+      <x:c r="G115"/>
+      <x:c r="H115"/>
+      <x:c r="I115"/>
+      <x:c r="J115"/>
       <x:c r="K115"/>
       <x:c r="L115"/>
       <x:c r="M115"/>
@@ -8190,12 +9394,15 @@
       <x:c r="AB115"/>
       <x:c r="AC115"/>
       <x:c r="AD115"/>
+      <x:c r="AE115"/>
+      <x:c r="AF115"/>
+      <x:c r="AG115"/>
     </x:row>
     <x:row r="116">
-      <x:c r="G116" s="448"/>
-      <x:c r="H116" s="448"/>
-      <x:c r="I116" s="448"/>
-      <x:c r="J116" s="448"/>
+      <x:c r="G116"/>
+      <x:c r="H116"/>
+      <x:c r="I116"/>
+      <x:c r="J116"/>
       <x:c r="K116"/>
       <x:c r="L116"/>
       <x:c r="M116"/>
@@ -8216,12 +9423,15 @@
       <x:c r="AB116"/>
       <x:c r="AC116"/>
       <x:c r="AD116"/>
+      <x:c r="AE116"/>
+      <x:c r="AF116"/>
+      <x:c r="AG116"/>
     </x:row>
     <x:row r="117">
-      <x:c r="G117" s="448"/>
-      <x:c r="H117" s="448"/>
-      <x:c r="I117" s="448"/>
-      <x:c r="J117" s="448"/>
+      <x:c r="G117"/>
+      <x:c r="H117"/>
+      <x:c r="I117"/>
+      <x:c r="J117"/>
       <x:c r="K117"/>
       <x:c r="L117"/>
       <x:c r="M117"/>
@@ -8242,12 +9452,15 @@
       <x:c r="AB117"/>
       <x:c r="AC117"/>
       <x:c r="AD117"/>
+      <x:c r="AE117"/>
+      <x:c r="AF117"/>
+      <x:c r="AG117"/>
     </x:row>
     <x:row r="118">
-      <x:c r="G118" s="448"/>
-      <x:c r="H118" s="448"/>
-      <x:c r="I118" s="448"/>
-      <x:c r="J118" s="448"/>
+      <x:c r="G118"/>
+      <x:c r="H118"/>
+      <x:c r="I118"/>
+      <x:c r="J118"/>
       <x:c r="K118"/>
       <x:c r="L118"/>
       <x:c r="M118"/>
@@ -8268,12 +9481,15 @@
       <x:c r="AB118"/>
       <x:c r="AC118"/>
       <x:c r="AD118"/>
+      <x:c r="AE118"/>
+      <x:c r="AF118"/>
+      <x:c r="AG118"/>
     </x:row>
     <x:row r="119">
-      <x:c r="G119" s="448"/>
-      <x:c r="H119" s="448"/>
-      <x:c r="I119" s="448"/>
-      <x:c r="J119" s="448"/>
+      <x:c r="G119"/>
+      <x:c r="H119"/>
+      <x:c r="I119"/>
+      <x:c r="J119"/>
       <x:c r="K119"/>
       <x:c r="L119"/>
       <x:c r="M119"/>
@@ -8294,12 +9510,15 @@
       <x:c r="AB119"/>
       <x:c r="AC119"/>
       <x:c r="AD119"/>
+      <x:c r="AE119"/>
+      <x:c r="AF119"/>
+      <x:c r="AG119"/>
     </x:row>
     <x:row r="120">
-      <x:c r="G120" s="448"/>
-      <x:c r="H120" s="448"/>
-      <x:c r="I120" s="448"/>
-      <x:c r="J120" s="448"/>
+      <x:c r="G120"/>
+      <x:c r="H120"/>
+      <x:c r="I120"/>
+      <x:c r="J120"/>
       <x:c r="K120"/>
       <x:c r="L120"/>
       <x:c r="M120"/>
@@ -8320,12 +9539,15 @@
       <x:c r="AB120"/>
       <x:c r="AC120"/>
       <x:c r="AD120"/>
+      <x:c r="AE120"/>
+      <x:c r="AF120"/>
+      <x:c r="AG120"/>
     </x:row>
     <x:row r="121">
-      <x:c r="G121" s="448"/>
-      <x:c r="H121" s="448"/>
-      <x:c r="I121" s="448"/>
-      <x:c r="J121" s="448"/>
+      <x:c r="G121"/>
+      <x:c r="H121"/>
+      <x:c r="I121"/>
+      <x:c r="J121"/>
       <x:c r="K121"/>
       <x:c r="L121"/>
       <x:c r="M121"/>
@@ -8346,12 +9568,15 @@
       <x:c r="AB121"/>
       <x:c r="AC121"/>
       <x:c r="AD121"/>
+      <x:c r="AE121"/>
+      <x:c r="AF121"/>
+      <x:c r="AG121"/>
     </x:row>
     <x:row r="122">
-      <x:c r="G122" s="448"/>
-      <x:c r="H122" s="448"/>
-      <x:c r="I122" s="448"/>
-      <x:c r="J122" s="448"/>
+      <x:c r="G122"/>
+      <x:c r="H122"/>
+      <x:c r="I122"/>
+      <x:c r="J122"/>
       <x:c r="K122"/>
       <x:c r="L122"/>
       <x:c r="M122"/>
@@ -8372,12 +9597,15 @@
       <x:c r="AB122"/>
       <x:c r="AC122"/>
       <x:c r="AD122"/>
+      <x:c r="AE122"/>
+      <x:c r="AF122"/>
+      <x:c r="AG122"/>
     </x:row>
     <x:row r="123">
-      <x:c r="G123" s="448"/>
-      <x:c r="H123" s="448"/>
-      <x:c r="I123" s="448"/>
-      <x:c r="J123" s="448"/>
+      <x:c r="G123"/>
+      <x:c r="H123"/>
+      <x:c r="I123"/>
+      <x:c r="J123"/>
       <x:c r="K123"/>
       <x:c r="L123"/>
       <x:c r="M123"/>
@@ -8398,12 +9626,15 @@
       <x:c r="AB123"/>
       <x:c r="AC123"/>
       <x:c r="AD123"/>
+      <x:c r="AE123"/>
+      <x:c r="AF123"/>
+      <x:c r="AG123"/>
     </x:row>
     <x:row r="124">
-      <x:c r="G124" s="448"/>
-      <x:c r="H124" s="448"/>
-      <x:c r="I124" s="448"/>
-      <x:c r="J124" s="448"/>
+      <x:c r="G124"/>
+      <x:c r="H124"/>
+      <x:c r="I124"/>
+      <x:c r="J124"/>
       <x:c r="K124"/>
       <x:c r="L124"/>
       <x:c r="M124"/>
@@ -8424,12 +9655,15 @@
       <x:c r="AB124"/>
       <x:c r="AC124"/>
       <x:c r="AD124"/>
+      <x:c r="AE124"/>
+      <x:c r="AF124"/>
+      <x:c r="AG124"/>
     </x:row>
     <x:row r="125">
-      <x:c r="G125" s="448"/>
-      <x:c r="H125" s="448"/>
-      <x:c r="I125" s="448"/>
-      <x:c r="J125" s="448"/>
+      <x:c r="G125"/>
+      <x:c r="H125"/>
+      <x:c r="I125"/>
+      <x:c r="J125"/>
       <x:c r="K125"/>
       <x:c r="L125"/>
       <x:c r="M125"/>
@@ -8450,12 +9684,15 @@
       <x:c r="AB125"/>
       <x:c r="AC125"/>
       <x:c r="AD125"/>
+      <x:c r="AE125"/>
+      <x:c r="AF125"/>
+      <x:c r="AG125"/>
     </x:row>
     <x:row r="126">
-      <x:c r="G126" s="448"/>
-      <x:c r="H126" s="448"/>
-      <x:c r="I126" s="448"/>
-      <x:c r="J126" s="448"/>
+      <x:c r="G126"/>
+      <x:c r="H126"/>
+      <x:c r="I126"/>
+      <x:c r="J126"/>
       <x:c r="K126"/>
       <x:c r="L126"/>
       <x:c r="M126"/>
@@ -8476,12 +9713,15 @@
       <x:c r="AB126"/>
       <x:c r="AC126"/>
       <x:c r="AD126"/>
+      <x:c r="AE126"/>
+      <x:c r="AF126"/>
+      <x:c r="AG126"/>
     </x:row>
     <x:row r="127">
-      <x:c r="G127" s="448"/>
-      <x:c r="H127" s="448"/>
-      <x:c r="I127" s="448"/>
-      <x:c r="J127" s="448"/>
+      <x:c r="G127"/>
+      <x:c r="H127"/>
+      <x:c r="I127"/>
+      <x:c r="J127"/>
       <x:c r="K127"/>
       <x:c r="L127"/>
       <x:c r="M127"/>
@@ -8502,12 +9742,15 @@
       <x:c r="AB127"/>
       <x:c r="AC127"/>
       <x:c r="AD127"/>
+      <x:c r="AE127"/>
+      <x:c r="AF127"/>
+      <x:c r="AG127"/>
     </x:row>
     <x:row r="128">
-      <x:c r="G128" s="448"/>
-      <x:c r="H128" s="448"/>
-      <x:c r="I128" s="448"/>
-      <x:c r="J128" s="448"/>
+      <x:c r="G128"/>
+      <x:c r="H128"/>
+      <x:c r="I128"/>
+      <x:c r="J128"/>
       <x:c r="K128"/>
       <x:c r="L128"/>
       <x:c r="M128"/>
@@ -8528,12 +9771,15 @@
       <x:c r="AB128"/>
       <x:c r="AC128"/>
       <x:c r="AD128"/>
+      <x:c r="AE128"/>
+      <x:c r="AF128"/>
+      <x:c r="AG128"/>
     </x:row>
     <x:row r="129">
-      <x:c r="G129" s="448"/>
-      <x:c r="H129" s="448"/>
-      <x:c r="I129" s="448"/>
-      <x:c r="J129" s="448"/>
+      <x:c r="G129"/>
+      <x:c r="H129"/>
+      <x:c r="I129"/>
+      <x:c r="J129"/>
       <x:c r="K129"/>
       <x:c r="L129"/>
       <x:c r="M129"/>
@@ -8554,12 +9800,15 @@
       <x:c r="AB129"/>
       <x:c r="AC129"/>
       <x:c r="AD129"/>
+      <x:c r="AE129"/>
+      <x:c r="AF129"/>
+      <x:c r="AG129"/>
     </x:row>
     <x:row r="130">
-      <x:c r="G130" s="448"/>
-      <x:c r="H130" s="448"/>
-      <x:c r="I130" s="448"/>
-      <x:c r="J130" s="448"/>
+      <x:c r="G130"/>
+      <x:c r="H130"/>
+      <x:c r="I130"/>
+      <x:c r="J130"/>
       <x:c r="K130"/>
       <x:c r="L130"/>
       <x:c r="M130"/>
@@ -8580,12 +9829,15 @@
       <x:c r="AB130"/>
       <x:c r="AC130"/>
       <x:c r="AD130"/>
+      <x:c r="AE130"/>
+      <x:c r="AF130"/>
+      <x:c r="AG130"/>
     </x:row>
     <x:row r="131">
-      <x:c r="G131" s="448"/>
-      <x:c r="H131" s="448"/>
-      <x:c r="I131" s="448"/>
-      <x:c r="J131" s="448"/>
+      <x:c r="G131"/>
+      <x:c r="H131"/>
+      <x:c r="I131"/>
+      <x:c r="J131"/>
       <x:c r="K131"/>
       <x:c r="L131"/>
       <x:c r="M131"/>
@@ -8606,12 +9858,15 @@
       <x:c r="AB131"/>
       <x:c r="AC131"/>
       <x:c r="AD131"/>
+      <x:c r="AE131"/>
+      <x:c r="AF131"/>
+      <x:c r="AG131"/>
     </x:row>
     <x:row r="132">
-      <x:c r="G132" s="448"/>
-      <x:c r="H132" s="448"/>
-      <x:c r="I132" s="448"/>
-      <x:c r="J132" s="448"/>
+      <x:c r="G132"/>
+      <x:c r="H132"/>
+      <x:c r="I132"/>
+      <x:c r="J132"/>
       <x:c r="K132"/>
       <x:c r="L132"/>
       <x:c r="M132"/>
@@ -8632,12 +9887,15 @@
       <x:c r="AB132"/>
       <x:c r="AC132"/>
       <x:c r="AD132"/>
+      <x:c r="AE132"/>
+      <x:c r="AF132"/>
+      <x:c r="AG132"/>
     </x:row>
     <x:row r="133">
-      <x:c r="G133" s="448"/>
-      <x:c r="H133" s="448"/>
-      <x:c r="I133" s="448"/>
-      <x:c r="J133" s="448"/>
+      <x:c r="G133"/>
+      <x:c r="H133"/>
+      <x:c r="I133"/>
+      <x:c r="J133"/>
       <x:c r="K133"/>
       <x:c r="L133"/>
       <x:c r="M133"/>
@@ -8658,28 +9916,34 @@
       <x:c r="AB133"/>
       <x:c r="AC133"/>
       <x:c r="AD133"/>
+      <x:c r="AE133"/>
+      <x:c r="AF133"/>
+      <x:c r="AG133"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="H1:L1"/>
-    <x:mergeCell ref="M1:Q1"/>
-    <x:mergeCell ref="R1:V1"/>
-    <x:mergeCell ref="X1:Y1"/>
-    <x:mergeCell ref="Z1:AA1"/>
+    <x:mergeCell ref="H1:M1"/>
+    <x:mergeCell ref="N1:S1"/>
+    <x:mergeCell ref="T1:Y1"/>
+    <x:mergeCell ref="AA1:AB1"/>
+    <x:mergeCell ref="AC1:AD1"/>
   </x:mergeCells>
-  <x:dataValidations count="4">
+  <x:dataValidations count="5">
     <x:dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="B3:B133">
       <x:formula1>INDIRECT("Strategy!$A$14:$A$17")</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="G3:G133">
       <x:formula1>"TRUE,FALSE"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="Y3:Y133">
+    <x:dataValidation type="list" sqref="AB3:AB133">
       <x:formula1>"General"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="AA3:AA133">
+    <x:dataValidation type="list" sqref="AD3:AD133">
       <x:formula1>"1,2,3,4,5"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="M3:M133 S3:S133 Y3:Y133">
+      <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8705,137 +9969,147 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="412" t="str">
+      <x:c r="A1" t="str" s="508">
         <x:v>Scoring</x:v>
       </x:c>
-      <x:c r="B1" s="412"/>
-      <x:c r="C1" s="412"/>
-      <x:c r="D1" s="412"/>
-      <x:c r="E1" s="390"/>
-      <x:c r="F1" s="390"/>
-      <x:c r="G1" s="390"/>
-      <x:c r="H1" s="390"/>
-      <x:c r="I1" s="390"/>
-      <x:c r="J1" s="390"/>
-      <x:c r="K1" s="390"/>
-      <x:c r="L1" s="390"/>
-      <x:c r="M1" s="390"/>
-      <x:c r="N1" s="390"/>
-      <x:c r="O1" s="390"/>
-      <x:c r="P1" s="390"/>
-      <x:c r="Q1" s="390"/>
-      <x:c r="R1" s="390"/>
-      <x:c r="S1"/>
+      <x:c r="B1" s="508"/>
+      <x:c r="C1" s="508"/>
+      <x:c r="D1" s="508"/>
+      <x:c r="E1" s="509"/>
+      <x:c r="F1" s="509"/>
+      <x:c r="G1" s="509"/>
+      <x:c r="H1" s="509"/>
+      <x:c r="I1" s="509"/>
+      <x:c r="J1" s="509"/>
+      <x:c r="K1" s="509"/>
+      <x:c r="L1" s="509"/>
+      <x:c r="M1" s="509"/>
+      <x:c r="N1" s="509"/>
+      <x:c r="O1" s="509"/>
+      <x:c r="P1" s="509"/>
+      <x:c r="Q1" s="509"/>
+      <x:c r="R1" s="509"/>
+      <x:c r="S1" s="510"/>
       <x:c r="T1"/>
     </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="390" t="str">
-        <x:v>Session summaries appear on the first row. Cal-Intervals exercises and timing are defined once in Library.</x:v>
+    <x:row r="2" ht="44" customHeight="1">
+      <x:c r="A2" t="str" s="511">
+        <x:v>Date</x:v>
       </x:c>
-      <x:c r="B2" s="390"/>
-      <x:c r="C2" s="390"/>
-      <x:c r="D2" s="390"/>
-      <x:c r="E2" s="390"/>
-      <x:c r="F2" s="390"/>
-      <x:c r="G2" s="390"/>
-      <x:c r="H2" s="390"/>
-      <x:c r="I2" s="390"/>
-      <x:c r="J2" s="390"/>
-      <x:c r="K2" s="390"/>
-      <x:c r="L2" s="390"/>
-      <x:c r="M2" s="390"/>
-      <x:c r="N2" s="390"/>
-      <x:c r="O2" s="390"/>
-      <x:c r="P2" s="390"/>
-      <x:c r="Q2" s="390"/>
-      <x:c r="R2" s="390"/>
-      <x:c r="S2" s="390"/>
+      <x:c r="B2" t="str" s="511">
+        <x:v>Session</x:v>
+      </x:c>
+      <x:c r="C2" t="str" s="511">
+        <x:v>Exercise</x:v>
+      </x:c>
+      <x:c r="D2" t="str" s="511">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="E2" t="str" s="511">
+        <x:v>Sets</x:v>
+      </x:c>
+      <x:c r="F2" t="str" s="511">
+        <x:v>Amount per set</x:v>
+      </x:c>
+      <x:c r="G2" t="str" s="511">
+        <x:v>Target</x:v>
+      </x:c>
+      <x:c r="H2" t="str" s="511">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="I2" t="str" s="511">
+        <x:v>Exercise performance (%)</x:v>
+      </x:c>
+      <x:c r="J2" t="str" s="511">
+        <x:v>Base intensity</x:v>
+      </x:c>
+      <x:c r="K2" t="str" s="511">
+        <x:v>Planned kg</x:v>
+      </x:c>
+      <x:c r="L2" t="str" s="511">
+        <x:v>Growth per kg</x:v>
+      </x:c>
+      <x:c r="M2" t="str" s="511">
+        <x:v>Loaded intensity</x:v>
+      </x:c>
+      <x:c r="N2" t="str" s="511">
+        <x:v>Volume weight</x:v>
+      </x:c>
+      <x:c r="O2" t="str" s="511">
+        <x:v>Contribution</x:v>
+      </x:c>
+      <x:c r="P2" t="str" s="511">
+        <x:v>Planned intensity</x:v>
+      </x:c>
+      <x:c r="Q2" t="str" s="511">
+        <x:v>Performance</x:v>
+      </x:c>
+      <x:c r="R2" t="str" s="511">
+        <x:v>Scored metrics</x:v>
+      </x:c>
+      <x:c r="S2" t="str" s="511">
+        <x:v>Planned metrics</x:v>
+      </x:c>
       <x:c r="T2"/>
       <x:c r="U2"/>
       <x:c r="V2"/>
       <x:c r="W2"/>
       <x:c r="X2"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="390"/>
-      <x:c r="B3" s="390"/>
-      <x:c r="C3" s="390"/>
-      <x:c r="D3" s="390"/>
-      <x:c r="E3" s="390"/>
-      <x:c r="F3" s="390"/>
-      <x:c r="G3" s="390"/>
-      <x:c r="H3" s="390"/>
-      <x:c r="I3" s="390"/>
-      <x:c r="J3" s="390"/>
-      <x:c r="K3" s="390"/>
-      <x:c r="L3" s="390"/>
-      <x:c r="M3" s="390"/>
-      <x:c r="N3" s="390"/>
-      <x:c r="O3" s="390"/>
-      <x:c r="P3" s="390"/>
-      <x:c r="Q3" s="390"/>
-      <x:c r="R3" s="390"/>
-      <x:c r="S3" s="390"/>
+      <x:c r="Y2"/>
+      <x:c r="Z2"/>
+      <x:c r="AA2"/>
+      <x:c r="AB2"/>
+    </x:row>
+    <x:row r="3" ht="38" hidden="0" customHeight="1">
+      <x:c r="A3" s="402"/>
+      <x:c r="B3" s="391"/>
+      <x:c r="C3" s="400"/>
+      <x:c r="D3" s="400"/>
+      <x:c r="E3" s="400"/>
+      <x:c r="F3" s="400"/>
+      <x:c r="G3" s="400"/>
+      <x:c r="H3" s="400"/>
+      <x:c r="I3" s="432"/>
+      <x:c r="J3" s="432"/>
+      <x:c r="K3" s="433"/>
+      <x:c r="L3" s="434"/>
+      <x:c r="M3" s="432"/>
+      <x:c r="N3" s="432"/>
+      <x:c r="O3" s="432"/>
+      <x:c r="P3" s="432"/>
+      <x:c r="Q3" s="432"/>
+      <x:c r="R3" s="400"/>
+      <x:c r="S3" s="400"/>
       <x:c r="T3"/>
-    </x:row>
-    <x:row r="4" ht="44" customHeight="1">
-      <x:c r="A4" s="415" t="str">
-        <x:v>Date</x:v>
-      </x:c>
-      <x:c r="B4" s="415" t="str">
-        <x:v>Session</x:v>
-      </x:c>
-      <x:c r="C4" s="415" t="str">
-        <x:v>Exercise</x:v>
-      </x:c>
-      <x:c r="D4" s="415" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="E4" s="415" t="str">
-        <x:v>Sets</x:v>
-      </x:c>
-      <x:c r="F4" s="415" t="str">
-        <x:v>Amount per set</x:v>
-      </x:c>
-      <x:c r="G4" s="415" t="str">
-        <x:v>Target</x:v>
-      </x:c>
-      <x:c r="H4" s="415" t="str">
-        <x:v>Result</x:v>
-      </x:c>
-      <x:c r="I4" s="415" t="str">
-        <x:v>Exercise performance (%)</x:v>
-      </x:c>
-      <x:c r="J4" s="415" t="str">
-        <x:v>Base intensity</x:v>
-      </x:c>
-      <x:c r="K4" s="415" t="str">
-        <x:v>Planned kg</x:v>
-      </x:c>
-      <x:c r="L4" s="415" t="str">
-        <x:v>Growth per kg</x:v>
-      </x:c>
-      <x:c r="M4" s="415" t="str">
-        <x:v>Loaded intensity</x:v>
-      </x:c>
-      <x:c r="N4" s="415" t="str">
-        <x:v>Volume weight</x:v>
-      </x:c>
-      <x:c r="O4" s="415" t="str">
-        <x:v>Contribution</x:v>
-      </x:c>
-      <x:c r="P4" s="415" t="str">
-        <x:v>Planned intensity</x:v>
-      </x:c>
-      <x:c r="Q4" s="415" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="R4" s="415" t="str">
-        <x:v>Scored metrics</x:v>
-      </x:c>
-      <x:c r="S4" s="415" t="str">
-        <x:v>Planned metrics</x:v>
-      </x:c>
+      <x:c r="U3"/>
+      <x:c r="V3"/>
+      <x:c r="W3"/>
+      <x:c r="X3"/>
+      <x:c r="Y3"/>
+      <x:c r="Z3"/>
+      <x:c r="AA3"/>
+      <x:c r="AB3"/>
+    </x:row>
+    <x:row r="4" ht="38" hidden="0" customHeight="1">
+      <x:c r="A4" s="402"/>
+      <x:c r="B4" s="391"/>
+      <x:c r="C4" s="400"/>
+      <x:c r="D4" s="400"/>
+      <x:c r="E4" s="400"/>
+      <x:c r="F4" s="400"/>
+      <x:c r="G4" s="400"/>
+      <x:c r="H4" s="400"/>
+      <x:c r="I4" s="432"/>
+      <x:c r="J4" s="432"/>
+      <x:c r="K4" s="433"/>
+      <x:c r="L4" s="434"/>
+      <x:c r="M4" s="432"/>
+      <x:c r="N4" s="432"/>
+      <x:c r="O4" s="432"/>
+      <x:c r="P4" s="432"/>
+      <x:c r="Q4" s="432"/>
+      <x:c r="R4" s="400"/>
+      <x:c r="S4" s="400"/>
       <x:c r="T4"/>
       <x:c r="U4"/>
       <x:c r="V4"/>
@@ -13826,26 +15100,26 @@
       <x:c r="AA170"/>
       <x:c r="AB170"/>
     </x:row>
-    <x:row r="171" ht="38" hidden="0" customHeight="1">
-      <x:c r="A171" s="402"/>
-      <x:c r="B171" s="391"/>
-      <x:c r="C171" s="400"/>
-      <x:c r="D171" s="400"/>
-      <x:c r="E171" s="400"/>
-      <x:c r="F171" s="400"/>
-      <x:c r="G171" s="400"/>
-      <x:c r="H171" s="400"/>
-      <x:c r="I171" s="432"/>
-      <x:c r="J171" s="432"/>
-      <x:c r="K171" s="433"/>
-      <x:c r="L171" s="434"/>
-      <x:c r="M171" s="432"/>
-      <x:c r="N171" s="432"/>
-      <x:c r="O171" s="432"/>
-      <x:c r="P171" s="432"/>
-      <x:c r="Q171" s="432"/>
-      <x:c r="R171" s="400"/>
-      <x:c r="S171" s="400"/>
+    <x:row r="171" ht="36" hidden="0" customHeight="1">
+      <x:c r="A171"/>
+      <x:c r="B171"/>
+      <x:c r="C171"/>
+      <x:c r="D171"/>
+      <x:c r="E171"/>
+      <x:c r="F171"/>
+      <x:c r="G171"/>
+      <x:c r="H171"/>
+      <x:c r="I171"/>
+      <x:c r="J171"/>
+      <x:c r="K171"/>
+      <x:c r="L171"/>
+      <x:c r="M171"/>
+      <x:c r="N171"/>
+      <x:c r="O171"/>
+      <x:c r="P171"/>
+      <x:c r="Q171"/>
+      <x:c r="R171"/>
+      <x:c r="S171"/>
       <x:c r="T171"/>
       <x:c r="U171"/>
       <x:c r="V171"/>
@@ -13856,26 +15130,26 @@
       <x:c r="AA171"/>
       <x:c r="AB171"/>
     </x:row>
-    <x:row r="172" ht="38" hidden="0" customHeight="1">
-      <x:c r="A172" s="402"/>
-      <x:c r="B172" s="391"/>
-      <x:c r="C172" s="400"/>
-      <x:c r="D172" s="400"/>
-      <x:c r="E172" s="400"/>
-      <x:c r="F172" s="400"/>
-      <x:c r="G172" s="400"/>
-      <x:c r="H172" s="400"/>
-      <x:c r="I172" s="432"/>
-      <x:c r="J172" s="432"/>
-      <x:c r="K172" s="433"/>
-      <x:c r="L172" s="434"/>
-      <x:c r="M172" s="432"/>
-      <x:c r="N172" s="432"/>
-      <x:c r="O172" s="432"/>
-      <x:c r="P172" s="432"/>
-      <x:c r="Q172" s="432"/>
-      <x:c r="R172" s="400"/>
-      <x:c r="S172" s="400"/>
+    <x:row r="172" ht="36" hidden="0" customHeight="1">
+      <x:c r="A172"/>
+      <x:c r="B172"/>
+      <x:c r="C172"/>
+      <x:c r="D172"/>
+      <x:c r="E172"/>
+      <x:c r="F172"/>
+      <x:c r="G172"/>
+      <x:c r="H172"/>
+      <x:c r="I172"/>
+      <x:c r="J172"/>
+      <x:c r="K172"/>
+      <x:c r="L172"/>
+      <x:c r="M172"/>
+      <x:c r="N172"/>
+      <x:c r="O172"/>
+      <x:c r="P172"/>
+      <x:c r="Q172"/>
+      <x:c r="R172"/>
+      <x:c r="S172"/>
       <x:c r="T172"/>
       <x:c r="U172"/>
       <x:c r="V172"/>
@@ -13886,10 +15160,12 @@
       <x:c r="AA172"/>
       <x:c r="AB172"/>
     </x:row>
-    <x:row r="173" ht="36" hidden="0" customHeight="1">
-      <x:c r="A173"/>
-      <x:c r="B173"/>
-      <x:c r="C173"/>
+    <x:row r="173" ht="28" hidden="0" customHeight="1">
+      <x:c r="A173" t="str" s="512">
+        <x:v>Assumptions</x:v>
+      </x:c>
+      <x:c r="B173" s="512"/>
+      <x:c r="C173" s="512"/>
       <x:c r="D173"/>
       <x:c r="E173"/>
       <x:c r="F173"/>
@@ -13916,10 +15192,16 @@
       <x:c r="AA173"/>
       <x:c r="AB173"/>
     </x:row>
-    <x:row r="174" ht="36" hidden="0" customHeight="1">
-      <x:c r="A174"/>
-      <x:c r="B174"/>
-      <x:c r="C174"/>
+    <x:row r="174" ht="28" hidden="0" customHeight="1">
+      <x:c r="A174" t="str" s="513">
+        <x:v>Setting</x:v>
+      </x:c>
+      <x:c r="B174" t="str" s="513">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C174" t="str" s="513">
+        <x:v>Unit</x:v>
+      </x:c>
       <x:c r="D174"/>
       <x:c r="E174"/>
       <x:c r="F174"/>
@@ -13947,11 +15229,15 @@
       <x:c r="AB174"/>
     </x:row>
     <x:row r="175" ht="28" hidden="0" customHeight="1">
-      <x:c r="A175" s="436" t="str">
-        <x:v>Assumptions</x:v>
+      <x:c r="A175" s="391" t="str">
+        <x:v>Timed work</x:v>
       </x:c>
-      <x:c r="B175" s="436"/>
-      <x:c r="C175" s="436"/>
+      <x:c r="B175" s="440" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C175" s="391" t="str">
+        <x:v>seconds per rep</x:v>
+      </x:c>
       <x:c r="D175"/>
       <x:c r="E175"/>
       <x:c r="F175"/>
@@ -13978,16 +15264,10 @@
       <x:c r="AA175"/>
       <x:c r="AB175"/>
     </x:row>
-    <x:row r="176" ht="28" hidden="0" customHeight="1">
-      <x:c r="A176" s="438" t="str">
-        <x:v>Setting</x:v>
-      </x:c>
-      <x:c r="B176" s="438" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="C176" s="438" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
+    <x:row r="176" ht="36" hidden="0" customHeight="1">
+      <x:c r="A176"/>
+      <x:c r="B176"/>
+      <x:c r="C176"/>
       <x:c r="D176"/>
       <x:c r="E176"/>
       <x:c r="F176"/>
@@ -14014,16 +15294,10 @@
       <x:c r="AA176"/>
       <x:c r="AB176"/>
     </x:row>
-    <x:row r="177" ht="28" hidden="0" customHeight="1">
-      <x:c r="A177" s="391" t="str">
-        <x:v>Timed work</x:v>
-      </x:c>
-      <x:c r="B177" s="440" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C177" s="391" t="str">
-        <x:v>seconds per rep</x:v>
-      </x:c>
+    <x:row r="177" ht="36" hidden="0" customHeight="1">
+      <x:c r="A177"/>
+      <x:c r="B177"/>
+      <x:c r="C177"/>
       <x:c r="D177"/>
       <x:c r="E177"/>
       <x:c r="F177"/>
@@ -16000,7 +17274,7 @@
       <x:c r="AA242"/>
       <x:c r="AB242"/>
     </x:row>
-    <x:row r="243" ht="36" hidden="0" customHeight="1">
+    <x:row r="243" ht="36" customHeight="1">
       <x:c r="A243"/>
       <x:c r="B243"/>
       <x:c r="C243"/>
@@ -16021,16 +17295,8 @@
       <x:c r="R243"/>
       <x:c r="S243"/>
       <x:c r="T243"/>
-      <x:c r="U243"/>
-      <x:c r="V243"/>
-      <x:c r="W243"/>
-      <x:c r="X243"/>
-      <x:c r="Y243"/>
-      <x:c r="Z243"/>
-      <x:c r="AA243"/>
-      <x:c r="AB243"/>
-    </x:row>
-    <x:row r="244" ht="36" hidden="0" customHeight="1">
+    </x:row>
+    <x:row r="244" ht="36" customHeight="1">
       <x:c r="A244"/>
       <x:c r="B244"/>
       <x:c r="C244"/>
@@ -16051,14 +17317,6 @@
       <x:c r="R244"/>
       <x:c r="S244"/>
       <x:c r="T244"/>
-      <x:c r="U244"/>
-      <x:c r="V244"/>
-      <x:c r="W244"/>
-      <x:c r="X244"/>
-      <x:c r="Y244"/>
-      <x:c r="Z244"/>
-      <x:c r="AA244"/>
-      <x:c r="AB244"/>
     </x:row>
     <x:row r="245" ht="36" customHeight="1">
       <x:c r="A245"/>
@@ -16368,7 +17626,7 @@
       <x:c r="S258"/>
       <x:c r="T258"/>
     </x:row>
-    <x:row r="259" ht="36" customHeight="1">
+    <x:row r="259">
       <x:c r="A259"/>
       <x:c r="B259"/>
       <x:c r="C259"/>
@@ -16390,7 +17648,7 @@
       <x:c r="S259"/>
       <x:c r="T259"/>
     </x:row>
-    <x:row r="260" ht="36" customHeight="1">
+    <x:row r="260">
       <x:c r="A260"/>
       <x:c r="B260"/>
       <x:c r="C260"/>
@@ -17248,62 +18506,13 @@
       <x:c r="S298"/>
       <x:c r="T298"/>
     </x:row>
-    <x:row r="299">
-      <x:c r="A299"/>
-      <x:c r="B299"/>
-      <x:c r="C299"/>
-      <x:c r="D299"/>
-      <x:c r="E299"/>
-      <x:c r="F299"/>
-      <x:c r="G299"/>
-      <x:c r="H299"/>
-      <x:c r="I299"/>
-      <x:c r="J299"/>
-      <x:c r="K299"/>
-      <x:c r="L299"/>
-      <x:c r="M299"/>
-      <x:c r="N299"/>
-      <x:c r="O299"/>
-      <x:c r="P299"/>
-      <x:c r="Q299"/>
-      <x:c r="R299"/>
-      <x:c r="S299"/>
-      <x:c r="T299"/>
-    </x:row>
-    <x:row r="300">
-      <x:c r="A300"/>
-      <x:c r="B300"/>
-      <x:c r="C300"/>
-      <x:c r="D300"/>
-      <x:c r="E300"/>
-      <x:c r="F300"/>
-      <x:c r="G300"/>
-      <x:c r="H300"/>
-      <x:c r="I300"/>
-      <x:c r="J300"/>
-      <x:c r="K300"/>
-      <x:c r="L300"/>
-      <x:c r="M300"/>
-      <x:c r="N300"/>
-      <x:c r="O300"/>
-      <x:c r="P300"/>
-      <x:c r="Q300"/>
-      <x:c r="R300"/>
-      <x:c r="S300"/>
-      <x:c r="T300"/>
-    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A175:C175"/>
+    <x:mergeCell ref="A173:C173"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="X5:X244">
-    <x:cfRule type="expression" dxfId="9" priority="1">
-      <x:formula>NOT(ISNUMBER(X5))</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="decimal" operator="greaterThan" sqref="B177">
+    <x:dataValidation type="decimal" operator="greaterThan" sqref="B175">
       <x:formula1>0</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -17321,427 +18530,427 @@
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="43" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
     <x:col min="5" max="6" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="394" t="str">
+      <x:c r="A1" t="str" s="497">
         <x:v>Exercise arsenal</x:v>
       </x:c>
-      <x:c r="B1" s="394"/>
-      <x:c r="C1" s="394"/>
-      <x:c r="D1" s="394"/>
-      <x:c r="E1" s="394"/>
+      <x:c r="B1" s="497"/>
+      <x:c r="C1" s="497"/>
+      <x:c r="D1" s="497"/>
+      <x:c r="E1" s="497"/>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
-      <x:c r="A2" s="397" t="str">
+      <x:c r="A2" t="str" s="498">
         <x:v>Group</x:v>
       </x:c>
-      <x:c r="B2" s="397" t="str">
+      <x:c r="B2" t="str" s="498">
         <x:v>Exercise</x:v>
       </x:c>
-      <x:c r="C2" s="397" t="str">
+      <x:c r="C2" t="str" s="498">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="D2" t="str" s="498">
         <x:v>Base intensity (0–10)</x:v>
       </x:c>
-      <x:c r="D2" s="397" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="E2" s="397" t="str">
+      <x:c r="E2" t="str" s="498">
         <x:v>Growth per kg</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="391"/>
       <x:c r="B3" s="400"/>
-      <x:c r="C3" s="398"/>
-      <x:c r="D3" s="391"/>
+      <x:c r="C3" s="391"/>
+      <x:c r="D3" s="398"/>
       <x:c r="E3" s="399"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="391"/>
       <x:c r="B4" s="400"/>
-      <x:c r="C4" s="398"/>
-      <x:c r="D4" s="391"/>
+      <x:c r="C4" s="391"/>
+      <x:c r="D4" s="398"/>
       <x:c r="E4" s="399"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="391"/>
       <x:c r="B5" s="400"/>
-      <x:c r="C5" s="398"/>
-      <x:c r="D5" s="391"/>
+      <x:c r="C5" s="391"/>
+      <x:c r="D5" s="398"/>
       <x:c r="E5" s="399"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="391"/>
       <x:c r="B6" s="400"/>
-      <x:c r="C6" s="398"/>
-      <x:c r="D6" s="391"/>
+      <x:c r="C6" s="391"/>
+      <x:c r="D6" s="398"/>
       <x:c r="E6" s="399"/>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="391"/>
       <x:c r="B7" s="400"/>
-      <x:c r="C7" s="398"/>
-      <x:c r="D7" s="391"/>
+      <x:c r="C7" s="391"/>
+      <x:c r="D7" s="398"/>
       <x:c r="E7" s="399"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="391"/>
       <x:c r="B8" s="400"/>
-      <x:c r="C8" s="398"/>
-      <x:c r="D8" s="391"/>
+      <x:c r="C8" s="391"/>
+      <x:c r="D8" s="398"/>
       <x:c r="E8" s="399"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="391"/>
       <x:c r="B9" s="400"/>
-      <x:c r="C9" s="398"/>
-      <x:c r="D9" s="391"/>
+      <x:c r="C9" s="391"/>
+      <x:c r="D9" s="398"/>
       <x:c r="E9" s="399"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="391"/>
       <x:c r="B10" s="400"/>
-      <x:c r="C10" s="398"/>
-      <x:c r="D10" s="391"/>
+      <x:c r="C10" s="391"/>
+      <x:c r="D10" s="398"/>
       <x:c r="E10" s="399"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="391"/>
       <x:c r="B11" s="400"/>
-      <x:c r="C11" s="398"/>
-      <x:c r="D11" s="391"/>
+      <x:c r="C11" s="391"/>
+      <x:c r="D11" s="398"/>
       <x:c r="E11" s="399"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="391"/>
       <x:c r="B12" s="400"/>
-      <x:c r="C12" s="398"/>
-      <x:c r="D12" s="391"/>
+      <x:c r="C12" s="391"/>
+      <x:c r="D12" s="398"/>
       <x:c r="E12" s="399"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="391"/>
       <x:c r="B13" s="400"/>
-      <x:c r="C13" s="398"/>
-      <x:c r="D13" s="391"/>
+      <x:c r="C13" s="391"/>
+      <x:c r="D13" s="398"/>
       <x:c r="E13" s="399"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="391"/>
       <x:c r="B14" s="400"/>
-      <x:c r="C14" s="398"/>
-      <x:c r="D14" s="391"/>
+      <x:c r="C14" s="391"/>
+      <x:c r="D14" s="398"/>
       <x:c r="E14" s="399"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="391"/>
       <x:c r="B15" s="400"/>
-      <x:c r="C15" s="398"/>
-      <x:c r="D15" s="391"/>
+      <x:c r="C15" s="391"/>
+      <x:c r="D15" s="398"/>
       <x:c r="E15" s="399"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="391"/>
       <x:c r="B16" s="400"/>
-      <x:c r="C16" s="398"/>
-      <x:c r="D16" s="391"/>
+      <x:c r="C16" s="391"/>
+      <x:c r="D16" s="398"/>
       <x:c r="E16" s="399"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="391"/>
       <x:c r="B17" s="400"/>
-      <x:c r="C17" s="398"/>
-      <x:c r="D17" s="391"/>
+      <x:c r="C17" s="391"/>
+      <x:c r="D17" s="398"/>
       <x:c r="E17" s="399"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
       <x:c r="A18" s="391"/>
       <x:c r="B18" s="400"/>
-      <x:c r="C18" s="398"/>
-      <x:c r="D18" s="391"/>
+      <x:c r="C18" s="391"/>
+      <x:c r="D18" s="398"/>
       <x:c r="E18" s="399"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="391"/>
       <x:c r="B19" s="400"/>
-      <x:c r="C19" s="398"/>
-      <x:c r="D19" s="391"/>
+      <x:c r="C19" s="391"/>
+      <x:c r="D19" s="398"/>
       <x:c r="E19" s="399"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
       <x:c r="A20" s="391"/>
       <x:c r="B20" s="400"/>
-      <x:c r="C20" s="398"/>
-      <x:c r="D20" s="391"/>
+      <x:c r="C20" s="391"/>
+      <x:c r="D20" s="398"/>
       <x:c r="E20" s="399"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="391"/>
       <x:c r="B21" s="400"/>
-      <x:c r="C21" s="398"/>
-      <x:c r="D21" s="391"/>
+      <x:c r="C21" s="391"/>
+      <x:c r="D21" s="398"/>
       <x:c r="E21" s="399"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="391"/>
       <x:c r="B22" s="400"/>
-      <x:c r="C22" s="398"/>
-      <x:c r="D22" s="391"/>
+      <x:c r="C22" s="391"/>
+      <x:c r="D22" s="398"/>
       <x:c r="E22" s="399"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
       <x:c r="A23" s="391"/>
       <x:c r="B23" s="400"/>
-      <x:c r="C23" s="398"/>
-      <x:c r="D23" s="391"/>
+      <x:c r="C23" s="391"/>
+      <x:c r="D23" s="398"/>
       <x:c r="E23" s="399"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
       <x:c r="A24" s="391"/>
       <x:c r="B24" s="400"/>
-      <x:c r="C24" s="398"/>
-      <x:c r="D24" s="391"/>
+      <x:c r="C24" s="391"/>
+      <x:c r="D24" s="398"/>
       <x:c r="E24" s="399"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="391"/>
       <x:c r="B25" s="400"/>
-      <x:c r="C25" s="398"/>
-      <x:c r="D25" s="391"/>
+      <x:c r="C25" s="391"/>
+      <x:c r="D25" s="398"/>
       <x:c r="E25" s="399"/>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
       <x:c r="A26" s="391"/>
       <x:c r="B26" s="400"/>
-      <x:c r="C26" s="398"/>
-      <x:c r="D26" s="391"/>
+      <x:c r="C26" s="391"/>
+      <x:c r="D26" s="398"/>
       <x:c r="E26" s="399"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
       <x:c r="A27" s="391"/>
       <x:c r="B27" s="400"/>
-      <x:c r="C27" s="398"/>
-      <x:c r="D27" s="391"/>
+      <x:c r="C27" s="391"/>
+      <x:c r="D27" s="398"/>
       <x:c r="E27" s="399"/>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
       <x:c r="A28" s="391"/>
       <x:c r="B28" s="400"/>
-      <x:c r="C28" s="398"/>
-      <x:c r="D28" s="391"/>
+      <x:c r="C28" s="391"/>
+      <x:c r="D28" s="398"/>
       <x:c r="E28" s="399"/>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
       <x:c r="A29" s="391"/>
       <x:c r="B29" s="400"/>
-      <x:c r="C29" s="398"/>
-      <x:c r="D29" s="391"/>
+      <x:c r="C29" s="391"/>
+      <x:c r="D29" s="398"/>
       <x:c r="E29" s="399"/>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
       <x:c r="A30" s="391"/>
       <x:c r="B30" s="400"/>
-      <x:c r="C30" s="398"/>
-      <x:c r="D30" s="391"/>
+      <x:c r="C30" s="391"/>
+      <x:c r="D30" s="398"/>
       <x:c r="E30" s="399"/>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
       <x:c r="A31" s="391"/>
       <x:c r="B31" s="400"/>
-      <x:c r="C31" s="398"/>
-      <x:c r="D31" s="391"/>
+      <x:c r="C31" s="391"/>
+      <x:c r="D31" s="398"/>
       <x:c r="E31" s="399"/>
     </x:row>
     <x:row r="32" ht="30" customHeight="1">
       <x:c r="A32" s="391"/>
       <x:c r="B32" s="400"/>
-      <x:c r="C32" s="398"/>
-      <x:c r="D32" s="391"/>
+      <x:c r="C32" s="391"/>
+      <x:c r="D32" s="398"/>
       <x:c r="E32" s="399"/>
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
       <x:c r="A33" s="391"/>
       <x:c r="B33" s="400"/>
-      <x:c r="C33" s="398"/>
-      <x:c r="D33" s="391"/>
+      <x:c r="C33" s="391"/>
+      <x:c r="D33" s="398"/>
       <x:c r="E33" s="399"/>
     </x:row>
     <x:row r="34" ht="30" customHeight="1">
       <x:c r="A34" s="391"/>
       <x:c r="B34" s="400"/>
-      <x:c r="C34" s="398"/>
-      <x:c r="D34" s="391"/>
+      <x:c r="C34" s="391"/>
+      <x:c r="D34" s="398"/>
       <x:c r="E34" s="399"/>
     </x:row>
     <x:row r="35" ht="30" customHeight="1">
       <x:c r="A35" s="391"/>
       <x:c r="B35" s="400"/>
-      <x:c r="C35" s="398"/>
-      <x:c r="D35" s="391"/>
+      <x:c r="C35" s="391"/>
+      <x:c r="D35" s="398"/>
       <x:c r="E35" s="399"/>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
       <x:c r="A36" s="391"/>
       <x:c r="B36" s="400"/>
-      <x:c r="C36" s="398"/>
-      <x:c r="D36" s="391"/>
+      <x:c r="C36" s="391"/>
+      <x:c r="D36" s="398"/>
       <x:c r="E36" s="399"/>
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
       <x:c r="A37" s="391"/>
       <x:c r="B37" s="400"/>
-      <x:c r="C37" s="398"/>
-      <x:c r="D37" s="391"/>
+      <x:c r="C37" s="391"/>
+      <x:c r="D37" s="398"/>
       <x:c r="E37" s="399"/>
     </x:row>
     <x:row r="38" ht="30" customHeight="1">
       <x:c r="A38" s="391"/>
       <x:c r="B38" s="400"/>
-      <x:c r="C38" s="398"/>
-      <x:c r="D38" s="391"/>
+      <x:c r="C38" s="391"/>
+      <x:c r="D38" s="398"/>
       <x:c r="E38" s="399"/>
     </x:row>
     <x:row r="39" ht="30" customHeight="1">
       <x:c r="A39" s="391"/>
       <x:c r="B39" s="400"/>
-      <x:c r="C39" s="398"/>
-      <x:c r="D39" s="391"/>
+      <x:c r="C39" s="391"/>
+      <x:c r="D39" s="398"/>
       <x:c r="E39" s="399"/>
     </x:row>
     <x:row r="40" ht="30" customHeight="1">
       <x:c r="A40" s="391"/>
       <x:c r="B40" s="400"/>
-      <x:c r="C40" s="398"/>
-      <x:c r="D40" s="391"/>
+      <x:c r="C40" s="391"/>
+      <x:c r="D40" s="398"/>
       <x:c r="E40" s="399"/>
     </x:row>
     <x:row r="41" ht="30" customHeight="1">
       <x:c r="A41" s="391"/>
       <x:c r="B41" s="400"/>
-      <x:c r="C41" s="398"/>
-      <x:c r="D41" s="391"/>
+      <x:c r="C41" s="391"/>
+      <x:c r="D41" s="398"/>
       <x:c r="E41" s="399"/>
     </x:row>
     <x:row r="42" ht="30" customHeight="1">
       <x:c r="A42" s="391"/>
       <x:c r="B42" s="400"/>
-      <x:c r="C42" s="398"/>
-      <x:c r="D42" s="391"/>
+      <x:c r="C42" s="391"/>
+      <x:c r="D42" s="398"/>
       <x:c r="E42" s="399"/>
     </x:row>
     <x:row r="43" ht="30" customHeight="1">
       <x:c r="A43" s="391"/>
       <x:c r="B43" s="400"/>
-      <x:c r="C43" s="398"/>
-      <x:c r="D43" s="391"/>
+      <x:c r="C43" s="391"/>
+      <x:c r="D43" s="398"/>
       <x:c r="E43" s="399"/>
     </x:row>
     <x:row r="44" ht="30" customHeight="1">
       <x:c r="A44" s="391"/>
       <x:c r="B44" s="400"/>
-      <x:c r="C44" s="398"/>
-      <x:c r="D44" s="391"/>
+      <x:c r="C44" s="391"/>
+      <x:c r="D44" s="398"/>
       <x:c r="E44" s="399"/>
     </x:row>
     <x:row r="45" ht="30" customHeight="1">
       <x:c r="A45" s="391"/>
       <x:c r="B45" s="400"/>
-      <x:c r="C45" s="398"/>
-      <x:c r="D45" s="391"/>
+      <x:c r="C45" s="391"/>
+      <x:c r="D45" s="398"/>
       <x:c r="E45" s="399"/>
     </x:row>
     <x:row r="46" ht="30" customHeight="1">
       <x:c r="A46" s="391"/>
       <x:c r="B46" s="400"/>
-      <x:c r="C46" s="398"/>
-      <x:c r="D46" s="391"/>
+      <x:c r="C46" s="391"/>
+      <x:c r="D46" s="398"/>
       <x:c r="E46" s="399"/>
     </x:row>
     <x:row r="47" ht="30" customHeight="1">
       <x:c r="A47" s="391"/>
       <x:c r="B47" s="400"/>
-      <x:c r="C47" s="398"/>
-      <x:c r="D47" s="391"/>
+      <x:c r="C47" s="391"/>
+      <x:c r="D47" s="398"/>
       <x:c r="E47" s="399"/>
     </x:row>
     <x:row r="48" ht="30" customHeight="1">
       <x:c r="A48" s="391"/>
       <x:c r="B48" s="400"/>
-      <x:c r="C48" s="398"/>
-      <x:c r="D48" s="391"/>
+      <x:c r="C48" s="391"/>
+      <x:c r="D48" s="398"/>
       <x:c r="E48" s="399"/>
     </x:row>
     <x:row r="49" ht="30" customHeight="1">
       <x:c r="A49" s="391"/>
       <x:c r="B49" s="400"/>
-      <x:c r="C49" s="398"/>
-      <x:c r="D49" s="391"/>
+      <x:c r="C49" s="391"/>
+      <x:c r="D49" s="398"/>
       <x:c r="E49" s="399"/>
     </x:row>
     <x:row r="50" ht="30" customHeight="1">
       <x:c r="A50" s="391"/>
       <x:c r="B50" s="400"/>
-      <x:c r="C50" s="398"/>
-      <x:c r="D50" s="391"/>
+      <x:c r="C50" s="391"/>
+      <x:c r="D50" s="398"/>
       <x:c r="E50" s="399"/>
     </x:row>
     <x:row r="51" ht="30" customHeight="1">
       <x:c r="A51" s="391"/>
       <x:c r="B51" s="400"/>
-      <x:c r="C51" s="398"/>
-      <x:c r="D51" s="391"/>
+      <x:c r="C51" s="391"/>
+      <x:c r="D51" s="398"/>
       <x:c r="E51" s="399"/>
     </x:row>
     <x:row r="52" ht="30" customHeight="1">
       <x:c r="A52" s="391"/>
       <x:c r="B52" s="400"/>
-      <x:c r="C52" s="398"/>
-      <x:c r="D52" s="391"/>
+      <x:c r="C52" s="391"/>
+      <x:c r="D52" s="398"/>
       <x:c r="E52" s="399"/>
     </x:row>
     <x:row r="53" ht="30" customHeight="1">
       <x:c r="A53" s="391"/>
       <x:c r="B53" s="400"/>
-      <x:c r="C53" s="398"/>
-      <x:c r="D53" s="391"/>
+      <x:c r="C53" s="391"/>
+      <x:c r="D53" s="398"/>
       <x:c r="E53" s="399"/>
     </x:row>
     <x:row r="54" ht="30" customHeight="1">
       <x:c r="A54" s="391"/>
       <x:c r="B54" s="400"/>
-      <x:c r="C54" s="398"/>
-      <x:c r="D54" s="391"/>
+      <x:c r="C54" s="391"/>
+      <x:c r="D54" s="398"/>
       <x:c r="E54" s="399"/>
     </x:row>
     <x:row r="55" ht="30" customHeight="1">
       <x:c r="A55" s="391"/>
       <x:c r="B55" s="400"/>
-      <x:c r="C55" s="398"/>
-      <x:c r="D55" s="391"/>
+      <x:c r="C55" s="391"/>
+      <x:c r="D55" s="398"/>
       <x:c r="E55" s="399"/>
     </x:row>
     <x:row r="56" ht="30" customHeight="1">
       <x:c r="A56" s="391"/>
       <x:c r="B56" s="400"/>
-      <x:c r="C56" s="398"/>
-      <x:c r="D56" s="391"/>
+      <x:c r="C56" s="391"/>
+      <x:c r="D56" s="398"/>
       <x:c r="E56" s="399"/>
     </x:row>
     <x:row r="57" ht="30" customHeight="1">
       <x:c r="A57" s="391"/>
       <x:c r="B57" s="400"/>
-      <x:c r="C57" s="398"/>
-      <x:c r="D57" s="391"/>
+      <x:c r="C57" s="391"/>
+      <x:c r="D57" s="398"/>
       <x:c r="E57" s="399"/>
     </x:row>
     <x:row r="58" ht="30" customHeight="1">
       <x:c r="A58" s="391"/>
       <x:c r="B58" s="400"/>
-      <x:c r="C58" s="398"/>
-      <x:c r="D58" s="391"/>
+      <x:c r="C58" s="391"/>
+      <x:c r="D58" s="398"/>
       <x:c r="E58" s="399"/>
     </x:row>
     <x:row r="59" ht="30" customHeight="1">
@@ -17752,28 +18961,28 @@
       <x:c r="E59"/>
     </x:row>
     <x:row r="60" ht="26" customHeight="1">
-      <x:c r="A60" s="394" t="str">
+      <x:c r="A60" t="str" s="497">
         <x:v>Equipment</x:v>
       </x:c>
-      <x:c r="B60" s="394"/>
-      <x:c r="C60" s="394"/>
-      <x:c r="D60" s="394"/>
-      <x:c r="E60" s="394"/>
+      <x:c r="B60" s="497"/>
+      <x:c r="C60" s="497"/>
+      <x:c r="D60" s="497"/>
+      <x:c r="E60" s="497"/>
     </x:row>
     <x:row r="61" ht="26" customHeight="1">
-      <x:c r="A61" s="397" t="str">
+      <x:c r="A61" t="str" s="498">
         <x:v>Equipment</x:v>
       </x:c>
-      <x:c r="B61" s="397" t="str">
+      <x:c r="B61" t="str" s="498">
         <x:v>Min kg</x:v>
       </x:c>
-      <x:c r="C61" s="397" t="str">
+      <x:c r="C61" t="str" s="498">
         <x:v>Max kg</x:v>
       </x:c>
-      <x:c r="D61" s="397" t="str">
+      <x:c r="D61" t="str" s="498">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="E61" s="391"/>
+      <x:c r="E61" s="514"/>
     </x:row>
     <x:row r="62" ht="44" customHeight="1">
       <x:c r="A62" s="391"/>
@@ -17783,32 +18992,32 @@
       <x:c r="E62" s="391"/>
     </x:row>
     <x:row r="65" ht="30" customHeight="1">
-      <x:c r="A65" s="425" t="str">
+      <x:c r="A65" t="str" s="515">
         <x:v>Cal-Intervals</x:v>
       </x:c>
-      <x:c r="B65" s="425"/>
-      <x:c r="C65" s="425"/>
-      <x:c r="D65" s="425"/>
-      <x:c r="E65" s="425"/>
-      <x:c r="F65" s="425"/>
+      <x:c r="B65" s="515"/>
+      <x:c r="C65" s="515"/>
+      <x:c r="D65" s="515"/>
+      <x:c r="E65" s="515"/>
+      <x:c r="F65" s="515"/>
     </x:row>
     <x:row r="66" ht="38" customHeight="1">
-      <x:c r="A66" s="428" t="str">
+      <x:c r="A66" t="str" s="516">
         <x:v>Exercise</x:v>
       </x:c>
-      <x:c r="B66" s="428" t="str">
+      <x:c r="B66" t="str" s="516">
         <x:v>Work seconds</x:v>
       </x:c>
-      <x:c r="C66" s="428" t="str">
+      <x:c r="C66" t="str" s="516">
         <x:v>Rest seconds</x:v>
       </x:c>
-      <x:c r="D66" s="428" t="str">
+      <x:c r="D66" t="str" s="516">
         <x:v>Base intensity</x:v>
       </x:c>
-      <x:c r="E66" s="428" t="str">
+      <x:c r="E66" t="str" s="516">
         <x:v>Volume weight</x:v>
       </x:c>
-      <x:c r="F66" s="428" t="str">
+      <x:c r="F66" t="str" s="516">
         <x:v>Contribution</x:v>
       </x:c>
     </x:row>
@@ -17852,7 +19061,7 @@
     <x:mergeCell ref="A65:F65"/>
   </x:mergeCells>
   <x:dataValidations count="2">
-    <x:dataValidation type="decimal" operator="between" sqref="C3:C58">
+    <x:dataValidation type="decimal" operator="between" sqref="D3:D58">
       <x:formula1>0</x:formula1>
       <x:formula2>10</x:formula2>
     </x:dataValidation>
@@ -17865,123 +19074,4 @@
     <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reea8b4a3c543488d"/>
   </x:tableParts>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
-    <x:col min="5" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="394" t="str">
-        <x:v>Added load</x:v>
-      </x:c>
-      <x:c r="B1" s="394"/>
-      <x:c r="C1" s="394"/>
-      <x:c r="D1" s="394"/>
-      <x:c r="E1" s="394"/>
-      <x:c r="F1" s="394"/>
-      <x:c r="G1" s="394"/>
-    </x:row>
-    <x:row r="2" ht="32" customHeight="1">
-      <x:c r="A2" s="397" t="str">
-        <x:v>Date</x:v>
-      </x:c>
-      <x:c r="B2" s="397" t="str">
-        <x:v>Session</x:v>
-      </x:c>
-      <x:c r="C2" s="397" t="str">
-        <x:v>Exercise</x:v>
-      </x:c>
-      <x:c r="D2" s="397" t="str">
-        <x:v>Equipment</x:v>
-      </x:c>
-      <x:c r="E2" s="397" t="str">
-        <x:v>Planned kg</x:v>
-      </x:c>
-      <x:c r="F2" s="397" t="str">
-        <x:v>Actual kg</x:v>
-      </x:c>
-      <x:c r="G2" s="397" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="46" customHeight="1">
-      <x:c r="A3" s="402"/>
-      <x:c r="B3" s="391"/>
-      <x:c r="C3" s="398"/>
-      <x:c r="D3" s="398"/>
-      <x:c r="E3" s="403"/>
-      <x:c r="F3" s="403"/>
-      <x:c r="G3" s="401"/>
-    </x:row>
-    <x:row r="4" ht="46" customHeight="1">
-      <x:c r="A4" s="402"/>
-      <x:c r="B4" s="391"/>
-      <x:c r="C4" s="398"/>
-      <x:c r="D4" s="398"/>
-      <x:c r="E4" s="403"/>
-      <x:c r="F4" s="403"/>
-      <x:c r="G4" s="401"/>
-    </x:row>
-    <x:row r="5" ht="46" customHeight="1">
-      <x:c r="A5" s="402"/>
-      <x:c r="B5" s="391"/>
-      <x:c r="C5" s="398"/>
-      <x:c r="D5" s="398"/>
-      <x:c r="E5" s="403"/>
-      <x:c r="F5" s="403"/>
-      <x:c r="G5" s="401"/>
-    </x:row>
-    <x:row r="6" ht="46" customHeight="1">
-      <x:c r="A6" s="402"/>
-      <x:c r="B6" s="391"/>
-      <x:c r="C6" s="398"/>
-      <x:c r="D6" s="398"/>
-      <x:c r="E6" s="403"/>
-      <x:c r="F6" s="403"/>
-      <x:c r="G6" s="401"/>
-    </x:row>
-    <x:row r="7" ht="46" customHeight="1">
-      <x:c r="A7" s="402"/>
-      <x:c r="B7" s="391"/>
-      <x:c r="C7" s="398"/>
-      <x:c r="D7" s="398"/>
-      <x:c r="E7" s="403"/>
-      <x:c r="F7" s="403"/>
-      <x:c r="G7" s="401"/>
-    </x:row>
-    <x:row r="8" ht="46" customHeight="1">
-      <x:c r="A8" s="402"/>
-      <x:c r="B8" s="391"/>
-      <x:c r="C8" s="398"/>
-      <x:c r="D8" s="398"/>
-      <x:c r="E8" s="403"/>
-      <x:c r="F8" s="403"/>
-      <x:c r="G8" s="401"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
-  </x:mergeCells>
-  <x:dataValidations count="3">
-    <x:dataValidation type="list" sqref="C3:C1000">
-      <x:formula1>Library!$B$3:$B$59</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="D3:D1000">
-      <x:formula1>Library!$A$62</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="decimal" operator="greaterThanOrEqual" sqref="E3:F1000">
-      <x:formula1>0</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>